--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252252</v>
+        <v>130252693</v>
       </c>
       <c r="B19" t="n">
-        <v>78938</v>
+        <v>78937</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497077</v>
+        <v>497066</v>
       </c>
       <c r="R19" t="n">
-        <v>6830219</v>
+        <v>6830179</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,29 +2592,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252693</v>
+        <v>130252252</v>
       </c>
       <c r="B20" t="n">
-        <v>78937</v>
+        <v>78938</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497066</v>
+        <v>497077</v>
       </c>
       <c r="R20" t="n">
-        <v>6830179</v>
+        <v>6830219</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,18 +2699,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130252250</v>
+        <v>130252263</v>
       </c>
       <c r="B39" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4657,35 +4657,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4693,10 +4684,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497113</v>
+        <v>497344</v>
       </c>
       <c r="R39" t="n">
-        <v>6830338</v>
+        <v>6830116</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4728,7 +4719,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4738,12 +4729,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Var i ett meståg med bla. trädkrypare</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4752,6 +4743,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4770,10 +4762,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252263</v>
+        <v>130252250</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4781,26 +4773,35 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4808,10 +4809,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497344</v>
+        <v>497113</v>
       </c>
       <c r="R40" t="n">
-        <v>6830116</v>
+        <v>6830338</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4843,7 +4844,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4853,12 +4854,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Var i ett meståg med bla. trädkrypare</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,7 +4868,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252690</v>
+        <v>130252254</v>
       </c>
       <c r="B43" t="n">
-        <v>78937</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497163</v>
+        <v>497253</v>
       </c>
       <c r="R43" t="n">
-        <v>6830392</v>
+        <v>6830488</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,57 +5195,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252686</v>
+        <v>130252248</v>
       </c>
       <c r="B44" t="n">
-        <v>78938</v>
+        <v>57016</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497085</v>
+        <v>497253</v>
       </c>
       <c r="R44" t="n">
-        <v>6830215</v>
+        <v>6830469</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5277,7 +5285,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5287,7 +5295,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5302,65 +5315,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252248</v>
+        <v>130252686</v>
       </c>
       <c r="B45" t="n">
-        <v>57016</v>
+        <v>78938</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497253</v>
+        <v>497085</v>
       </c>
       <c r="R45" t="n">
-        <v>6830469</v>
+        <v>6830215</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5392,7 +5397,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5402,12 +5407,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5422,44 +5422,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252254</v>
+        <v>130252690</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>78937</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497253</v>
+        <v>497163</v>
       </c>
       <c r="R46" t="n">
-        <v>6830488</v>
+        <v>6830392</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5529,12 +5529,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6434,10 +6434,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130256299</v>
+        <v>130257277</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497390</v>
+        <v>497092</v>
       </c>
       <c r="R56" t="n">
-        <v>6830226</v>
+        <v>6830180</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6502,19 +6502,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6529,22 +6519,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130257277</v>
+        <v>130256299</v>
       </c>
       <c r="B57" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6552,21 +6542,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6576,10 +6566,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497092</v>
+        <v>497390</v>
       </c>
       <c r="R57" t="n">
-        <v>6830180</v>
+        <v>6830226</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6609,9 +6599,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6626,12 +6626,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -8282,56 +8282,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130256313</v>
+        <v>130257275</v>
       </c>
       <c r="B74" t="n">
-        <v>93010</v>
+        <v>78937</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497260</v>
+        <v>497096</v>
       </c>
       <c r="R74" t="n">
-        <v>6830540</v>
+        <v>6830218</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8361,85 +8350,85 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130256306</v>
+        <v>130256313</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>93010</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497253</v>
+        <v>497260</v>
       </c>
       <c r="R75" t="n">
-        <v>6830351</v>
+        <v>6830540</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8471,7 +8460,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8481,7 +8470,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8490,6 +8479,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8508,10 +8498,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130257275</v>
+        <v>130256306</v>
       </c>
       <c r="B76" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8519,21 +8509,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8543,10 +8533,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497096</v>
+        <v>497253</v>
       </c>
       <c r="R76" t="n">
-        <v>6830218</v>
+        <v>6830351</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8576,9 +8566,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8593,12 +8593,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9110,10 +9110,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130257266</v>
+        <v>130257261</v>
       </c>
       <c r="B82" t="n">
-        <v>57826</v>
+        <v>79799</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9121,42 +9121,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497142</v>
+        <v>497107</v>
       </c>
       <c r="R82" t="n">
-        <v>6830327</v>
+        <v>6830221</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9215,10 +9207,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130257261</v>
+        <v>130257266</v>
       </c>
       <c r="B83" t="n">
-        <v>79799</v>
+        <v>57826</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9226,34 +9218,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497107</v>
+        <v>497142</v>
       </c>
       <c r="R83" t="n">
-        <v>6830221</v>
+        <v>6830327</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10770,10 +10770,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130257290</v>
+        <v>130256296</v>
       </c>
       <c r="B98" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10781,21 +10781,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10805,10 +10805,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497200</v>
+        <v>497074</v>
       </c>
       <c r="R98" t="n">
-        <v>6830326</v>
+        <v>6830224</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10838,9 +10838,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10855,22 +10865,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130256296</v>
+        <v>130257294</v>
       </c>
       <c r="B99" t="n">
-        <v>78937</v>
+        <v>78187</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10878,21 +10888,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10902,10 +10912,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497074</v>
+        <v>497072</v>
       </c>
       <c r="R99" t="n">
-        <v>6830224</v>
+        <v>6830282</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10935,19 +10945,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>09:40</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10962,22 +10962,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130257294</v>
+        <v>130257286</v>
       </c>
       <c r="B100" t="n">
-        <v>78187</v>
+        <v>79180</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10985,21 +10985,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497072</v>
+        <v>497240</v>
       </c>
       <c r="R100" t="n">
-        <v>6830282</v>
+        <v>6830306</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11071,7 +11071,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130257286</v>
+        <v>130257290</v>
       </c>
       <c r="B101" t="n">
         <v>79180</v>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497240</v>
+        <v>497200</v>
       </c>
       <c r="R101" t="n">
-        <v>6830306</v>
+        <v>6830326</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130252273</v>
+        <v>130252255</v>
       </c>
       <c r="B2" t="n">
-        <v>93010</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497114</v>
+        <v>497263</v>
       </c>
       <c r="R2" t="n">
-        <v>6830195</v>
+        <v>6830449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252255</v>
+        <v>130252273</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>93010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497263</v>
+        <v>497114</v>
       </c>
       <c r="R3" t="n">
-        <v>6830449</v>
+        <v>6830195</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2825,32 +2825,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252272</v>
+        <v>130252696</v>
       </c>
       <c r="B22" t="n">
-        <v>93010</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497084</v>
+        <v>497147</v>
       </c>
       <c r="R22" t="n">
-        <v>6830218</v>
+        <v>6830398</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,22 +2920,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252696</v>
+        <v>130252691</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,21 +2943,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497147</v>
+        <v>497108</v>
       </c>
       <c r="R23" t="n">
-        <v>6830398</v>
+        <v>6830371</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,32 +3039,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252691</v>
+        <v>130252272</v>
       </c>
       <c r="B24" t="n">
-        <v>78937</v>
+        <v>93010</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497108</v>
+        <v>497084</v>
       </c>
       <c r="R24" t="n">
-        <v>6830371</v>
+        <v>6830218</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,12 +3134,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252254</v>
+        <v>130252690</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>78937</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497253</v>
+        <v>497163</v>
       </c>
       <c r="R43" t="n">
-        <v>6830488</v>
+        <v>6830392</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,65 +5195,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252248</v>
+        <v>130252686</v>
       </c>
       <c r="B44" t="n">
-        <v>57016</v>
+        <v>78938</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497253</v>
+        <v>497085</v>
       </c>
       <c r="R44" t="n">
-        <v>6830469</v>
+        <v>6830215</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5285,7 +5277,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5295,12 +5287,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5315,57 +5302,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252686</v>
+        <v>130252248</v>
       </c>
       <c r="B45" t="n">
-        <v>78938</v>
+        <v>57016</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497085</v>
+        <v>497253</v>
       </c>
       <c r="R45" t="n">
-        <v>6830215</v>
+        <v>6830469</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5397,7 +5392,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5407,7 +5402,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5422,44 +5422,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252690</v>
+        <v>130252254</v>
       </c>
       <c r="B46" t="n">
-        <v>78937</v>
+        <v>8451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497163</v>
+        <v>497253</v>
       </c>
       <c r="R46" t="n">
-        <v>6830392</v>
+        <v>6830488</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5529,12 +5529,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6434,10 +6434,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130257277</v>
+        <v>130256299</v>
       </c>
       <c r="B56" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497092</v>
+        <v>497390</v>
       </c>
       <c r="R56" t="n">
-        <v>6830180</v>
+        <v>6830226</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6502,9 +6502,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6519,22 +6529,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130256299</v>
+        <v>130257277</v>
       </c>
       <c r="B57" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6542,21 +6552,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6566,10 +6576,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497390</v>
+        <v>497092</v>
       </c>
       <c r="R57" t="n">
-        <v>6830226</v>
+        <v>6830180</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6599,19 +6609,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6626,12 +6626,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7551,45 +7551,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130257281</v>
+        <v>130257270</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497275</v>
+        <v>497113</v>
       </c>
       <c r="R67" t="n">
-        <v>6830388</v>
+        <v>6830234</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7630,6 +7639,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7648,10 +7658,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130256291</v>
+        <v>130257281</v>
       </c>
       <c r="B68" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7659,21 +7669,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7683,10 +7693,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497251</v>
+        <v>497275</v>
       </c>
       <c r="R68" t="n">
-        <v>6830491</v>
+        <v>6830388</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7716,19 +7726,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7743,44 +7743,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130257293</v>
+        <v>130256291</v>
       </c>
       <c r="B69" t="n">
-        <v>93010</v>
+        <v>78937</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497087</v>
+        <v>497251</v>
       </c>
       <c r="R69" t="n">
-        <v>6830238</v>
+        <v>6830491</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7823,9 +7823,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7840,22 +7850,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130257270</v>
+        <v>130257293</v>
       </c>
       <c r="B70" t="n">
-        <v>8451</v>
+        <v>93010</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7863,43 +7873,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497113</v>
+        <v>497087</v>
       </c>
       <c r="R70" t="n">
-        <v>6830234</v>
+        <v>6830238</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7940,7 +7941,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130252255</v>
+        <v>130252273</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>93010</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497263</v>
+        <v>497114</v>
       </c>
       <c r="R2" t="n">
-        <v>6830449</v>
+        <v>6830195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252273</v>
+        <v>130252255</v>
       </c>
       <c r="B3" t="n">
-        <v>93010</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497114</v>
+        <v>497263</v>
       </c>
       <c r="R3" t="n">
-        <v>6830195</v>
+        <v>6830449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252693</v>
+        <v>130252252</v>
       </c>
       <c r="B19" t="n">
-        <v>78937</v>
+        <v>78938</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497066</v>
+        <v>497077</v>
       </c>
       <c r="R19" t="n">
-        <v>6830179</v>
+        <v>6830219</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,28 +2592,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252252</v>
+        <v>130252693</v>
       </c>
       <c r="B20" t="n">
-        <v>78938</v>
+        <v>78937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497077</v>
+        <v>497066</v>
       </c>
       <c r="R20" t="n">
-        <v>6830219</v>
+        <v>6830179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2699,19 +2700,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252696</v>
+        <v>130252272</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>93010</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497147</v>
+        <v>497084</v>
       </c>
       <c r="R22" t="n">
-        <v>6830398</v>
+        <v>6830218</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,22 +2920,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252691</v>
+        <v>130252696</v>
       </c>
       <c r="B23" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,21 +2943,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497108</v>
+        <v>497147</v>
       </c>
       <c r="R23" t="n">
-        <v>6830371</v>
+        <v>6830398</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,32 +3039,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252272</v>
+        <v>130252691</v>
       </c>
       <c r="B24" t="n">
-        <v>93010</v>
+        <v>78937</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497084</v>
+        <v>497108</v>
       </c>
       <c r="R24" t="n">
-        <v>6830218</v>
+        <v>6830371</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,12 +3134,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130252263</v>
+        <v>130252250</v>
       </c>
       <c r="B39" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4657,26 +4657,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4684,10 +4693,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497344</v>
+        <v>497113</v>
       </c>
       <c r="R39" t="n">
-        <v>6830116</v>
+        <v>6830338</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4719,7 +4728,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4729,12 +4738,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Var i ett meståg med bla. trädkrypare</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,7 +4752,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4762,10 +4770,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252250</v>
+        <v>130252263</v>
       </c>
       <c r="B40" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4773,35 +4781,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4809,10 +4808,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497113</v>
+        <v>497344</v>
       </c>
       <c r="R40" t="n">
-        <v>6830338</v>
+        <v>6830116</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4844,7 +4843,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4854,12 +4853,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Var i ett meståg med bla. trädkrypare</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4868,6 +4867,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252690</v>
+        <v>130252254</v>
       </c>
       <c r="B43" t="n">
-        <v>78937</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497163</v>
+        <v>497253</v>
       </c>
       <c r="R43" t="n">
-        <v>6830392</v>
+        <v>6830488</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,57 +5195,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252686</v>
+        <v>130252248</v>
       </c>
       <c r="B44" t="n">
-        <v>78938</v>
+        <v>57016</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497085</v>
+        <v>497253</v>
       </c>
       <c r="R44" t="n">
-        <v>6830215</v>
+        <v>6830469</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5277,7 +5285,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5287,7 +5295,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5302,65 +5315,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252248</v>
+        <v>130252686</v>
       </c>
       <c r="B45" t="n">
-        <v>57016</v>
+        <v>78938</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497253</v>
+        <v>497085</v>
       </c>
       <c r="R45" t="n">
-        <v>6830469</v>
+        <v>6830215</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5392,7 +5397,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5402,12 +5407,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5422,44 +5422,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252254</v>
+        <v>130252690</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>78937</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497253</v>
+        <v>497163</v>
       </c>
       <c r="R46" t="n">
-        <v>6830488</v>
+        <v>6830392</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5529,12 +5529,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -7551,54 +7551,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130257270</v>
+        <v>130257281</v>
       </c>
       <c r="B67" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497113</v>
+        <v>497275</v>
       </c>
       <c r="R67" t="n">
-        <v>6830234</v>
+        <v>6830388</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7639,7 +7630,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7658,10 +7648,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130257281</v>
+        <v>130256291</v>
       </c>
       <c r="B68" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7669,21 +7659,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7693,10 +7683,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497275</v>
+        <v>497251</v>
       </c>
       <c r="R68" t="n">
-        <v>6830388</v>
+        <v>6830491</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7726,9 +7716,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7743,44 +7743,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130256291</v>
+        <v>130257293</v>
       </c>
       <c r="B69" t="n">
-        <v>78937</v>
+        <v>93010</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497251</v>
+        <v>497087</v>
       </c>
       <c r="R69" t="n">
-        <v>6830491</v>
+        <v>6830238</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7823,19 +7823,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7850,22 +7840,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130257293</v>
+        <v>130257270</v>
       </c>
       <c r="B70" t="n">
-        <v>93010</v>
+        <v>8451</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7873,34 +7863,43 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497087</v>
+        <v>497113</v>
       </c>
       <c r="R70" t="n">
-        <v>6830238</v>
+        <v>6830234</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7941,6 +7940,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -10770,10 +10770,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130256296</v>
+        <v>130257290</v>
       </c>
       <c r="B98" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10781,21 +10781,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10805,10 +10805,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497074</v>
+        <v>497200</v>
       </c>
       <c r="R98" t="n">
-        <v>6830224</v>
+        <v>6830326</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10838,19 +10838,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>09:40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10865,22 +10855,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130257294</v>
+        <v>130256296</v>
       </c>
       <c r="B99" t="n">
-        <v>78187</v>
+        <v>78937</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10888,21 +10878,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10912,10 +10902,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497072</v>
+        <v>497074</v>
       </c>
       <c r="R99" t="n">
-        <v>6830282</v>
+        <v>6830224</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10945,9 +10935,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10962,22 +10962,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130257286</v>
+        <v>130257294</v>
       </c>
       <c r="B100" t="n">
-        <v>79180</v>
+        <v>78187</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10985,21 +10985,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497240</v>
+        <v>497072</v>
       </c>
       <c r="R100" t="n">
-        <v>6830306</v>
+        <v>6830282</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11071,7 +11071,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130257290</v>
+        <v>130257286</v>
       </c>
       <c r="B101" t="n">
         <v>79180</v>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497200</v>
+        <v>497240</v>
       </c>
       <c r="R101" t="n">
-        <v>6830326</v>
+        <v>6830306</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11168,10 +11168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256292</v>
+        <v>130256312</v>
       </c>
       <c r="B102" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497168</v>
+        <v>497244</v>
       </c>
       <c r="R102" t="n">
-        <v>6830310</v>
+        <v>6830538</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11275,10 +11275,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256312</v>
+        <v>130256286</v>
       </c>
       <c r="B103" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497244</v>
+        <v>497251</v>
       </c>
       <c r="R103" t="n">
-        <v>6830538</v>
+        <v>6830494</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11382,10 +11382,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256286</v>
+        <v>130256292</v>
       </c>
       <c r="B104" t="n">
-        <v>78938</v>
+        <v>78937</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11393,21 +11393,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497251</v>
+        <v>497168</v>
       </c>
       <c r="R104" t="n">
-        <v>6830494</v>
+        <v>6830310</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130252273</v>
       </c>
       <c r="B2" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252694</v>
+        <v>130252256</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497321</v>
+        <v>497168</v>
       </c>
       <c r="R4" t="n">
-        <v>6830343</v>
+        <v>6830390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252270</v>
+        <v>130252694</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497118</v>
+        <v>497321</v>
       </c>
       <c r="R5" t="n">
-        <v>6830323</v>
+        <v>6830343</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,44 +1091,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252256</v>
+        <v>130252270</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497168</v>
+        <v>497118</v>
       </c>
       <c r="R6" t="n">
-        <v>6830390</v>
+        <v>6830323</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252262</v>
+        <v>130252271</v>
       </c>
       <c r="B7" t="n">
-        <v>78937</v>
+        <v>93013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497260</v>
+        <v>497241</v>
       </c>
       <c r="R7" t="n">
-        <v>6830494</v>
+        <v>6830507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,7 +1299,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1318,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130252259</v>
+        <v>130252262</v>
       </c>
       <c r="B8" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497236</v>
+        <v>497260</v>
       </c>
       <c r="R8" t="n">
-        <v>6830502</v>
+        <v>6830494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1398,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,6 +1406,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1425,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252271</v>
+        <v>130252259</v>
       </c>
       <c r="B9" t="n">
-        <v>93010</v>
+        <v>78940</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497241</v>
+        <v>497236</v>
       </c>
       <c r="R9" t="n">
-        <v>6830507</v>
+        <v>6830502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,7 +1535,7 @@
         <v>130252269</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252244</v>
+        <v>130252251</v>
       </c>
       <c r="B11" t="n">
-        <v>79799</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,34 +1650,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497260</v>
+        <v>497063</v>
       </c>
       <c r="R11" t="n">
-        <v>6830494</v>
+        <v>6830279</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252695</v>
+        <v>130252244</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,21 +1765,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497166</v>
+        <v>497260</v>
       </c>
       <c r="R12" t="n">
-        <v>6830368</v>
+        <v>6830494</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,22 +1849,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252251</v>
+        <v>130252695</v>
       </c>
       <c r="B13" t="n">
-        <v>57985</v>
+        <v>79183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,42 +1872,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497063</v>
+        <v>497166</v>
       </c>
       <c r="R13" t="n">
-        <v>6830279</v>
+        <v>6830368</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,12 +1956,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1971,7 +1971,7 @@
         <v>130252258</v>
       </c>
       <c r="B14" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>130252245</v>
       </c>
       <c r="B15" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>130252688</v>
       </c>
       <c r="B16" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>130252261</v>
       </c>
       <c r="B17" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252252</v>
+        <v>130252693</v>
       </c>
       <c r="B19" t="n">
-        <v>78938</v>
+        <v>78940</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497077</v>
+        <v>497066</v>
       </c>
       <c r="R19" t="n">
-        <v>6830219</v>
+        <v>6830179</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,29 +2592,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252693</v>
+        <v>130252252</v>
       </c>
       <c r="B20" t="n">
-        <v>78937</v>
+        <v>78941</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497066</v>
+        <v>497077</v>
       </c>
       <c r="R20" t="n">
-        <v>6830179</v>
+        <v>6830219</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,50 +2699,51 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252264</v>
+        <v>130252272</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>93013</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497334</v>
+        <v>497084</v>
       </c>
       <c r="R21" t="n">
-        <v>6830124</v>
+        <v>6830218</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,32 +2825,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252272</v>
+        <v>130252696</v>
       </c>
       <c r="B22" t="n">
-        <v>93010</v>
+        <v>79183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497084</v>
+        <v>497147</v>
       </c>
       <c r="R22" t="n">
-        <v>6830218</v>
+        <v>6830398</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,22 +2920,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252696</v>
+        <v>130252691</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,21 +2943,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497147</v>
+        <v>497108</v>
       </c>
       <c r="R23" t="n">
-        <v>6830398</v>
+        <v>6830371</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252691</v>
+        <v>130252264</v>
       </c>
       <c r="B24" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3050,21 +3050,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497108</v>
+        <v>497334</v>
       </c>
       <c r="R24" t="n">
-        <v>6830371</v>
+        <v>6830124</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,44 +3134,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130252684</v>
+        <v>130252253</v>
       </c>
       <c r="B25" t="n">
-        <v>78938</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497063</v>
+        <v>497334</v>
       </c>
       <c r="R25" t="n">
-        <v>6830346</v>
+        <v>6830121</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,22 +3241,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252685</v>
+        <v>130252267</v>
       </c>
       <c r="B26" t="n">
-        <v>78938</v>
+        <v>79183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,21 +3264,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497071</v>
+        <v>497178</v>
       </c>
       <c r="R26" t="n">
-        <v>6830207</v>
+        <v>6830332</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,12 +3348,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3363,7 +3363,7 @@
         <v>130252698</v>
       </c>
       <c r="B27" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252267</v>
+        <v>130252685</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>78941</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,21 +3479,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497178</v>
+        <v>497071</v>
       </c>
       <c r="R28" t="n">
-        <v>6830332</v>
+        <v>6830207</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,44 +3563,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252253</v>
+        <v>130252684</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>78941</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497334</v>
+        <v>497063</v>
       </c>
       <c r="R29" t="n">
-        <v>6830121</v>
+        <v>6830346</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3670,22 +3670,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252689</v>
+        <v>130252268</v>
       </c>
       <c r="B30" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497261</v>
+        <v>497175</v>
       </c>
       <c r="R30" t="n">
-        <v>6830425</v>
+        <v>6830390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,22 +3777,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252268</v>
+        <v>130252689</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,21 +3800,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497175</v>
+        <v>497261</v>
       </c>
       <c r="R31" t="n">
-        <v>6830390</v>
+        <v>6830425</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3884,12 +3884,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
         <v>130252265</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>130252697</v>
       </c>
       <c r="B34" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>130252682</v>
       </c>
       <c r="B35" t="n">
-        <v>78938</v>
+        <v>78941</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>130252692</v>
       </c>
       <c r="B36" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>130252246</v>
       </c>
       <c r="B37" t="n">
-        <v>79770</v>
+        <v>79773</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252260</v>
+        <v>130252250</v>
       </c>
       <c r="B38" t="n">
-        <v>78937</v>
+        <v>57985</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,34 +4550,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497077</v>
+        <v>497113</v>
       </c>
       <c r="R38" t="n">
-        <v>6830219</v>
+        <v>6830338</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4609,7 +4621,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4619,7 +4631,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Var i ett meståg med bla. trädkrypare</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4646,10 +4663,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130252250</v>
+        <v>130252683</v>
       </c>
       <c r="B39" t="n">
-        <v>57985</v>
+        <v>78941</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4657,46 +4674,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497113</v>
+        <v>497089</v>
       </c>
       <c r="R39" t="n">
-        <v>6830338</v>
+        <v>6830358</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4728,7 +4733,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4738,12 +4743,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Var i ett meståg med bla. trädkrypare</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4758,22 +4758,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252263</v>
+        <v>130252260</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4781,37 +4781,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497344</v>
+        <v>497077</v>
       </c>
       <c r="R40" t="n">
-        <v>6830116</v>
+        <v>6830219</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4843,7 +4840,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4853,12 +4850,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,7 +4859,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4886,10 +4877,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252683</v>
+        <v>130252263</v>
       </c>
       <c r="B41" t="n">
-        <v>78938</v>
+        <v>79183</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,34 +4888,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497089</v>
+        <v>497344</v>
       </c>
       <c r="R41" t="n">
-        <v>6830358</v>
+        <v>6830116</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4956,7 +4950,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4966,7 +4960,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4975,18 +4974,19 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4996,7 +4996,7 @@
         <v>130252266</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5100,10 +5100,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252254</v>
+        <v>130252248</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>57016</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5111,24 +5111,32 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
@@ -5138,7 +5146,7 @@
         <v>497253</v>
       </c>
       <c r="R43" t="n">
-        <v>6830488</v>
+        <v>6830469</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,7 +5178,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5180,7 +5188,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5207,10 +5220,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252248</v>
+        <v>130252254</v>
       </c>
       <c r="B44" t="n">
-        <v>57016</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5218,32 +5231,24 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
@@ -5253,7 +5258,7 @@
         <v>497253</v>
       </c>
       <c r="R44" t="n">
-        <v>6830469</v>
+        <v>6830488</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5285,7 +5290,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5295,12 +5300,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,10 +5327,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252686</v>
+        <v>130252690</v>
       </c>
       <c r="B45" t="n">
-        <v>78938</v>
+        <v>78940</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5338,21 +5338,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497085</v>
+        <v>497163</v>
       </c>
       <c r="R45" t="n">
-        <v>6830215</v>
+        <v>6830392</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5434,10 +5434,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252690</v>
+        <v>130252686</v>
       </c>
       <c r="B46" t="n">
-        <v>78937</v>
+        <v>78941</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5445,21 +5445,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497163</v>
+        <v>497085</v>
       </c>
       <c r="R46" t="n">
-        <v>6830392</v>
+        <v>6830215</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5544,7 +5544,7 @@
         <v>130256297</v>
       </c>
       <c r="B47" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>130257279</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>130256288</v>
       </c>
       <c r="B49" t="n">
-        <v>78938</v>
+        <v>78941</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130257295</v>
+        <v>130257265</v>
       </c>
       <c r="B50" t="n">
-        <v>78187</v>
+        <v>91752</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5863,21 +5863,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6487</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497072</v>
+        <v>497131</v>
       </c>
       <c r="R50" t="n">
-        <v>6830261</v>
+        <v>6830311</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130257276</v>
+        <v>130257295</v>
       </c>
       <c r="B51" t="n">
-        <v>78937</v>
+        <v>78190</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497082</v>
+        <v>497072</v>
       </c>
       <c r="R51" t="n">
-        <v>6830202</v>
+        <v>6830261</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130257271</v>
+        <v>130257276</v>
       </c>
       <c r="B52" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497270</v>
+        <v>497082</v>
       </c>
       <c r="R52" t="n">
-        <v>6830422</v>
+        <v>6830202</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130257265</v>
+        <v>130257271</v>
       </c>
       <c r="B53" t="n">
-        <v>91749</v>
+        <v>78940</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497131</v>
+        <v>497270</v>
       </c>
       <c r="R53" t="n">
-        <v>6830311</v>
+        <v>6830422</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,7 +6243,7 @@
         <v>130257280</v>
       </c>
       <c r="B54" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>130257291</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130256299</v>
+        <v>130257277</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497390</v>
+        <v>497092</v>
       </c>
       <c r="R56" t="n">
-        <v>6830226</v>
+        <v>6830180</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6502,19 +6502,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6529,22 +6519,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130257277</v>
+        <v>130256299</v>
       </c>
       <c r="B57" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6552,21 +6542,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6576,10 +6566,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497092</v>
+        <v>497390</v>
       </c>
       <c r="R57" t="n">
-        <v>6830180</v>
+        <v>6830226</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6609,9 +6599,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6626,12 +6626,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
         <v>130257284</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6735,10 +6735,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130257278</v>
+        <v>130256311</v>
       </c>
       <c r="B59" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497327</v>
+        <v>497159</v>
       </c>
       <c r="R59" t="n">
-        <v>6830133</v>
+        <v>6830345</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6803,9 +6803,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6820,22 +6830,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130256311</v>
+        <v>130257278</v>
       </c>
       <c r="B60" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6867,10 +6877,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497159</v>
+        <v>497327</v>
       </c>
       <c r="R60" t="n">
-        <v>6830345</v>
+        <v>6830133</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6900,19 +6910,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6927,12 +6927,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6942,7 +6942,7 @@
         <v>130257262</v>
       </c>
       <c r="B61" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7036,10 +7036,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130257287</v>
+        <v>130256304</v>
       </c>
       <c r="B62" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497234</v>
+        <v>497247</v>
       </c>
       <c r="R62" t="n">
-        <v>6830313</v>
+        <v>6830499</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7104,9 +7104,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7121,22 +7131,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130257297</v>
+        <v>130256309</v>
       </c>
       <c r="B63" t="n">
-        <v>78583</v>
+        <v>79183</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7144,21 +7154,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7168,10 +7178,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497072</v>
+        <v>497156</v>
       </c>
       <c r="R63" t="n">
-        <v>6830261</v>
+        <v>6830327</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7201,9 +7211,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7218,22 +7238,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130256307</v>
+        <v>130257287</v>
       </c>
       <c r="B64" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7265,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497221</v>
+        <v>497234</v>
       </c>
       <c r="R64" t="n">
-        <v>6830314</v>
+        <v>6830313</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7298,19 +7318,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7325,22 +7335,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130256309</v>
+        <v>130256307</v>
       </c>
       <c r="B65" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7372,10 +7382,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497156</v>
+        <v>497221</v>
       </c>
       <c r="R65" t="n">
-        <v>6830327</v>
+        <v>6830314</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7407,7 +7417,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7417,7 +7427,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7444,10 +7454,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130256304</v>
+        <v>130257297</v>
       </c>
       <c r="B66" t="n">
-        <v>79180</v>
+        <v>78586</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7455,21 +7465,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7479,10 +7489,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497247</v>
+        <v>497072</v>
       </c>
       <c r="R66" t="n">
-        <v>6830499</v>
+        <v>6830261</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7512,19 +7522,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7539,44 +7539,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130257281</v>
+        <v>130257293</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>93013</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497275</v>
+        <v>497087</v>
       </c>
       <c r="R67" t="n">
-        <v>6830388</v>
+        <v>6830238</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7648,10 +7648,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130256291</v>
+        <v>130257281</v>
       </c>
       <c r="B68" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7659,21 +7659,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497251</v>
+        <v>497275</v>
       </c>
       <c r="R68" t="n">
-        <v>6830491</v>
+        <v>6830388</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7716,19 +7716,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7743,44 +7733,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130257293</v>
+        <v>130256291</v>
       </c>
       <c r="B69" t="n">
-        <v>93010</v>
+        <v>78940</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7790,10 +7780,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497087</v>
+        <v>497251</v>
       </c>
       <c r="R69" t="n">
-        <v>6830238</v>
+        <v>6830491</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7823,9 +7813,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7840,12 +7840,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7959,45 +7959,56 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256303</v>
+        <v>130256314</v>
       </c>
       <c r="B71" t="n">
-        <v>79180</v>
+        <v>93013</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497291</v>
+        <v>497242</v>
       </c>
       <c r="R71" t="n">
-        <v>6830488</v>
+        <v>6830510</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8029,7 +8040,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8039,7 +8050,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8048,6 +8059,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8066,56 +8078,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130256314</v>
+        <v>130256303</v>
       </c>
       <c r="B72" t="n">
-        <v>93010</v>
+        <v>79183</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497242</v>
+        <v>497291</v>
       </c>
       <c r="R72" t="n">
-        <v>6830510</v>
+        <v>6830488</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8147,7 +8148,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8157,7 +8158,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8166,7 +8167,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8188,7 +8188,7 @@
         <v>130257263</v>
       </c>
       <c r="B73" t="n">
-        <v>79770</v>
+        <v>79773</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8282,45 +8282,56 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130257275</v>
+        <v>130256313</v>
       </c>
       <c r="B74" t="n">
-        <v>78937</v>
+        <v>93013</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497096</v>
+        <v>497260</v>
       </c>
       <c r="R74" t="n">
-        <v>6830218</v>
+        <v>6830540</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8350,85 +8361,85 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130256313</v>
+        <v>130257275</v>
       </c>
       <c r="B75" t="n">
-        <v>93010</v>
+        <v>78940</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497260</v>
+        <v>497096</v>
       </c>
       <c r="R75" t="n">
-        <v>6830540</v>
+        <v>6830218</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8458,40 +8469,29 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8501,7 +8501,7 @@
         <v>130256306</v>
       </c>
       <c r="B76" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130257285</v>
+        <v>130257282</v>
       </c>
       <c r="B77" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497250</v>
+        <v>497252</v>
       </c>
       <c r="R77" t="n">
-        <v>6830356</v>
+        <v>6830372</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8702,10 +8702,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130257292</v>
+        <v>130257285</v>
       </c>
       <c r="B78" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8737,10 +8737,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497138</v>
+        <v>497250</v>
       </c>
       <c r="R78" t="n">
-        <v>6830320</v>
+        <v>6830356</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8799,10 +8799,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130257282</v>
+        <v>130257292</v>
       </c>
       <c r="B79" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497252</v>
+        <v>497138</v>
       </c>
       <c r="R79" t="n">
-        <v>6830372</v>
+        <v>6830320</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8899,7 +8899,7 @@
         <v>130256310</v>
       </c>
       <c r="B80" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>130256301</v>
       </c>
       <c r="B81" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9110,10 +9110,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130257261</v>
+        <v>130257289</v>
       </c>
       <c r="B82" t="n">
-        <v>79799</v>
+        <v>79183</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9121,21 +9121,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497107</v>
+        <v>497222</v>
       </c>
       <c r="R82" t="n">
-        <v>6830221</v>
+        <v>6830325</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9207,10 +9207,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130257266</v>
+        <v>130257261</v>
       </c>
       <c r="B83" t="n">
-        <v>57826</v>
+        <v>79802</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9218,42 +9218,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497142</v>
+        <v>497107</v>
       </c>
       <c r="R83" t="n">
-        <v>6830327</v>
+        <v>6830221</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9315,7 +9307,7 @@
         <v>130256302</v>
       </c>
       <c r="B84" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9419,10 +9411,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130257289</v>
+        <v>130257266</v>
       </c>
       <c r="B85" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9430,34 +9422,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497222</v>
+        <v>497142</v>
       </c>
       <c r="R85" t="n">
-        <v>6830325</v>
+        <v>6830327</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9516,45 +9516,56 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130257274</v>
+        <v>130256315</v>
       </c>
       <c r="B86" t="n">
-        <v>78937</v>
+        <v>93013</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497107</v>
+        <v>497261</v>
       </c>
       <c r="R86" t="n">
-        <v>6830221</v>
+        <v>6830529</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9584,74 +9595,94 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130257268</v>
+        <v>130256289</v>
       </c>
       <c r="B87" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497074</v>
+        <v>497101</v>
       </c>
       <c r="R87" t="n">
-        <v>6830292</v>
+        <v>6830183</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9681,39 +9712,50 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130257283</v>
+        <v>130257274</v>
       </c>
       <c r="B88" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9721,21 +9763,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9745,10 +9787,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497244</v>
+        <v>497107</v>
       </c>
       <c r="R88" t="n">
-        <v>6830388</v>
+        <v>6830221</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9807,56 +9849,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130256315</v>
+        <v>130257268</v>
       </c>
       <c r="B89" t="n">
-        <v>93010</v>
+        <v>79183</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497261</v>
+        <v>497074</v>
       </c>
       <c r="R89" t="n">
-        <v>6830529</v>
+        <v>6830292</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9886,94 +9917,74 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130256289</v>
+        <v>130257283</v>
       </c>
       <c r="B90" t="n">
-        <v>8451</v>
+        <v>79183</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497101</v>
+        <v>497244</v>
       </c>
       <c r="R90" t="n">
-        <v>6830183</v>
+        <v>6830388</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10003,50 +10014,39 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130256293</v>
+        <v>130256300</v>
       </c>
       <c r="B91" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10054,21 +10054,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497117</v>
+        <v>497391</v>
       </c>
       <c r="R91" t="n">
-        <v>6830376</v>
+        <v>6830230</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10150,10 +10150,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130256305</v>
+        <v>130256293</v>
       </c>
       <c r="B92" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10161,21 +10161,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497258</v>
+        <v>497117</v>
       </c>
       <c r="R92" t="n">
-        <v>6830560</v>
+        <v>6830376</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10257,10 +10257,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130256308</v>
+        <v>130256305</v>
       </c>
       <c r="B93" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497137</v>
+        <v>497258</v>
       </c>
       <c r="R93" t="n">
-        <v>6830325</v>
+        <v>6830560</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10364,10 +10364,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130256300</v>
+        <v>130256308</v>
       </c>
       <c r="B94" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10399,10 +10399,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497391</v>
+        <v>497137</v>
       </c>
       <c r="R94" t="n">
-        <v>6830230</v>
+        <v>6830325</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10474,7 +10474,7 @@
         <v>130257272</v>
       </c>
       <c r="B95" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>130257288</v>
       </c>
       <c r="B96" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10770,10 +10770,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130257290</v>
+        <v>130256296</v>
       </c>
       <c r="B98" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10781,21 +10781,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10805,10 +10805,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497200</v>
+        <v>497074</v>
       </c>
       <c r="R98" t="n">
-        <v>6830326</v>
+        <v>6830224</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10838,9 +10838,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10855,22 +10865,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130256296</v>
+        <v>130257294</v>
       </c>
       <c r="B99" t="n">
-        <v>78937</v>
+        <v>78190</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10878,21 +10888,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10902,10 +10912,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497074</v>
+        <v>497072</v>
       </c>
       <c r="R99" t="n">
-        <v>6830224</v>
+        <v>6830282</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10935,19 +10945,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>09:40</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10962,22 +10962,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130257294</v>
+        <v>130257290</v>
       </c>
       <c r="B100" t="n">
-        <v>78187</v>
+        <v>79183</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10985,21 +10985,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497072</v>
+        <v>497200</v>
       </c>
       <c r="R100" t="n">
-        <v>6830282</v>
+        <v>6830326</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11074,7 +11074,7 @@
         <v>130257286</v>
       </c>
       <c r="B101" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11168,10 +11168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256312</v>
+        <v>130256292</v>
       </c>
       <c r="B102" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497244</v>
+        <v>497168</v>
       </c>
       <c r="R102" t="n">
-        <v>6830538</v>
+        <v>6830310</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11275,10 +11275,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256286</v>
+        <v>130256312</v>
       </c>
       <c r="B103" t="n">
-        <v>78938</v>
+        <v>79183</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497251</v>
+        <v>497244</v>
       </c>
       <c r="R103" t="n">
-        <v>6830494</v>
+        <v>6830538</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11382,10 +11382,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256292</v>
+        <v>130256286</v>
       </c>
       <c r="B104" t="n">
-        <v>78937</v>
+        <v>78941</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11393,21 +11393,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497168</v>
+        <v>497251</v>
       </c>
       <c r="R104" t="n">
-        <v>6830310</v>
+        <v>6830494</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130252273</v>
       </c>
       <c r="B2" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252694</v>
+        <v>130252270</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497321</v>
+        <v>497118</v>
       </c>
       <c r="R5" t="n">
-        <v>6830343</v>
+        <v>6830323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252270</v>
+        <v>130252694</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497118</v>
+        <v>497321</v>
       </c>
       <c r="R6" t="n">
-        <v>6830323</v>
+        <v>6830343</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,12 +1198,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1213,7 +1213,7 @@
         <v>130252271</v>
       </c>
       <c r="B7" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130252262</v>
+        <v>130252259</v>
       </c>
       <c r="B8" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497260</v>
+        <v>497236</v>
       </c>
       <c r="R8" t="n">
-        <v>6830494</v>
+        <v>6830502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1406,7 +1406,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1425,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252259</v>
+        <v>130252262</v>
       </c>
       <c r="B9" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497236</v>
+        <v>497260</v>
       </c>
       <c r="R9" t="n">
-        <v>6830502</v>
+        <v>6830494</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,6 +1513,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>130252269</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252251</v>
+        <v>130252695</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,42 +1650,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497063</v>
+        <v>497166</v>
       </c>
       <c r="R11" t="n">
-        <v>6830279</v>
+        <v>6830368</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1727,7 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,12 +1734,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1757,7 +1749,7 @@
         <v>130252244</v>
       </c>
       <c r="B12" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252695</v>
+        <v>130252251</v>
       </c>
       <c r="B13" t="n">
-        <v>79183</v>
+        <v>58011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,34 +1864,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497166</v>
+        <v>497063</v>
       </c>
       <c r="R13" t="n">
-        <v>6830368</v>
+        <v>6830279</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,22 +1956,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252258</v>
+        <v>130252688</v>
       </c>
       <c r="B14" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497245</v>
+        <v>497300</v>
       </c>
       <c r="R14" t="n">
-        <v>6830449</v>
+        <v>6830438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,12 +2063,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2078,7 +2078,7 @@
         <v>130252245</v>
       </c>
       <c r="B15" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252688</v>
+        <v>130252258</v>
       </c>
       <c r="B16" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497300</v>
+        <v>497245</v>
       </c>
       <c r="R16" t="n">
-        <v>6830438</v>
+        <v>6830449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,12 +2277,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2292,7 +2292,7 @@
         <v>130252261</v>
       </c>
       <c r="B17" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>130252693</v>
       </c>
       <c r="B19" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>130252252</v>
       </c>
       <c r="B20" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252272</v>
+        <v>130252264</v>
       </c>
       <c r="B21" t="n">
-        <v>93013</v>
+        <v>79209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497084</v>
+        <v>497334</v>
       </c>
       <c r="R21" t="n">
-        <v>6830218</v>
+        <v>6830124</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2828,7 +2828,7 @@
         <v>130252696</v>
       </c>
       <c r="B22" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>130252691</v>
       </c>
       <c r="B23" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,32 +3039,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252264</v>
+        <v>130252272</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>93039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497334</v>
+        <v>497084</v>
       </c>
       <c r="R24" t="n">
-        <v>6830124</v>
+        <v>6830218</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3253,10 +3253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252267</v>
+        <v>130252685</v>
       </c>
       <c r="B26" t="n">
-        <v>79183</v>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,21 +3264,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497178</v>
+        <v>497071</v>
       </c>
       <c r="R26" t="n">
-        <v>6830332</v>
+        <v>6830207</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,44 +3348,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130252698</v>
+        <v>130252684</v>
       </c>
       <c r="B27" t="n">
-        <v>93013</v>
+        <v>78967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497112</v>
+        <v>497063</v>
       </c>
       <c r="R27" t="n">
-        <v>6830192</v>
+        <v>6830346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,7 +3449,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3468,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252685</v>
+        <v>130252267</v>
       </c>
       <c r="B28" t="n">
-        <v>78941</v>
+        <v>79209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,21 +3478,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497071</v>
+        <v>497178</v>
       </c>
       <c r="R28" t="n">
-        <v>6830207</v>
+        <v>6830332</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,7 +3537,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3548,7 +3547,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,44 +3562,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252684</v>
+        <v>130252698</v>
       </c>
       <c r="B29" t="n">
-        <v>78941</v>
+        <v>93039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3610,10 +3609,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497063</v>
+        <v>497112</v>
       </c>
       <c r="R29" t="n">
-        <v>6830346</v>
+        <v>6830192</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,7 +3644,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3655,7 +3654,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3664,6 +3663,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>130252268</v>
       </c>
       <c r="B30" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>130252689</v>
       </c>
       <c r="B31" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3896,32 +3896,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252265</v>
+        <v>130252687</v>
       </c>
       <c r="B32" t="n">
-        <v>79183</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497328</v>
+        <v>497050</v>
       </c>
       <c r="R32" t="n">
-        <v>6830125</v>
+        <v>6830313</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3991,44 +3991,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130252687</v>
+        <v>130252265</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497050</v>
+        <v>497328</v>
       </c>
       <c r="R33" t="n">
-        <v>6830313</v>
+        <v>6830125</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4098,12 +4098,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4113,7 +4113,7 @@
         <v>130252697</v>
       </c>
       <c r="B34" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>130252682</v>
       </c>
       <c r="B35" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>130252692</v>
       </c>
       <c r="B36" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>130252246</v>
       </c>
       <c r="B37" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252250</v>
+        <v>130252263</v>
       </c>
       <c r="B38" t="n">
-        <v>57985</v>
+        <v>79209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,35 +4550,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4586,10 +4577,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497113</v>
+        <v>497344</v>
       </c>
       <c r="R38" t="n">
-        <v>6830338</v>
+        <v>6830116</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4621,7 +4612,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4631,12 +4622,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Var i ett meståg med bla. trädkrypare</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4645,6 +4636,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4663,10 +4655,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130252683</v>
+        <v>130252260</v>
       </c>
       <c r="B39" t="n">
-        <v>78941</v>
+        <v>78966</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4674,21 +4666,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4698,10 +4690,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497089</v>
+        <v>497077</v>
       </c>
       <c r="R39" t="n">
-        <v>6830358</v>
+        <v>6830219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4733,7 +4725,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4743,7 +4735,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4758,22 +4750,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252260</v>
+        <v>130252250</v>
       </c>
       <c r="B40" t="n">
-        <v>78940</v>
+        <v>58011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4781,34 +4773,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497077</v>
+        <v>497113</v>
       </c>
       <c r="R40" t="n">
-        <v>6830219</v>
+        <v>6830338</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4840,7 +4844,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4850,7 +4854,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Var i ett meståg med bla. trädkrypare</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4877,10 +4886,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252263</v>
+        <v>130252683</v>
       </c>
       <c r="B41" t="n">
-        <v>79183</v>
+        <v>78967</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,37 +4897,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497344</v>
+        <v>497089</v>
       </c>
       <c r="R41" t="n">
-        <v>6830116</v>
+        <v>6830358</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4950,7 +4956,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4960,12 +4966,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4974,19 +4975,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4996,7 +4996,7 @@
         <v>130252266</v>
       </c>
       <c r="B42" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5100,53 +5100,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252248</v>
+        <v>130252686</v>
       </c>
       <c r="B43" t="n">
-        <v>57016</v>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497253</v>
+        <v>497085</v>
       </c>
       <c r="R43" t="n">
-        <v>6830469</v>
+        <v>6830215</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5178,7 +5170,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5188,12 +5180,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5208,44 +5195,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252254</v>
+        <v>130252690</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>78966</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5255,10 +5242,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497253</v>
+        <v>497163</v>
       </c>
       <c r="R44" t="n">
-        <v>6830488</v>
+        <v>6830392</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5290,7 +5277,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5300,7 +5287,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5315,57 +5302,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252690</v>
+        <v>130252248</v>
       </c>
       <c r="B45" t="n">
-        <v>78940</v>
+        <v>57042</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497163</v>
+        <v>497253</v>
       </c>
       <c r="R45" t="n">
-        <v>6830392</v>
+        <v>6830469</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5397,7 +5392,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5407,7 +5402,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5422,44 +5422,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252686</v>
+        <v>130252254</v>
       </c>
       <c r="B46" t="n">
-        <v>78941</v>
+        <v>8451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497085</v>
+        <v>497253</v>
       </c>
       <c r="R46" t="n">
-        <v>6830215</v>
+        <v>6830488</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5529,22 +5529,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130256297</v>
+        <v>130257279</v>
       </c>
       <c r="B47" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497115</v>
+        <v>497320</v>
       </c>
       <c r="R47" t="n">
-        <v>6830196</v>
+        <v>6830386</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5609,19 +5609,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5636,22 +5626,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130257279</v>
+        <v>130256297</v>
       </c>
       <c r="B48" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5659,21 +5649,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5683,10 +5673,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497320</v>
+        <v>497115</v>
       </c>
       <c r="R48" t="n">
-        <v>6830386</v>
+        <v>6830196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5716,9 +5706,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5733,12 +5733,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5748,7 +5748,7 @@
         <v>130256288</v>
       </c>
       <c r="B49" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>130257265</v>
       </c>
       <c r="B50" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130257295</v>
+        <v>130257276</v>
       </c>
       <c r="B51" t="n">
-        <v>78190</v>
+        <v>78966</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497072</v>
+        <v>497082</v>
       </c>
       <c r="R51" t="n">
-        <v>6830261</v>
+        <v>6830202</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130257276</v>
+        <v>130257271</v>
       </c>
       <c r="B52" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497082</v>
+        <v>497270</v>
       </c>
       <c r="R52" t="n">
-        <v>6830202</v>
+        <v>6830422</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130257271</v>
+        <v>130257295</v>
       </c>
       <c r="B53" t="n">
-        <v>78940</v>
+        <v>78216</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497270</v>
+        <v>497072</v>
       </c>
       <c r="R53" t="n">
-        <v>6830422</v>
+        <v>6830261</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,7 +6243,7 @@
         <v>130257280</v>
       </c>
       <c r="B54" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>130257291</v>
       </c>
       <c r="B55" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130257277</v>
+        <v>130256299</v>
       </c>
       <c r="B56" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497092</v>
+        <v>497390</v>
       </c>
       <c r="R56" t="n">
-        <v>6830180</v>
+        <v>6830226</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6502,9 +6502,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6519,22 +6529,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130256299</v>
+        <v>130257277</v>
       </c>
       <c r="B57" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6542,21 +6552,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6566,10 +6576,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497390</v>
+        <v>497092</v>
       </c>
       <c r="R57" t="n">
-        <v>6830226</v>
+        <v>6830180</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6599,19 +6609,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6626,12 +6626,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
         <v>130257284</v>
       </c>
       <c r="B58" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6735,10 +6735,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130256311</v>
+        <v>130257278</v>
       </c>
       <c r="B59" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497159</v>
+        <v>497327</v>
       </c>
       <c r="R59" t="n">
-        <v>6830345</v>
+        <v>6830133</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6803,19 +6803,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6830,22 +6820,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130257278</v>
+        <v>130256311</v>
       </c>
       <c r="B60" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6877,10 +6867,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497327</v>
+        <v>497159</v>
       </c>
       <c r="R60" t="n">
-        <v>6830133</v>
+        <v>6830345</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6910,9 +6900,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6927,22 +6927,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130257262</v>
+        <v>130256304</v>
       </c>
       <c r="B61" t="n">
-        <v>79802</v>
+        <v>79209</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6950,21 +6950,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497128</v>
+        <v>497247</v>
       </c>
       <c r="R61" t="n">
-        <v>6830348</v>
+        <v>6830499</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7007,9 +7007,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7024,22 +7034,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130256304</v>
+        <v>130257287</v>
       </c>
       <c r="B62" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7071,10 +7081,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497247</v>
+        <v>497234</v>
       </c>
       <c r="R62" t="n">
-        <v>6830499</v>
+        <v>6830313</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7104,19 +7114,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7131,22 +7131,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130256309</v>
+        <v>130257262</v>
       </c>
       <c r="B63" t="n">
-        <v>79183</v>
+        <v>79828</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7154,21 +7154,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497156</v>
+        <v>497128</v>
       </c>
       <c r="R63" t="n">
-        <v>6830327</v>
+        <v>6830348</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7211,19 +7211,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7238,22 +7228,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130257287</v>
+        <v>130256307</v>
       </c>
       <c r="B64" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7285,10 +7275,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497234</v>
+        <v>497221</v>
       </c>
       <c r="R64" t="n">
-        <v>6830313</v>
+        <v>6830314</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7318,9 +7308,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7335,22 +7335,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130256307</v>
+        <v>130256309</v>
       </c>
       <c r="B65" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497221</v>
+        <v>497156</v>
       </c>
       <c r="R65" t="n">
-        <v>6830314</v>
+        <v>6830327</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7457,7 +7457,7 @@
         <v>130257297</v>
       </c>
       <c r="B66" t="n">
-        <v>78586</v>
+        <v>78612</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>130257293</v>
       </c>
       <c r="B67" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>130257281</v>
       </c>
       <c r="B68" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>130256291</v>
       </c>
       <c r="B69" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>130256314</v>
       </c>
       <c r="B71" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>130256303</v>
       </c>
       <c r="B72" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>130257263</v>
       </c>
       <c r="B73" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>130256313</v>
       </c>
       <c r="B74" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8401,10 +8401,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130257275</v>
+        <v>130256306</v>
       </c>
       <c r="B75" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8412,21 +8412,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497096</v>
+        <v>497253</v>
       </c>
       <c r="R75" t="n">
-        <v>6830218</v>
+        <v>6830351</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8469,9 +8469,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8486,22 +8496,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130256306</v>
+        <v>130257275</v>
       </c>
       <c r="B76" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8509,21 +8519,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8533,10 +8543,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497253</v>
+        <v>497096</v>
       </c>
       <c r="R76" t="n">
-        <v>6830351</v>
+        <v>6830218</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8566,19 +8576,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8593,12 +8593,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8608,7 +8608,7 @@
         <v>130257282</v>
       </c>
       <c r="B77" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8702,10 +8702,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130257285</v>
+        <v>130257292</v>
       </c>
       <c r="B78" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8737,10 +8737,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497250</v>
+        <v>497138</v>
       </c>
       <c r="R78" t="n">
-        <v>6830356</v>
+        <v>6830320</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8799,10 +8799,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130257292</v>
+        <v>130257285</v>
       </c>
       <c r="B79" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497138</v>
+        <v>497250</v>
       </c>
       <c r="R79" t="n">
-        <v>6830320</v>
+        <v>6830356</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8896,10 +8896,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130256310</v>
+        <v>130256301</v>
       </c>
       <c r="B80" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497160</v>
+        <v>497384</v>
       </c>
       <c r="R80" t="n">
-        <v>6830342</v>
+        <v>6830217</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9003,10 +9003,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130256301</v>
+        <v>130256310</v>
       </c>
       <c r="B81" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9038,10 +9038,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497384</v>
+        <v>497160</v>
       </c>
       <c r="R81" t="n">
-        <v>6830217</v>
+        <v>6830342</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9113,7 +9113,7 @@
         <v>130257289</v>
       </c>
       <c r="B82" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9207,10 +9207,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130257261</v>
+        <v>130256302</v>
       </c>
       <c r="B83" t="n">
-        <v>79802</v>
+        <v>79209</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497107</v>
+        <v>497273</v>
       </c>
       <c r="R83" t="n">
-        <v>6830221</v>
+        <v>6830394</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9275,9 +9275,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9292,22 +9302,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130256302</v>
+        <v>130257261</v>
       </c>
       <c r="B84" t="n">
-        <v>79183</v>
+        <v>79828</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9315,21 +9325,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9339,10 +9349,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497273</v>
+        <v>497107</v>
       </c>
       <c r="R84" t="n">
-        <v>6830394</v>
+        <v>6830221</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9372,19 +9382,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9399,12 +9399,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9414,7 +9414,7 @@
         <v>130257266</v>
       </c>
       <c r="B85" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>130256315</v>
       </c>
       <c r="B86" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9635,54 +9635,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130256289</v>
+        <v>130257283</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497101</v>
+        <v>497244</v>
       </c>
       <c r="R87" t="n">
-        <v>6830183</v>
+        <v>6830388</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9712,40 +9703,29 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9755,7 +9735,7 @@
         <v>130257274</v>
       </c>
       <c r="B88" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9852,7 +9832,7 @@
         <v>130257268</v>
       </c>
       <c r="B89" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9946,45 +9926,54 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130257283</v>
+        <v>130256289</v>
       </c>
       <c r="B90" t="n">
-        <v>79183</v>
+        <v>8451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497244</v>
+        <v>497101</v>
       </c>
       <c r="R90" t="n">
-        <v>6830388</v>
+        <v>6830183</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10014,39 +10003,50 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130256300</v>
+        <v>130256308</v>
       </c>
       <c r="B91" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497391</v>
+        <v>497137</v>
       </c>
       <c r="R91" t="n">
-        <v>6830230</v>
+        <v>6830325</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10150,10 +10150,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130256293</v>
+        <v>130256300</v>
       </c>
       <c r="B92" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10161,21 +10161,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497117</v>
+        <v>497391</v>
       </c>
       <c r="R92" t="n">
-        <v>6830376</v>
+        <v>6830230</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10257,10 +10257,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130256305</v>
+        <v>130256293</v>
       </c>
       <c r="B93" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10268,21 +10268,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497258</v>
+        <v>497117</v>
       </c>
       <c r="R93" t="n">
-        <v>6830560</v>
+        <v>6830376</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10364,10 +10364,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130256308</v>
+        <v>130256305</v>
       </c>
       <c r="B94" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10399,10 +10399,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497137</v>
+        <v>497258</v>
       </c>
       <c r="R94" t="n">
-        <v>6830325</v>
+        <v>6830560</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10474,7 +10474,7 @@
         <v>130257272</v>
       </c>
       <c r="B95" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>130257288</v>
       </c>
       <c r="B96" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>130257269</v>
       </c>
       <c r="B97" t="n">
-        <v>57019</v>
+        <v>57045</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>130256296</v>
       </c>
       <c r="B98" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10877,10 +10877,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130257294</v>
+        <v>130257290</v>
       </c>
       <c r="B99" t="n">
-        <v>78190</v>
+        <v>79209</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10888,21 +10888,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497072</v>
+        <v>497200</v>
       </c>
       <c r="R99" t="n">
-        <v>6830282</v>
+        <v>6830326</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130257290</v>
+        <v>130257294</v>
       </c>
       <c r="B100" t="n">
-        <v>79183</v>
+        <v>78216</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10985,21 +10985,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497200</v>
+        <v>497072</v>
       </c>
       <c r="R100" t="n">
-        <v>6830326</v>
+        <v>6830282</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11074,7 +11074,7 @@
         <v>130257286</v>
       </c>
       <c r="B101" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11168,10 +11168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256292</v>
+        <v>130256286</v>
       </c>
       <c r="B102" t="n">
-        <v>78940</v>
+        <v>78967</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497168</v>
+        <v>497251</v>
       </c>
       <c r="R102" t="n">
-        <v>6830310</v>
+        <v>6830494</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11275,10 +11275,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256312</v>
+        <v>130256292</v>
       </c>
       <c r="B103" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497244</v>
+        <v>497168</v>
       </c>
       <c r="R103" t="n">
-        <v>6830538</v>
+        <v>6830310</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11382,10 +11382,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256286</v>
+        <v>130256312</v>
       </c>
       <c r="B104" t="n">
-        <v>78941</v>
+        <v>79209</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11393,21 +11393,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497251</v>
+        <v>497244</v>
       </c>
       <c r="R104" t="n">
-        <v>6830494</v>
+        <v>6830538</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252256</v>
+        <v>130252270</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497168</v>
+        <v>497118</v>
       </c>
       <c r="R4" t="n">
-        <v>6830390</v>
+        <v>6830323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252270</v>
+        <v>130252694</v>
       </c>
       <c r="B5" t="n">
         <v>79209</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497118</v>
+        <v>497321</v>
       </c>
       <c r="R5" t="n">
-        <v>6830323</v>
+        <v>6830343</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,44 +1091,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252694</v>
+        <v>130252256</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497321</v>
+        <v>497168</v>
       </c>
       <c r="R6" t="n">
-        <v>6830343</v>
+        <v>6830390</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,12 +1198,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130252273</v>
+        <v>130252255</v>
       </c>
       <c r="B2" t="n">
-        <v>93039</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497114</v>
+        <v>497263</v>
       </c>
       <c r="R2" t="n">
-        <v>6830195</v>
+        <v>6830449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252255</v>
+        <v>130252273</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>93040</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497263</v>
+        <v>497114</v>
       </c>
       <c r="R3" t="n">
-        <v>6830449</v>
+        <v>6830195</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252270</v>
+        <v>130252256</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497118</v>
+        <v>497168</v>
       </c>
       <c r="R4" t="n">
-        <v>6830323</v>
+        <v>6830390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252256</v>
+        <v>130252270</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497168</v>
+        <v>497118</v>
       </c>
       <c r="R6" t="n">
-        <v>6830390</v>
+        <v>6830323</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1213,7 @@
         <v>130252271</v>
       </c>
       <c r="B7" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130252259</v>
+        <v>130252262</v>
       </c>
       <c r="B8" t="n">
         <v>78966</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497236</v>
+        <v>497260</v>
       </c>
       <c r="R8" t="n">
-        <v>6830502</v>
+        <v>6830494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1406,6 +1406,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1424,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252262</v>
+        <v>130252259</v>
       </c>
       <c r="B9" t="n">
         <v>78966</v>
@@ -1459,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497260</v>
+        <v>497236</v>
       </c>
       <c r="R9" t="n">
-        <v>6830494</v>
+        <v>6830502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,7 +1514,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252695</v>
+        <v>130252251</v>
       </c>
       <c r="B11" t="n">
-        <v>79209</v>
+        <v>58011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,34 +1650,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497166</v>
+        <v>497063</v>
       </c>
       <c r="R11" t="n">
-        <v>6830368</v>
+        <v>6830279</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,12 +1742,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1853,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252251</v>
+        <v>130252695</v>
       </c>
       <c r="B13" t="n">
-        <v>58011</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,42 +1872,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497063</v>
+        <v>497166</v>
       </c>
       <c r="R13" t="n">
-        <v>6830279</v>
+        <v>6830368</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,19 +1956,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252688</v>
+        <v>130252258</v>
       </c>
       <c r="B14" t="n">
         <v>78966</v>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497300</v>
+        <v>497245</v>
       </c>
       <c r="R14" t="n">
-        <v>6830438</v>
+        <v>6830449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,22 +2063,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252245</v>
+        <v>130252688</v>
       </c>
       <c r="B15" t="n">
-        <v>79828</v>
+        <v>78966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497169</v>
+        <v>497300</v>
       </c>
       <c r="R15" t="n">
-        <v>6830390</v>
+        <v>6830438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,22 +2170,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252258</v>
+        <v>130252245</v>
       </c>
       <c r="B16" t="n">
-        <v>78966</v>
+        <v>79828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,21 +2193,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497245</v>
+        <v>497169</v>
       </c>
       <c r="R16" t="n">
-        <v>6830449</v>
+        <v>6830390</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,32 +2289,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252261</v>
+        <v>130252257</v>
       </c>
       <c r="B17" t="n">
-        <v>78966</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497167</v>
+        <v>497076</v>
       </c>
       <c r="R17" t="n">
-        <v>6830200</v>
+        <v>6830213</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252257</v>
+        <v>130252261</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>78966</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497076</v>
+        <v>497167</v>
       </c>
       <c r="R18" t="n">
-        <v>6830213</v>
+        <v>6830200</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252264</v>
+        <v>130252272</v>
       </c>
       <c r="B21" t="n">
-        <v>79209</v>
+        <v>93040</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497334</v>
+        <v>497084</v>
       </c>
       <c r="R21" t="n">
-        <v>6830124</v>
+        <v>6830218</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252696</v>
+        <v>130252691</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497147</v>
+        <v>497108</v>
       </c>
       <c r="R22" t="n">
-        <v>6830398</v>
+        <v>6830371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2932,10 +2932,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252691</v>
+        <v>130252696</v>
       </c>
       <c r="B23" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,21 +2943,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497108</v>
+        <v>497147</v>
       </c>
       <c r="R23" t="n">
-        <v>6830371</v>
+        <v>6830398</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,32 +3039,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252272</v>
+        <v>130252264</v>
       </c>
       <c r="B24" t="n">
-        <v>93039</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497084</v>
+        <v>497334</v>
       </c>
       <c r="R24" t="n">
-        <v>6830218</v>
+        <v>6830124</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,32 +3146,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130252253</v>
+        <v>130252267</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497334</v>
+        <v>497178</v>
       </c>
       <c r="R25" t="n">
-        <v>6830121</v>
+        <v>6830332</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3467,32 +3467,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252267</v>
+        <v>130252253</v>
       </c>
       <c r="B28" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497178</v>
+        <v>497334</v>
       </c>
       <c r="R28" t="n">
-        <v>6830332</v>
+        <v>6830121</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,7 +3577,7 @@
         <v>130252698</v>
       </c>
       <c r="B29" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,32 +3896,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252687</v>
+        <v>130252265</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497050</v>
+        <v>497328</v>
       </c>
       <c r="R32" t="n">
-        <v>6830313</v>
+        <v>6830125</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3991,44 +3991,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130252265</v>
+        <v>130252687</v>
       </c>
       <c r="B33" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497328</v>
+        <v>497050</v>
       </c>
       <c r="R33" t="n">
-        <v>6830125</v>
+        <v>6830313</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4098,44 +4098,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252697</v>
+        <v>130252682</v>
       </c>
       <c r="B34" t="n">
-        <v>93039</v>
+        <v>78967</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497086</v>
+        <v>497144</v>
       </c>
       <c r="R34" t="n">
-        <v>6830210</v>
+        <v>6830357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4199,7 +4199,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4218,32 +4217,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130252682</v>
+        <v>130252697</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>93040</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4252,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497144</v>
+        <v>497086</v>
       </c>
       <c r="R35" t="n">
-        <v>6830357</v>
+        <v>6830210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4288,7 +4287,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4298,7 +4297,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4307,6 +4306,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252263</v>
+        <v>130252250</v>
       </c>
       <c r="B38" t="n">
-        <v>79209</v>
+        <v>58011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,26 +4550,35 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4577,10 +4586,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497344</v>
+        <v>497113</v>
       </c>
       <c r="R38" t="n">
-        <v>6830116</v>
+        <v>6830338</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4612,7 +4621,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4622,12 +4631,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Var i ett meståg med bla. trädkrypare</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,7 +4645,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4655,10 +4663,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130252260</v>
+        <v>130252263</v>
       </c>
       <c r="B39" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,34 +4674,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497077</v>
+        <v>497344</v>
       </c>
       <c r="R39" t="n">
-        <v>6830219</v>
+        <v>6830116</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4725,7 +4736,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4735,7 +4746,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4744,6 +4760,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4762,10 +4779,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252250</v>
+        <v>130252260</v>
       </c>
       <c r="B40" t="n">
-        <v>58011</v>
+        <v>78966</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4773,46 +4790,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497113</v>
+        <v>497077</v>
       </c>
       <c r="R40" t="n">
-        <v>6830338</v>
+        <v>6830219</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4844,7 +4849,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4854,12 +4859,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Var i ett meståg med bla. trädkrypare</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5100,32 +5100,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252686</v>
+        <v>130252254</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497085</v>
+        <v>497253</v>
       </c>
       <c r="R43" t="n">
-        <v>6830215</v>
+        <v>6830488</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,22 +5195,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252690</v>
+        <v>130252686</v>
       </c>
       <c r="B44" t="n">
-        <v>78966</v>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5218,21 +5218,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5242,10 +5242,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497163</v>
+        <v>497085</v>
       </c>
       <c r="R44" t="n">
-        <v>6830392</v>
+        <v>6830215</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5434,32 +5434,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252254</v>
+        <v>130252690</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>78966</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497253</v>
+        <v>497163</v>
       </c>
       <c r="R46" t="n">
-        <v>6830488</v>
+        <v>6830392</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5529,22 +5529,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130257279</v>
+        <v>130256297</v>
       </c>
       <c r="B47" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497320</v>
+        <v>497115</v>
       </c>
       <c r="R47" t="n">
-        <v>6830386</v>
+        <v>6830196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5609,9 +5609,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5626,22 +5636,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130256297</v>
+        <v>130257279</v>
       </c>
       <c r="B48" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5649,21 +5659,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5673,10 +5683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497115</v>
+        <v>497320</v>
       </c>
       <c r="R48" t="n">
-        <v>6830196</v>
+        <v>6830386</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5706,19 +5716,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5733,12 +5733,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5855,7 +5855,7 @@
         <v>130257265</v>
       </c>
       <c r="B50" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130257276</v>
+        <v>130257271</v>
       </c>
       <c r="B51" t="n">
         <v>78966</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497082</v>
+        <v>497270</v>
       </c>
       <c r="R51" t="n">
-        <v>6830202</v>
+        <v>6830422</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6046,7 +6046,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130257271</v>
+        <v>130257276</v>
       </c>
       <c r="B52" t="n">
         <v>78966</v>
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497270</v>
+        <v>497082</v>
       </c>
       <c r="R52" t="n">
-        <v>6830422</v>
+        <v>6830202</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6735,7 +6735,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130257278</v>
+        <v>130256311</v>
       </c>
       <c r="B59" t="n">
         <v>79209</v>
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497327</v>
+        <v>497159</v>
       </c>
       <c r="R59" t="n">
-        <v>6830133</v>
+        <v>6830345</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6803,9 +6803,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6820,19 +6830,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130256311</v>
+        <v>130257278</v>
       </c>
       <c r="B60" t="n">
         <v>79209</v>
@@ -6867,10 +6877,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497159</v>
+        <v>497327</v>
       </c>
       <c r="R60" t="n">
-        <v>6830345</v>
+        <v>6830133</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6900,19 +6910,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6927,22 +6927,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130256304</v>
+        <v>130257262</v>
       </c>
       <c r="B61" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6950,21 +6950,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497247</v>
+        <v>497128</v>
       </c>
       <c r="R61" t="n">
-        <v>6830499</v>
+        <v>6830348</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7007,19 +7007,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7034,22 +7024,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130257287</v>
+        <v>130257297</v>
       </c>
       <c r="B62" t="n">
-        <v>79209</v>
+        <v>78612</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7057,21 +7047,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7081,10 +7071,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497234</v>
+        <v>497072</v>
       </c>
       <c r="R62" t="n">
-        <v>6830313</v>
+        <v>6830261</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7143,10 +7133,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130257262</v>
+        <v>130256304</v>
       </c>
       <c r="B63" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7154,21 +7144,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7178,10 +7168,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497128</v>
+        <v>497247</v>
       </c>
       <c r="R63" t="n">
-        <v>6830348</v>
+        <v>6830499</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7211,9 +7201,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7228,19 +7228,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130256307</v>
+        <v>130256309</v>
       </c>
       <c r="B64" t="n">
         <v>79209</v>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497221</v>
+        <v>497156</v>
       </c>
       <c r="R64" t="n">
-        <v>6830314</v>
+        <v>6830327</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7347,7 +7347,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130256309</v>
+        <v>130257287</v>
       </c>
       <c r="B65" t="n">
         <v>79209</v>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497156</v>
+        <v>497234</v>
       </c>
       <c r="R65" t="n">
-        <v>6830327</v>
+        <v>6830313</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7415,19 +7415,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7442,22 +7432,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130257297</v>
+        <v>130256307</v>
       </c>
       <c r="B66" t="n">
-        <v>78612</v>
+        <v>79209</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7465,21 +7455,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7489,10 +7479,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497072</v>
+        <v>497221</v>
       </c>
       <c r="R66" t="n">
-        <v>6830261</v>
+        <v>6830314</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7522,9 +7512,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7539,12 +7539,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7554,7 +7554,7 @@
         <v>130257293</v>
       </c>
       <c r="B67" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7648,10 +7648,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130257281</v>
+        <v>130256291</v>
       </c>
       <c r="B68" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7659,21 +7659,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497275</v>
+        <v>497251</v>
       </c>
       <c r="R68" t="n">
-        <v>6830388</v>
+        <v>6830491</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7716,9 +7716,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7733,22 +7743,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130256291</v>
+        <v>130257281</v>
       </c>
       <c r="B69" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7756,21 +7766,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7780,10 +7790,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497251</v>
+        <v>497275</v>
       </c>
       <c r="R69" t="n">
-        <v>6830491</v>
+        <v>6830388</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7813,19 +7823,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7840,12 +7840,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7962,7 +7962,7 @@
         <v>130256314</v>
       </c>
       <c r="B71" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8282,56 +8282,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130256313</v>
+        <v>130256306</v>
       </c>
       <c r="B74" t="n">
-        <v>93039</v>
+        <v>79209</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497260</v>
+        <v>497253</v>
       </c>
       <c r="R74" t="n">
-        <v>6830540</v>
+        <v>6830351</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8363,7 +8352,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8373,7 +8362,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8382,7 +8371,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8401,10 +8389,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130256306</v>
+        <v>130257275</v>
       </c>
       <c r="B75" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8412,21 +8400,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8436,10 +8424,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497253</v>
+        <v>497096</v>
       </c>
       <c r="R75" t="n">
-        <v>6830351</v>
+        <v>6830218</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8469,19 +8457,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8496,57 +8474,68 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130257275</v>
+        <v>130256313</v>
       </c>
       <c r="B76" t="n">
-        <v>78966</v>
+        <v>93040</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497096</v>
+        <v>497260</v>
       </c>
       <c r="R76" t="n">
-        <v>6830218</v>
+        <v>6830540</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8576,29 +8565,40 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8702,7 +8702,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130257292</v>
+        <v>130257285</v>
       </c>
       <c r="B78" t="n">
         <v>79209</v>
@@ -8737,10 +8737,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497138</v>
+        <v>497250</v>
       </c>
       <c r="R78" t="n">
-        <v>6830320</v>
+        <v>6830356</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8799,7 +8799,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130257285</v>
+        <v>130257292</v>
       </c>
       <c r="B79" t="n">
         <v>79209</v>
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497250</v>
+        <v>497138</v>
       </c>
       <c r="R79" t="n">
-        <v>6830356</v>
+        <v>6830320</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8896,7 +8896,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130256301</v>
+        <v>130256310</v>
       </c>
       <c r="B80" t="n">
         <v>79209</v>
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497384</v>
+        <v>497160</v>
       </c>
       <c r="R80" t="n">
-        <v>6830217</v>
+        <v>6830342</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9003,7 +9003,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130256310</v>
+        <v>130256301</v>
       </c>
       <c r="B81" t="n">
         <v>79209</v>
@@ -9038,10 +9038,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497160</v>
+        <v>497384</v>
       </c>
       <c r="R81" t="n">
-        <v>6830342</v>
+        <v>6830217</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9519,7 +9519,7 @@
         <v>130256315</v>
       </c>
       <c r="B86" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9635,10 +9635,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130257283</v>
+        <v>130257274</v>
       </c>
       <c r="B87" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9646,21 +9646,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497244</v>
+        <v>497107</v>
       </c>
       <c r="R87" t="n">
-        <v>6830388</v>
+        <v>6830221</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9732,10 +9732,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130257274</v>
+        <v>130257268</v>
       </c>
       <c r="B88" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9743,21 +9743,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9767,10 +9767,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497107</v>
+        <v>497074</v>
       </c>
       <c r="R88" t="n">
-        <v>6830221</v>
+        <v>6830292</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9829,7 +9829,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130257268</v>
+        <v>130257283</v>
       </c>
       <c r="B89" t="n">
         <v>79209</v>
@@ -9864,10 +9864,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497074</v>
+        <v>497244</v>
       </c>
       <c r="R89" t="n">
-        <v>6830292</v>
+        <v>6830388</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10043,7 +10043,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130256308</v>
+        <v>130256300</v>
       </c>
       <c r="B91" t="n">
         <v>79209</v>
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497137</v>
+        <v>497391</v>
       </c>
       <c r="R91" t="n">
-        <v>6830325</v>
+        <v>6830230</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10150,7 +10150,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130256300</v>
+        <v>130256305</v>
       </c>
       <c r="B92" t="n">
         <v>79209</v>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497391</v>
+        <v>497258</v>
       </c>
       <c r="R92" t="n">
-        <v>6830230</v>
+        <v>6830560</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10257,10 +10257,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130256293</v>
+        <v>130256308</v>
       </c>
       <c r="B93" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10268,21 +10268,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497117</v>
+        <v>497137</v>
       </c>
       <c r="R93" t="n">
-        <v>6830376</v>
+        <v>6830325</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10364,10 +10364,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130256305</v>
+        <v>130256293</v>
       </c>
       <c r="B94" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10375,21 +10375,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10399,10 +10399,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497258</v>
+        <v>497117</v>
       </c>
       <c r="R94" t="n">
-        <v>6830560</v>
+        <v>6830376</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10471,10 +10471,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130257272</v>
+        <v>130257288</v>
       </c>
       <c r="B95" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10482,21 +10482,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497128</v>
+        <v>497224</v>
       </c>
       <c r="R95" t="n">
-        <v>6830345</v>
+        <v>6830319</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10568,10 +10568,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130257288</v>
+        <v>130257272</v>
       </c>
       <c r="B96" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10579,21 +10579,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497224</v>
+        <v>497128</v>
       </c>
       <c r="R96" t="n">
-        <v>6830319</v>
+        <v>6830345</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10877,10 +10877,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130257290</v>
+        <v>130257294</v>
       </c>
       <c r="B99" t="n">
-        <v>79209</v>
+        <v>78216</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10888,21 +10888,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497200</v>
+        <v>497072</v>
       </c>
       <c r="R99" t="n">
-        <v>6830326</v>
+        <v>6830282</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130257294</v>
+        <v>130257290</v>
       </c>
       <c r="B100" t="n">
-        <v>78216</v>
+        <v>79209</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10985,21 +10985,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497072</v>
+        <v>497200</v>
       </c>
       <c r="R100" t="n">
-        <v>6830282</v>
+        <v>6830326</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130252255</v>
+        <v>130252273</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>93041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497263</v>
+        <v>497114</v>
       </c>
       <c r="R2" t="n">
-        <v>6830449</v>
+        <v>6830195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252273</v>
+        <v>130252255</v>
       </c>
       <c r="B3" t="n">
-        <v>93040</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497114</v>
+        <v>497263</v>
       </c>
       <c r="R3" t="n">
-        <v>6830195</v>
+        <v>6830449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252256</v>
+        <v>130252694</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497168</v>
+        <v>497321</v>
       </c>
       <c r="R4" t="n">
-        <v>6830390</v>
+        <v>6830343</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +984,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252694</v>
+        <v>130252270</v>
       </c>
       <c r="B5" t="n">
         <v>79209</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497321</v>
+        <v>497118</v>
       </c>
       <c r="R5" t="n">
-        <v>6830343</v>
+        <v>6830323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,44 +1091,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252270</v>
+        <v>130252256</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497118</v>
+        <v>497168</v>
       </c>
       <c r="R6" t="n">
-        <v>6830323</v>
+        <v>6830390</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252271</v>
+        <v>130252262</v>
       </c>
       <c r="B7" t="n">
-        <v>93040</v>
+        <v>78966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497241</v>
+        <v>497260</v>
       </c>
       <c r="R7" t="n">
-        <v>6830507</v>
+        <v>6830494</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,6 +1299,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1317,7 +1318,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130252262</v>
+        <v>130252259</v>
       </c>
       <c r="B8" t="n">
         <v>78966</v>
@@ -1352,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497260</v>
+        <v>497236</v>
       </c>
       <c r="R8" t="n">
-        <v>6830494</v>
+        <v>6830502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1388,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1398,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1406,7 +1407,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1425,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252259</v>
+        <v>130252271</v>
       </c>
       <c r="B9" t="n">
-        <v>78966</v>
+        <v>93041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497236</v>
+        <v>497241</v>
       </c>
       <c r="R9" t="n">
-        <v>6830502</v>
+        <v>6830507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252251</v>
+        <v>130252244</v>
       </c>
       <c r="B11" t="n">
-        <v>58011</v>
+        <v>79828</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,42 +1650,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497063</v>
+        <v>497260</v>
       </c>
       <c r="R11" t="n">
-        <v>6830279</v>
+        <v>6830494</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1727,7 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252244</v>
+        <v>130252695</v>
       </c>
       <c r="B12" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1789,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497260</v>
+        <v>497166</v>
       </c>
       <c r="R12" t="n">
-        <v>6830494</v>
+        <v>6830368</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1816,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1834,7 +1826,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,22 +1841,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252695</v>
+        <v>130252251</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>58011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,34 +1864,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497166</v>
+        <v>497063</v>
       </c>
       <c r="R13" t="n">
-        <v>6830368</v>
+        <v>6830279</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,12 +1956,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252688</v>
+        <v>130252245</v>
       </c>
       <c r="B15" t="n">
-        <v>78966</v>
+        <v>79828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497300</v>
+        <v>497169</v>
       </c>
       <c r="R15" t="n">
-        <v>6830438</v>
+        <v>6830390</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,22 +2170,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252245</v>
+        <v>130252688</v>
       </c>
       <c r="B16" t="n">
-        <v>79828</v>
+        <v>78966</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,21 +2193,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497169</v>
+        <v>497300</v>
       </c>
       <c r="R16" t="n">
-        <v>6830390</v>
+        <v>6830438</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,44 +2277,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252257</v>
+        <v>130252261</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>78966</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497076</v>
+        <v>497167</v>
       </c>
       <c r="R17" t="n">
-        <v>6830213</v>
+        <v>6830200</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252261</v>
+        <v>130252257</v>
       </c>
       <c r="B18" t="n">
-        <v>78966</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497167</v>
+        <v>497076</v>
       </c>
       <c r="R18" t="n">
-        <v>6830200</v>
+        <v>6830213</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252272</v>
+        <v>130252696</v>
       </c>
       <c r="B21" t="n">
-        <v>93040</v>
+        <v>79209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497084</v>
+        <v>497147</v>
       </c>
       <c r="R21" t="n">
-        <v>6830218</v>
+        <v>6830398</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252696</v>
+        <v>130252264</v>
       </c>
       <c r="B23" t="n">
         <v>79209</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497147</v>
+        <v>497334</v>
       </c>
       <c r="R23" t="n">
-        <v>6830398</v>
+        <v>6830124</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,44 +3027,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252264</v>
+        <v>130252272</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497334</v>
+        <v>497084</v>
       </c>
       <c r="R24" t="n">
-        <v>6830124</v>
+        <v>6830218</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,32 +3146,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130252267</v>
+        <v>130252253</v>
       </c>
       <c r="B25" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497178</v>
+        <v>497334</v>
       </c>
       <c r="R25" t="n">
-        <v>6830332</v>
+        <v>6830121</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3467,32 +3467,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252253</v>
+        <v>130252267</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497334</v>
+        <v>497178</v>
       </c>
       <c r="R28" t="n">
-        <v>6830121</v>
+        <v>6830332</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,7 +3577,7 @@
         <v>130252698</v>
       </c>
       <c r="B29" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252268</v>
+        <v>130252689</v>
       </c>
       <c r="B30" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497175</v>
+        <v>497261</v>
       </c>
       <c r="R30" t="n">
-        <v>6830390</v>
+        <v>6830425</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,22 +3777,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252689</v>
+        <v>130252268</v>
       </c>
       <c r="B31" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,21 +3800,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497261</v>
+        <v>497175</v>
       </c>
       <c r="R31" t="n">
-        <v>6830425</v>
+        <v>6830390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3884,44 +3884,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252265</v>
+        <v>130252687</v>
       </c>
       <c r="B32" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497328</v>
+        <v>497050</v>
       </c>
       <c r="R32" t="n">
-        <v>6830125</v>
+        <v>6830313</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3991,44 +3991,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130252687</v>
+        <v>130252265</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497050</v>
+        <v>497328</v>
       </c>
       <c r="R33" t="n">
-        <v>6830313</v>
+        <v>6830125</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4098,44 +4098,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252682</v>
+        <v>130252697</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>93041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497144</v>
+        <v>497086</v>
       </c>
       <c r="R34" t="n">
-        <v>6830357</v>
+        <v>6830210</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4199,6 +4199,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4217,32 +4218,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130252697</v>
+        <v>130252682</v>
       </c>
       <c r="B35" t="n">
-        <v>93040</v>
+        <v>78967</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4252,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497086</v>
+        <v>497144</v>
       </c>
       <c r="R35" t="n">
-        <v>6830210</v>
+        <v>6830357</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4287,7 +4288,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4297,7 +4298,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4306,7 +4307,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130252263</v>
+        <v>130252683</v>
       </c>
       <c r="B39" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4674,37 +4674,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497344</v>
+        <v>497089</v>
       </c>
       <c r="R39" t="n">
-        <v>6830116</v>
+        <v>6830358</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4736,7 +4733,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4746,12 +4743,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4760,19 +4752,18 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4886,10 +4877,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252683</v>
+        <v>130252263</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,34 +4888,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497089</v>
+        <v>497344</v>
       </c>
       <c r="R41" t="n">
-        <v>6830358</v>
+        <v>6830116</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4956,7 +4950,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4966,7 +4960,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4975,18 +4974,19 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252254</v>
+        <v>130252690</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>78966</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497253</v>
+        <v>497163</v>
       </c>
       <c r="R43" t="n">
-        <v>6830488</v>
+        <v>6830392</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,57 +5195,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252686</v>
+        <v>130252248</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>57042</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497085</v>
+        <v>497253</v>
       </c>
       <c r="R44" t="n">
-        <v>6830215</v>
+        <v>6830469</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5277,7 +5285,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5287,7 +5295,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5302,65 +5315,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252248</v>
+        <v>130252686</v>
       </c>
       <c r="B45" t="n">
-        <v>57042</v>
+        <v>78967</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497253</v>
+        <v>497085</v>
       </c>
       <c r="R45" t="n">
-        <v>6830469</v>
+        <v>6830215</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5392,7 +5397,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5402,12 +5407,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5422,44 +5422,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252690</v>
+        <v>130252254</v>
       </c>
       <c r="B46" t="n">
-        <v>78966</v>
+        <v>8451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497163</v>
+        <v>497253</v>
       </c>
       <c r="R46" t="n">
-        <v>6830392</v>
+        <v>6830488</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5529,12 +5529,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5855,7 +5855,7 @@
         <v>130257265</v>
       </c>
       <c r="B50" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130257271</v>
+        <v>130257295</v>
       </c>
       <c r="B51" t="n">
-        <v>78966</v>
+        <v>78216</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497270</v>
+        <v>497072</v>
       </c>
       <c r="R51" t="n">
-        <v>6830422</v>
+        <v>6830261</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130257295</v>
+        <v>130257271</v>
       </c>
       <c r="B53" t="n">
-        <v>78216</v>
+        <v>78966</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497072</v>
+        <v>497270</v>
       </c>
       <c r="R53" t="n">
-        <v>6830261</v>
+        <v>6830422</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6434,10 +6434,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130256299</v>
+        <v>130257277</v>
       </c>
       <c r="B56" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497390</v>
+        <v>497092</v>
       </c>
       <c r="R56" t="n">
-        <v>6830226</v>
+        <v>6830180</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6502,19 +6502,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6529,22 +6519,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130257277</v>
+        <v>130256299</v>
       </c>
       <c r="B57" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6552,21 +6542,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6576,10 +6566,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497092</v>
+        <v>497390</v>
       </c>
       <c r="R57" t="n">
-        <v>6830180</v>
+        <v>6830226</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6609,9 +6599,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6626,12 +6626,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6939,10 +6939,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130257262</v>
+        <v>130256309</v>
       </c>
       <c r="B61" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6950,21 +6950,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497128</v>
+        <v>497156</v>
       </c>
       <c r="R61" t="n">
-        <v>6830348</v>
+        <v>6830327</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7007,9 +7007,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7024,22 +7034,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130257297</v>
+        <v>130257287</v>
       </c>
       <c r="B62" t="n">
-        <v>78612</v>
+        <v>79209</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7047,21 +7057,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7071,10 +7081,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497072</v>
+        <v>497234</v>
       </c>
       <c r="R62" t="n">
-        <v>6830261</v>
+        <v>6830313</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7143,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130256304</v>
+        <v>130256307</v>
       </c>
       <c r="B63" t="n">
         <v>79209</v>
@@ -7168,10 +7178,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497247</v>
+        <v>497221</v>
       </c>
       <c r="R63" t="n">
-        <v>6830499</v>
+        <v>6830314</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7203,7 +7213,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7213,7 +7223,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7240,10 +7250,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130256309</v>
+        <v>130257262</v>
       </c>
       <c r="B64" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7251,21 +7261,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7275,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497156</v>
+        <v>497128</v>
       </c>
       <c r="R64" t="n">
-        <v>6830327</v>
+        <v>6830348</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7308,19 +7318,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7335,19 +7335,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130257287</v>
+        <v>130256304</v>
       </c>
       <c r="B65" t="n">
         <v>79209</v>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497234</v>
+        <v>497247</v>
       </c>
       <c r="R65" t="n">
-        <v>6830313</v>
+        <v>6830499</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7415,9 +7415,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7432,22 +7442,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130256307</v>
+        <v>130257297</v>
       </c>
       <c r="B66" t="n">
-        <v>79209</v>
+        <v>78612</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7455,21 +7465,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7479,10 +7489,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497221</v>
+        <v>497072</v>
       </c>
       <c r="R66" t="n">
-        <v>6830314</v>
+        <v>6830261</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7512,19 +7522,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7539,44 +7539,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130257293</v>
+        <v>130257281</v>
       </c>
       <c r="B67" t="n">
-        <v>93040</v>
+        <v>79209</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497087</v>
+        <v>497275</v>
       </c>
       <c r="R67" t="n">
-        <v>6830238</v>
+        <v>6830388</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7755,32 +7755,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130257281</v>
+        <v>130257293</v>
       </c>
       <c r="B69" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497275</v>
+        <v>497087</v>
       </c>
       <c r="R69" t="n">
-        <v>6830388</v>
+        <v>6830238</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7959,56 +7959,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256314</v>
+        <v>130256303</v>
       </c>
       <c r="B71" t="n">
-        <v>93040</v>
+        <v>79209</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497242</v>
+        <v>497291</v>
       </c>
       <c r="R71" t="n">
-        <v>6830510</v>
+        <v>6830488</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8040,7 +8029,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8050,7 +8039,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8059,7 +8048,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8078,45 +8066,56 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130256303</v>
+        <v>130256314</v>
       </c>
       <c r="B72" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497291</v>
+        <v>497242</v>
       </c>
       <c r="R72" t="n">
-        <v>6830488</v>
+        <v>6830510</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8148,7 +8147,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8158,7 +8157,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8167,6 +8166,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8282,10 +8282,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130256306</v>
+        <v>130257275</v>
       </c>
       <c r="B74" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8293,21 +8293,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497253</v>
+        <v>497096</v>
       </c>
       <c r="R74" t="n">
-        <v>6830351</v>
+        <v>6830218</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8350,19 +8350,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8377,22 +8367,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130257275</v>
+        <v>130256306</v>
       </c>
       <c r="B75" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8400,21 +8390,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8424,10 +8414,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497096</v>
+        <v>497253</v>
       </c>
       <c r="R75" t="n">
-        <v>6830218</v>
+        <v>6830351</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8457,9 +8447,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8474,12 +8474,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8489,7 +8489,7 @@
         <v>130256313</v>
       </c>
       <c r="B76" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,10 +9207,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130256302</v>
+        <v>130257261</v>
       </c>
       <c r="B83" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497273</v>
+        <v>497107</v>
       </c>
       <c r="R83" t="n">
-        <v>6830394</v>
+        <v>6830221</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9275,19 +9275,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9302,22 +9292,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130257261</v>
+        <v>130256302</v>
       </c>
       <c r="B84" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9325,21 +9315,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9349,10 +9339,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497107</v>
+        <v>497273</v>
       </c>
       <c r="R84" t="n">
-        <v>6830221</v>
+        <v>6830394</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9382,9 +9372,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9399,12 +9399,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9519,7 +9519,7 @@
         <v>130256315</v>
       </c>
       <c r="B86" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10150,10 +10150,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130256305</v>
+        <v>130256293</v>
       </c>
       <c r="B92" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10161,21 +10161,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497258</v>
+        <v>497117</v>
       </c>
       <c r="R92" t="n">
-        <v>6830560</v>
+        <v>6830376</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10257,7 +10257,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130256308</v>
+        <v>130256305</v>
       </c>
       <c r="B93" t="n">
         <v>79209</v>
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497137</v>
+        <v>497258</v>
       </c>
       <c r="R93" t="n">
-        <v>6830325</v>
+        <v>6830560</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10364,10 +10364,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130256293</v>
+        <v>130256308</v>
       </c>
       <c r="B94" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10375,21 +10375,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10399,10 +10399,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497117</v>
+        <v>497137</v>
       </c>
       <c r="R94" t="n">
-        <v>6830376</v>
+        <v>6830325</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11168,10 +11168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256286</v>
+        <v>130256292</v>
       </c>
       <c r="B102" t="n">
-        <v>78967</v>
+        <v>78966</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497251</v>
+        <v>497168</v>
       </c>
       <c r="R102" t="n">
-        <v>6830494</v>
+        <v>6830310</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11275,10 +11275,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256292</v>
+        <v>130256312</v>
       </c>
       <c r="B103" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497168</v>
+        <v>497244</v>
       </c>
       <c r="R103" t="n">
-        <v>6830310</v>
+        <v>6830538</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11382,10 +11382,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256312</v>
+        <v>130256286</v>
       </c>
       <c r="B104" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11393,21 +11393,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497244</v>
+        <v>497251</v>
       </c>
       <c r="R104" t="n">
-        <v>6830538</v>
+        <v>6830494</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130252273</v>
       </c>
       <c r="B2" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130252694</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130252270</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252262</v>
+        <v>130252271</v>
       </c>
       <c r="B7" t="n">
-        <v>78966</v>
+        <v>93043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497260</v>
+        <v>497241</v>
       </c>
       <c r="R7" t="n">
-        <v>6830494</v>
+        <v>6830507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,7 +1299,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1318,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130252259</v>
+        <v>130252262</v>
       </c>
       <c r="B8" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497236</v>
+        <v>497260</v>
       </c>
       <c r="R8" t="n">
-        <v>6830502</v>
+        <v>6830494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1398,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,6 +1406,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1425,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252271</v>
+        <v>130252259</v>
       </c>
       <c r="B9" t="n">
-        <v>93041</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497241</v>
+        <v>497236</v>
       </c>
       <c r="R9" t="n">
-        <v>6830507</v>
+        <v>6830502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,7 +1535,7 @@
         <v>130252269</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252244</v>
+        <v>130252695</v>
       </c>
       <c r="B11" t="n">
-        <v>79828</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497260</v>
+        <v>497166</v>
       </c>
       <c r="R11" t="n">
-        <v>6830494</v>
+        <v>6830368</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,22 +1734,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252695</v>
+        <v>130252244</v>
       </c>
       <c r="B12" t="n">
-        <v>79209</v>
+        <v>79830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497166</v>
+        <v>497260</v>
       </c>
       <c r="R12" t="n">
-        <v>6830368</v>
+        <v>6830494</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,12 +1841,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
         <v>130252251</v>
       </c>
       <c r="B13" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>130252258</v>
       </c>
       <c r="B14" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>130252245</v>
       </c>
       <c r="B15" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>130252688</v>
       </c>
       <c r="B16" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,32 +2289,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252261</v>
+        <v>130252257</v>
       </c>
       <c r="B17" t="n">
-        <v>78966</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497167</v>
+        <v>497076</v>
       </c>
       <c r="R17" t="n">
-        <v>6830200</v>
+        <v>6830213</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252257</v>
+        <v>130252261</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497076</v>
+        <v>497167</v>
       </c>
       <c r="R18" t="n">
-        <v>6830213</v>
+        <v>6830200</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,7 +2506,7 @@
         <v>130252693</v>
       </c>
       <c r="B19" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>130252252</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252696</v>
+        <v>130252272</v>
       </c>
       <c r="B21" t="n">
-        <v>79209</v>
+        <v>93043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497147</v>
+        <v>497084</v>
       </c>
       <c r="R21" t="n">
-        <v>6830398</v>
+        <v>6830218</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
         <v>130252691</v>
       </c>
       <c r="B22" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>130252264</v>
       </c>
       <c r="B23" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,32 +3039,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252272</v>
+        <v>130252696</v>
       </c>
       <c r="B24" t="n">
-        <v>93041</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497084</v>
+        <v>497147</v>
       </c>
       <c r="R24" t="n">
-        <v>6830218</v>
+        <v>6830398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,22 +3134,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130252253</v>
+        <v>130252698</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>93043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,21 +3157,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497334</v>
+        <v>497112</v>
       </c>
       <c r="R25" t="n">
-        <v>6830121</v>
+        <v>6830192</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,28 +3235,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252685</v>
+        <v>130252267</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,21 +3265,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497071</v>
+        <v>497178</v>
       </c>
       <c r="R26" t="n">
-        <v>6830207</v>
+        <v>6830332</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3324,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3334,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,22 +3349,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130252684</v>
+        <v>130252685</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3395,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497063</v>
+        <v>497071</v>
       </c>
       <c r="R27" t="n">
-        <v>6830346</v>
+        <v>6830207</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3431,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3440,7 +3441,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,10 +3468,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252267</v>
+        <v>130252684</v>
       </c>
       <c r="B28" t="n">
-        <v>79209</v>
+        <v>78969</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3478,21 +3479,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3502,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497178</v>
+        <v>497063</v>
       </c>
       <c r="R28" t="n">
-        <v>6830332</v>
+        <v>6830346</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,7 +3538,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3547,7 +3548,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,22 +3563,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252698</v>
+        <v>130252253</v>
       </c>
       <c r="B29" t="n">
-        <v>93041</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,21 +3586,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3609,10 +3610,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497112</v>
+        <v>497334</v>
       </c>
       <c r="R29" t="n">
-        <v>6830192</v>
+        <v>6830121</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,7 +3645,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3654,7 +3655,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3663,29 +3664,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252689</v>
+        <v>130252268</v>
       </c>
       <c r="B30" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497261</v>
+        <v>497175</v>
       </c>
       <c r="R30" t="n">
-        <v>6830425</v>
+        <v>6830390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,22 +3777,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252268</v>
+        <v>130252689</v>
       </c>
       <c r="B31" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,21 +3800,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497175</v>
+        <v>497261</v>
       </c>
       <c r="R31" t="n">
-        <v>6830390</v>
+        <v>6830425</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3884,44 +3884,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252687</v>
+        <v>130252265</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497050</v>
+        <v>497328</v>
       </c>
       <c r="R32" t="n">
-        <v>6830313</v>
+        <v>6830125</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3991,44 +3991,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130252265</v>
+        <v>130252687</v>
       </c>
       <c r="B33" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497328</v>
+        <v>497050</v>
       </c>
       <c r="R33" t="n">
-        <v>6830125</v>
+        <v>6830313</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4098,12 +4098,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4113,7 +4113,7 @@
         <v>130252697</v>
       </c>
       <c r="B34" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>130252682</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>130252692</v>
       </c>
       <c r="B36" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>130252246</v>
       </c>
       <c r="B37" t="n">
-        <v>79799</v>
+        <v>79801</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252250</v>
+        <v>130252260</v>
       </c>
       <c r="B38" t="n">
-        <v>58011</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,46 +4550,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497113</v>
+        <v>497077</v>
       </c>
       <c r="R38" t="n">
-        <v>6830338</v>
+        <v>6830219</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4621,7 +4609,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4631,12 +4619,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Var i ett meståg med bla. trädkrypare</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4663,10 +4646,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130252683</v>
+        <v>130252263</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>79211</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4674,34 +4657,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497089</v>
+        <v>497344</v>
       </c>
       <c r="R39" t="n">
-        <v>6830358</v>
+        <v>6830116</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4733,7 +4719,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4743,7 +4729,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4752,28 +4743,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252260</v>
+        <v>130252250</v>
       </c>
       <c r="B40" t="n">
-        <v>78966</v>
+        <v>58013</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4781,34 +4773,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497077</v>
+        <v>497113</v>
       </c>
       <c r="R40" t="n">
-        <v>6830219</v>
+        <v>6830338</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4840,7 +4844,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4850,7 +4854,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Var i ett meståg med bla. trädkrypare</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4877,10 +4886,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252263</v>
+        <v>130252683</v>
       </c>
       <c r="B41" t="n">
-        <v>79209</v>
+        <v>78969</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,37 +4897,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497344</v>
+        <v>497089</v>
       </c>
       <c r="R41" t="n">
-        <v>6830116</v>
+        <v>6830358</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4950,7 +4956,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4960,12 +4966,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4974,19 +4975,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4996,7 +4996,7 @@
         <v>130252266</v>
       </c>
       <c r="B42" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252690</v>
+        <v>130252254</v>
       </c>
       <c r="B43" t="n">
-        <v>78966</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497163</v>
+        <v>497253</v>
       </c>
       <c r="R43" t="n">
-        <v>6830392</v>
+        <v>6830488</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,65 +5195,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252248</v>
+        <v>130252686</v>
       </c>
       <c r="B44" t="n">
-        <v>57042</v>
+        <v>78969</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497253</v>
+        <v>497085</v>
       </c>
       <c r="R44" t="n">
-        <v>6830469</v>
+        <v>6830215</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5285,7 +5277,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5295,12 +5287,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5315,57 +5302,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252686</v>
+        <v>130252248</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>57044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497085</v>
+        <v>497253</v>
       </c>
       <c r="R45" t="n">
-        <v>6830215</v>
+        <v>6830469</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5397,7 +5392,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5407,7 +5402,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5422,44 +5422,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252254</v>
+        <v>130252690</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497253</v>
+        <v>497163</v>
       </c>
       <c r="R46" t="n">
-        <v>6830488</v>
+        <v>6830392</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5529,22 +5529,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130256297</v>
+        <v>130257279</v>
       </c>
       <c r="B47" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497115</v>
+        <v>497320</v>
       </c>
       <c r="R47" t="n">
-        <v>6830196</v>
+        <v>6830386</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5609,19 +5609,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5636,22 +5626,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130257279</v>
+        <v>130256297</v>
       </c>
       <c r="B48" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5659,21 +5649,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5683,10 +5673,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497320</v>
+        <v>497115</v>
       </c>
       <c r="R48" t="n">
-        <v>6830386</v>
+        <v>6830196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5716,9 +5706,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5733,12 +5733,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5748,7 +5748,7 @@
         <v>130256288</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130257265</v>
+        <v>130257295</v>
       </c>
       <c r="B50" t="n">
-        <v>91780</v>
+        <v>78218</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5863,21 +5863,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6487</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497131</v>
+        <v>497072</v>
       </c>
       <c r="R50" t="n">
-        <v>6830311</v>
+        <v>6830261</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130257295</v>
+        <v>130257276</v>
       </c>
       <c r="B51" t="n">
-        <v>78216</v>
+        <v>78968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497072</v>
+        <v>497082</v>
       </c>
       <c r="R51" t="n">
-        <v>6830261</v>
+        <v>6830202</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130257276</v>
+        <v>130257271</v>
       </c>
       <c r="B52" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497082</v>
+        <v>497270</v>
       </c>
       <c r="R52" t="n">
-        <v>6830202</v>
+        <v>6830422</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130257271</v>
+        <v>130257265</v>
       </c>
       <c r="B53" t="n">
-        <v>78966</v>
+        <v>91782</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497270</v>
+        <v>497131</v>
       </c>
       <c r="R53" t="n">
-        <v>6830422</v>
+        <v>6830311</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130257280</v>
+        <v>130257291</v>
       </c>
       <c r="B54" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497302</v>
+        <v>497164</v>
       </c>
       <c r="R54" t="n">
-        <v>6830384</v>
+        <v>6830343</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130257291</v>
+        <v>130257280</v>
       </c>
       <c r="B55" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497164</v>
+        <v>497302</v>
       </c>
       <c r="R55" t="n">
-        <v>6830343</v>
+        <v>6830384</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6437,7 +6437,7 @@
         <v>130257277</v>
       </c>
       <c r="B56" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>130256299</v>
       </c>
       <c r="B57" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>130257284</v>
       </c>
       <c r="B58" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>130256311</v>
       </c>
       <c r="B59" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>130257278</v>
       </c>
       <c r="B60" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6939,10 +6939,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130256309</v>
+        <v>130257262</v>
       </c>
       <c r="B61" t="n">
-        <v>79209</v>
+        <v>79830</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6950,21 +6950,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497156</v>
+        <v>497128</v>
       </c>
       <c r="R61" t="n">
-        <v>6830327</v>
+        <v>6830348</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7007,19 +7007,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7034,22 +7024,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130257287</v>
+        <v>130256304</v>
       </c>
       <c r="B62" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7081,10 +7071,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497234</v>
+        <v>497247</v>
       </c>
       <c r="R62" t="n">
-        <v>6830313</v>
+        <v>6830499</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7114,9 +7104,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7131,22 +7131,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130256307</v>
+        <v>130256309</v>
       </c>
       <c r="B63" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497221</v>
+        <v>497156</v>
       </c>
       <c r="R63" t="n">
-        <v>6830314</v>
+        <v>6830327</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7250,10 +7250,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130257262</v>
+        <v>130256307</v>
       </c>
       <c r="B64" t="n">
-        <v>79828</v>
+        <v>79211</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7261,21 +7261,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497128</v>
+        <v>497221</v>
       </c>
       <c r="R64" t="n">
-        <v>6830348</v>
+        <v>6830314</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7318,9 +7318,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7335,22 +7345,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130256304</v>
+        <v>130257297</v>
       </c>
       <c r="B65" t="n">
-        <v>79209</v>
+        <v>78614</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7358,21 +7368,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7382,10 +7392,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497247</v>
+        <v>497072</v>
       </c>
       <c r="R65" t="n">
-        <v>6830499</v>
+        <v>6830261</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7415,19 +7425,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7442,22 +7442,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130257297</v>
+        <v>130257287</v>
       </c>
       <c r="B66" t="n">
-        <v>78612</v>
+        <v>79211</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7465,21 +7465,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497072</v>
+        <v>497234</v>
       </c>
       <c r="R66" t="n">
-        <v>6830261</v>
+        <v>6830313</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7551,32 +7551,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130257281</v>
+        <v>130257293</v>
       </c>
       <c r="B67" t="n">
-        <v>79209</v>
+        <v>93043</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497275</v>
+        <v>497087</v>
       </c>
       <c r="R67" t="n">
-        <v>6830388</v>
+        <v>6830238</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7651,7 +7651,7 @@
         <v>130256291</v>
       </c>
       <c r="B68" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7755,32 +7755,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130257293</v>
+        <v>130257281</v>
       </c>
       <c r="B69" t="n">
-        <v>93041</v>
+        <v>79211</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497087</v>
+        <v>497275</v>
       </c>
       <c r="R69" t="n">
-        <v>6830238</v>
+        <v>6830388</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7959,45 +7959,56 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256303</v>
+        <v>130256314</v>
       </c>
       <c r="B71" t="n">
-        <v>79209</v>
+        <v>93043</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497291</v>
+        <v>497242</v>
       </c>
       <c r="R71" t="n">
-        <v>6830488</v>
+        <v>6830510</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8029,7 +8040,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8039,7 +8050,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8048,6 +8059,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8066,56 +8078,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130256314</v>
+        <v>130256303</v>
       </c>
       <c r="B72" t="n">
-        <v>93041</v>
+        <v>79211</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497242</v>
+        <v>497291</v>
       </c>
       <c r="R72" t="n">
-        <v>6830510</v>
+        <v>6830488</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8147,7 +8148,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8157,7 +8158,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8166,7 +8167,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8188,7 +8188,7 @@
         <v>130257263</v>
       </c>
       <c r="B73" t="n">
-        <v>79799</v>
+        <v>79801</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8282,45 +8282,56 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130257275</v>
+        <v>130256313</v>
       </c>
       <c r="B74" t="n">
-        <v>78966</v>
+        <v>93043</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497096</v>
+        <v>497260</v>
       </c>
       <c r="R74" t="n">
-        <v>6830218</v>
+        <v>6830540</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8350,39 +8361,50 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130256306</v>
+        <v>130257275</v>
       </c>
       <c r="B75" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8390,21 +8412,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8414,10 +8436,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497253</v>
+        <v>497096</v>
       </c>
       <c r="R75" t="n">
-        <v>6830351</v>
+        <v>6830218</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8447,19 +8469,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8474,68 +8486,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130256313</v>
+        <v>130256306</v>
       </c>
       <c r="B76" t="n">
-        <v>93041</v>
+        <v>79211</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497260</v>
+        <v>497253</v>
       </c>
       <c r="R76" t="n">
-        <v>6830540</v>
+        <v>6830351</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8567,7 +8568,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8577,7 +8578,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8586,7 +8587,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8605,10 +8605,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130257282</v>
+        <v>130257285</v>
       </c>
       <c r="B77" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497252</v>
+        <v>497250</v>
       </c>
       <c r="R77" t="n">
-        <v>6830372</v>
+        <v>6830356</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8702,10 +8702,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130257285</v>
+        <v>130257292</v>
       </c>
       <c r="B78" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8737,10 +8737,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497250</v>
+        <v>497138</v>
       </c>
       <c r="R78" t="n">
-        <v>6830356</v>
+        <v>6830320</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8799,10 +8799,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130257292</v>
+        <v>130257282</v>
       </c>
       <c r="B79" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497138</v>
+        <v>497252</v>
       </c>
       <c r="R79" t="n">
-        <v>6830320</v>
+        <v>6830372</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8899,7 +8899,7 @@
         <v>130256310</v>
       </c>
       <c r="B80" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>130256301</v>
       </c>
       <c r="B81" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9110,10 +9110,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130257289</v>
+        <v>130257261</v>
       </c>
       <c r="B82" t="n">
-        <v>79209</v>
+        <v>79830</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9121,21 +9121,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497222</v>
+        <v>497107</v>
       </c>
       <c r="R82" t="n">
-        <v>6830325</v>
+        <v>6830221</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9207,10 +9207,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130257261</v>
+        <v>130256302</v>
       </c>
       <c r="B83" t="n">
-        <v>79828</v>
+        <v>79211</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497107</v>
+        <v>497273</v>
       </c>
       <c r="R83" t="n">
-        <v>6830221</v>
+        <v>6830394</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9275,9 +9275,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9292,22 +9302,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130256302</v>
+        <v>130257289</v>
       </c>
       <c r="B84" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9339,10 +9349,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497273</v>
+        <v>497222</v>
       </c>
       <c r="R84" t="n">
-        <v>6830394</v>
+        <v>6830325</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9372,19 +9382,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9399,12 +9399,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9414,7 +9414,7 @@
         <v>130257266</v>
       </c>
       <c r="B85" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>130256315</v>
       </c>
       <c r="B86" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>130257274</v>
       </c>
       <c r="B87" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>130257268</v>
       </c>
       <c r="B88" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>130257283</v>
       </c>
       <c r="B89" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>130256300</v>
       </c>
       <c r="B91" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>130256293</v>
       </c>
       <c r="B92" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>130256305</v>
       </c>
       <c r="B93" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>130256308</v>
       </c>
       <c r="B94" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10471,10 +10471,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130257288</v>
+        <v>130257272</v>
       </c>
       <c r="B95" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10482,21 +10482,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497224</v>
+        <v>497128</v>
       </c>
       <c r="R95" t="n">
-        <v>6830319</v>
+        <v>6830345</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10568,10 +10568,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130257272</v>
+        <v>130257288</v>
       </c>
       <c r="B96" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10579,21 +10579,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497128</v>
+        <v>497224</v>
       </c>
       <c r="R96" t="n">
-        <v>6830345</v>
+        <v>6830319</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10668,7 +10668,7 @@
         <v>130257269</v>
       </c>
       <c r="B97" t="n">
-        <v>57045</v>
+        <v>57047</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>130256296</v>
       </c>
       <c r="B98" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>130257294</v>
       </c>
       <c r="B99" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130257290</v>
+        <v>130257286</v>
       </c>
       <c r="B100" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497200</v>
+        <v>497240</v>
       </c>
       <c r="R100" t="n">
-        <v>6830326</v>
+        <v>6830306</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130257286</v>
+        <v>130257290</v>
       </c>
       <c r="B101" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497240</v>
+        <v>497200</v>
       </c>
       <c r="R101" t="n">
-        <v>6830306</v>
+        <v>6830326</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11168,10 +11168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256292</v>
+        <v>130256286</v>
       </c>
       <c r="B102" t="n">
-        <v>78966</v>
+        <v>78969</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497168</v>
+        <v>497251</v>
       </c>
       <c r="R102" t="n">
-        <v>6830310</v>
+        <v>6830494</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11275,10 +11275,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256312</v>
+        <v>130256292</v>
       </c>
       <c r="B103" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497244</v>
+        <v>497168</v>
       </c>
       <c r="R103" t="n">
-        <v>6830538</v>
+        <v>6830310</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11382,10 +11382,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256286</v>
+        <v>130256312</v>
       </c>
       <c r="B104" t="n">
-        <v>78967</v>
+        <v>79211</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11393,21 +11393,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497251</v>
+        <v>497244</v>
       </c>
       <c r="R104" t="n">
-        <v>6830494</v>
+        <v>6830538</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130252273</v>
+        <v>130252255</v>
       </c>
       <c r="B2" t="n">
-        <v>93043</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497114</v>
+        <v>497263</v>
       </c>
       <c r="R2" t="n">
-        <v>6830195</v>
+        <v>6830449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252255</v>
+        <v>130252273</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>93047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497263</v>
+        <v>497114</v>
       </c>
       <c r="R3" t="n">
-        <v>6830449</v>
+        <v>6830195</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252694</v>
+        <v>130252256</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497321</v>
+        <v>497168</v>
       </c>
       <c r="R4" t="n">
-        <v>6830343</v>
+        <v>6830390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +984,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252270</v>
+        <v>130252694</v>
       </c>
       <c r="B5" t="n">
         <v>79211</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497118</v>
+        <v>497321</v>
       </c>
       <c r="R5" t="n">
-        <v>6830323</v>
+        <v>6830343</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,44 +1091,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252256</v>
+        <v>130252270</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497168</v>
+        <v>497118</v>
       </c>
       <c r="R6" t="n">
-        <v>6830390</v>
+        <v>6830323</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252271</v>
+        <v>130252259</v>
       </c>
       <c r="B7" t="n">
-        <v>93043</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497241</v>
+        <v>497236</v>
       </c>
       <c r="R7" t="n">
-        <v>6830507</v>
+        <v>6830502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252259</v>
+        <v>130252271</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497236</v>
+        <v>497241</v>
       </c>
       <c r="R9" t="n">
-        <v>6830502</v>
+        <v>6830507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252695</v>
+        <v>130252251</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>58013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,34 +1650,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497166</v>
+        <v>497063</v>
       </c>
       <c r="R11" t="n">
-        <v>6830368</v>
+        <v>6830279</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,12 +1742,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1853,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252251</v>
+        <v>130252695</v>
       </c>
       <c r="B13" t="n">
-        <v>58013</v>
+        <v>79211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,42 +1872,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497063</v>
+        <v>497166</v>
       </c>
       <c r="R13" t="n">
-        <v>6830279</v>
+        <v>6830368</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,12 +1956,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2289,32 +2289,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252257</v>
+        <v>130252261</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497076</v>
+        <v>497167</v>
       </c>
       <c r="R17" t="n">
-        <v>6830213</v>
+        <v>6830200</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252261</v>
+        <v>130252257</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497167</v>
+        <v>497076</v>
       </c>
       <c r="R18" t="n">
-        <v>6830200</v>
+        <v>6830213</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252693</v>
+        <v>130252252</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78969</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497066</v>
+        <v>497077</v>
       </c>
       <c r="R19" t="n">
-        <v>6830179</v>
+        <v>6830219</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,28 +2592,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252252</v>
+        <v>130252693</v>
       </c>
       <c r="B20" t="n">
-        <v>78969</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497077</v>
+        <v>497066</v>
       </c>
       <c r="R20" t="n">
-        <v>6830219</v>
+        <v>6830179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2699,51 +2700,50 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252272</v>
+        <v>130252696</v>
       </c>
       <c r="B21" t="n">
-        <v>93043</v>
+        <v>79211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497084</v>
+        <v>497147</v>
       </c>
       <c r="R21" t="n">
-        <v>6830218</v>
+        <v>6830398</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3039,32 +3039,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252696</v>
+        <v>130252272</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497147</v>
+        <v>497084</v>
       </c>
       <c r="R24" t="n">
-        <v>6830398</v>
+        <v>6830218</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,44 +3134,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130252698</v>
+        <v>130252267</v>
       </c>
       <c r="B25" t="n">
-        <v>93043</v>
+        <v>79211</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497112</v>
+        <v>497178</v>
       </c>
       <c r="R25" t="n">
-        <v>6830192</v>
+        <v>6830332</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,51 +3235,50 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252267</v>
+        <v>130252698</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497178</v>
+        <v>497112</v>
       </c>
       <c r="R26" t="n">
-        <v>6830332</v>
+        <v>6830192</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3324,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3334,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,18 +3342,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4110,32 +4110,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252697</v>
+        <v>130252682</v>
       </c>
       <c r="B34" t="n">
-        <v>93043</v>
+        <v>78969</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497086</v>
+        <v>497144</v>
       </c>
       <c r="R34" t="n">
-        <v>6830210</v>
+        <v>6830357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4199,7 +4199,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4218,32 +4217,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130252682</v>
+        <v>130252697</v>
       </c>
       <c r="B35" t="n">
-        <v>78969</v>
+        <v>93047</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4252,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497144</v>
+        <v>497086</v>
       </c>
       <c r="R35" t="n">
-        <v>6830357</v>
+        <v>6830210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4288,7 +4287,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4298,7 +4297,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4307,6 +4306,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5100,10 +5100,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252254</v>
+        <v>130252248</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>57044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5111,24 +5111,32 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
@@ -5138,7 +5146,7 @@
         <v>497253</v>
       </c>
       <c r="R43" t="n">
-        <v>6830488</v>
+        <v>6830469</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,7 +5178,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5180,7 +5188,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5207,10 +5220,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252686</v>
+        <v>130252690</v>
       </c>
       <c r="B44" t="n">
-        <v>78969</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5218,21 +5231,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5242,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497085</v>
+        <v>497163</v>
       </c>
       <c r="R44" t="n">
-        <v>6830215</v>
+        <v>6830392</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5277,7 +5290,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5287,7 +5300,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5314,10 +5327,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252248</v>
+        <v>130252254</v>
       </c>
       <c r="B45" t="n">
-        <v>57044</v>
+        <v>8451</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5325,32 +5338,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
@@ -5360,7 +5365,7 @@
         <v>497253</v>
       </c>
       <c r="R45" t="n">
-        <v>6830469</v>
+        <v>6830488</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5392,7 +5397,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5402,12 +5407,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5434,10 +5434,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252690</v>
+        <v>130252686</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>78969</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5445,21 +5445,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497163</v>
+        <v>497085</v>
       </c>
       <c r="R46" t="n">
-        <v>6830392</v>
+        <v>6830215</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5541,10 +5541,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130257279</v>
+        <v>130256297</v>
       </c>
       <c r="B47" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497320</v>
+        <v>497115</v>
       </c>
       <c r="R47" t="n">
-        <v>6830386</v>
+        <v>6830196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5609,9 +5609,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5626,22 +5636,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130256297</v>
+        <v>130257279</v>
       </c>
       <c r="B48" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5649,21 +5659,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5673,10 +5683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497115</v>
+        <v>497320</v>
       </c>
       <c r="R48" t="n">
-        <v>6830196</v>
+        <v>6830386</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5706,19 +5716,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5733,12 +5733,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130257291</v>
+        <v>130257280</v>
       </c>
       <c r="B54" t="n">
         <v>79211</v>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497164</v>
+        <v>497302</v>
       </c>
       <c r="R54" t="n">
-        <v>6830343</v>
+        <v>6830384</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130257280</v>
+        <v>130257291</v>
       </c>
       <c r="B55" t="n">
         <v>79211</v>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497302</v>
+        <v>497164</v>
       </c>
       <c r="R55" t="n">
-        <v>6830384</v>
+        <v>6830343</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130256307</v>
+        <v>130257287</v>
       </c>
       <c r="B64" t="n">
         <v>79211</v>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497221</v>
+        <v>497234</v>
       </c>
       <c r="R64" t="n">
-        <v>6830314</v>
+        <v>6830313</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7318,19 +7318,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7345,22 +7335,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130257297</v>
+        <v>130256307</v>
       </c>
       <c r="B65" t="n">
-        <v>78614</v>
+        <v>79211</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7368,21 +7358,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7392,10 +7382,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497072</v>
+        <v>497221</v>
       </c>
       <c r="R65" t="n">
-        <v>6830261</v>
+        <v>6830314</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7425,9 +7415,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7442,22 +7442,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130257287</v>
+        <v>130257297</v>
       </c>
       <c r="B66" t="n">
-        <v>79211</v>
+        <v>78614</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7465,21 +7465,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497234</v>
+        <v>497072</v>
       </c>
       <c r="R66" t="n">
-        <v>6830313</v>
+        <v>6830261</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7551,32 +7551,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130257293</v>
+        <v>130257281</v>
       </c>
       <c r="B67" t="n">
-        <v>93043</v>
+        <v>79211</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497087</v>
+        <v>497275</v>
       </c>
       <c r="R67" t="n">
-        <v>6830238</v>
+        <v>6830388</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7755,32 +7755,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130257281</v>
+        <v>130257293</v>
       </c>
       <c r="B69" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497275</v>
+        <v>497087</v>
       </c>
       <c r="R69" t="n">
-        <v>6830388</v>
+        <v>6830238</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7962,7 +7962,7 @@
         <v>130256314</v>
       </c>
       <c r="B71" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8078,10 +8078,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130256303</v>
+        <v>130257263</v>
       </c>
       <c r="B72" t="n">
-        <v>79211</v>
+        <v>79801</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,21 +8089,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497291</v>
+        <v>497069</v>
       </c>
       <c r="R72" t="n">
-        <v>6830488</v>
+        <v>6830264</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8146,19 +8146,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8173,22 +8163,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130257263</v>
+        <v>130256303</v>
       </c>
       <c r="B73" t="n">
-        <v>79801</v>
+        <v>79211</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8196,21 +8186,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8220,10 +8210,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497069</v>
+        <v>497291</v>
       </c>
       <c r="R73" t="n">
-        <v>6830264</v>
+        <v>6830488</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8253,9 +8243,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8270,68 +8270,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130256313</v>
+        <v>130257275</v>
       </c>
       <c r="B74" t="n">
-        <v>93043</v>
+        <v>78968</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497260</v>
+        <v>497096</v>
       </c>
       <c r="R74" t="n">
-        <v>6830540</v>
+        <v>6830218</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8361,50 +8350,39 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130257275</v>
+        <v>130256306</v>
       </c>
       <c r="B75" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8412,21 +8390,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8436,10 +8414,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497096</v>
+        <v>497253</v>
       </c>
       <c r="R75" t="n">
-        <v>6830218</v>
+        <v>6830351</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8469,9 +8447,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8486,57 +8474,68 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130256306</v>
+        <v>130256313</v>
       </c>
       <c r="B76" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497253</v>
+        <v>497260</v>
       </c>
       <c r="R76" t="n">
-        <v>6830351</v>
+        <v>6830540</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8568,7 +8567,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8578,7 +8577,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8587,6 +8586,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8605,7 +8605,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130257285</v>
+        <v>130257282</v>
       </c>
       <c r="B77" t="n">
         <v>79211</v>
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497250</v>
+        <v>497252</v>
       </c>
       <c r="R77" t="n">
-        <v>6830356</v>
+        <v>6830372</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8702,7 +8702,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130257292</v>
+        <v>130257285</v>
       </c>
       <c r="B78" t="n">
         <v>79211</v>
@@ -8737,10 +8737,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497138</v>
+        <v>497250</v>
       </c>
       <c r="R78" t="n">
-        <v>6830320</v>
+        <v>6830356</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8799,7 +8799,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130257282</v>
+        <v>130257292</v>
       </c>
       <c r="B79" t="n">
         <v>79211</v>
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497252</v>
+        <v>497138</v>
       </c>
       <c r="R79" t="n">
-        <v>6830372</v>
+        <v>6830320</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9110,10 +9110,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130257261</v>
+        <v>130257289</v>
       </c>
       <c r="B82" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9121,21 +9121,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497107</v>
+        <v>497222</v>
       </c>
       <c r="R82" t="n">
-        <v>6830221</v>
+        <v>6830325</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9207,10 +9207,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130256302</v>
+        <v>130257261</v>
       </c>
       <c r="B83" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497273</v>
+        <v>497107</v>
       </c>
       <c r="R83" t="n">
-        <v>6830394</v>
+        <v>6830221</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9275,19 +9275,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9302,19 +9292,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130257289</v>
+        <v>130256302</v>
       </c>
       <c r="B84" t="n">
         <v>79211</v>
@@ -9349,10 +9339,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497222</v>
+        <v>497273</v>
       </c>
       <c r="R84" t="n">
-        <v>6830325</v>
+        <v>6830394</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9382,9 +9372,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9399,12 +9399,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9519,7 +9519,7 @@
         <v>130256315</v>
       </c>
       <c r="B86" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9635,10 +9635,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130257274</v>
+        <v>130257268</v>
       </c>
       <c r="B87" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9646,21 +9646,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497107</v>
+        <v>497074</v>
       </c>
       <c r="R87" t="n">
-        <v>6830221</v>
+        <v>6830292</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9732,10 +9732,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130257268</v>
+        <v>130257274</v>
       </c>
       <c r="B88" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9743,21 +9743,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9767,10 +9767,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497074</v>
+        <v>497107</v>
       </c>
       <c r="R88" t="n">
-        <v>6830292</v>
+        <v>6830221</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10043,7 +10043,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130256300</v>
+        <v>130256305</v>
       </c>
       <c r="B91" t="n">
         <v>79211</v>
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497391</v>
+        <v>497258</v>
       </c>
       <c r="R91" t="n">
-        <v>6830230</v>
+        <v>6830560</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10150,10 +10150,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130256293</v>
+        <v>130256300</v>
       </c>
       <c r="B92" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10161,21 +10161,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497117</v>
+        <v>497391</v>
       </c>
       <c r="R92" t="n">
-        <v>6830376</v>
+        <v>6830230</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10257,10 +10257,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130256305</v>
+        <v>130256293</v>
       </c>
       <c r="B93" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10268,21 +10268,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497258</v>
+        <v>497117</v>
       </c>
       <c r="R93" t="n">
-        <v>6830560</v>
+        <v>6830376</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10974,7 +10974,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130257286</v>
+        <v>130257290</v>
       </c>
       <c r="B100" t="n">
         <v>79211</v>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497240</v>
+        <v>497200</v>
       </c>
       <c r="R100" t="n">
-        <v>6830306</v>
+        <v>6830326</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11071,7 +11071,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130257290</v>
+        <v>130257286</v>
       </c>
       <c r="B101" t="n">
         <v>79211</v>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497200</v>
+        <v>497240</v>
       </c>
       <c r="R101" t="n">
-        <v>6830326</v>
+        <v>6830306</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11168,10 +11168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256286</v>
+        <v>130256312</v>
       </c>
       <c r="B102" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497251</v>
+        <v>497244</v>
       </c>
       <c r="R102" t="n">
-        <v>6830494</v>
+        <v>6830538</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11275,10 +11275,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256292</v>
+        <v>130256286</v>
       </c>
       <c r="B103" t="n">
-        <v>78968</v>
+        <v>78969</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497168</v>
+        <v>497251</v>
       </c>
       <c r="R103" t="n">
-        <v>6830310</v>
+        <v>6830494</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11382,10 +11382,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256312</v>
+        <v>130256292</v>
       </c>
       <c r="B104" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11393,21 +11393,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497244</v>
+        <v>497168</v>
       </c>
       <c r="R104" t="n">
-        <v>6830538</v>
+        <v>6830310</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252256</v>
+        <v>130252694</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497168</v>
+        <v>497321</v>
       </c>
       <c r="R4" t="n">
-        <v>6830390</v>
+        <v>6830343</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +984,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252694</v>
+        <v>130252270</v>
       </c>
       <c r="B5" t="n">
         <v>79211</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497321</v>
+        <v>497118</v>
       </c>
       <c r="R5" t="n">
-        <v>6830343</v>
+        <v>6830323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,44 +1091,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252270</v>
+        <v>130252256</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497118</v>
+        <v>497168</v>
       </c>
       <c r="R6" t="n">
-        <v>6830323</v>
+        <v>6830390</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252259</v>
+        <v>130252262</v>
       </c>
       <c r="B7" t="n">
         <v>78968</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497236</v>
+        <v>497260</v>
       </c>
       <c r="R7" t="n">
-        <v>6830502</v>
+        <v>6830494</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,6 +1299,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1317,32 +1318,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130252262</v>
+        <v>130252271</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497260</v>
+        <v>497241</v>
       </c>
       <c r="R8" t="n">
-        <v>6830494</v>
+        <v>6830507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1388,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1398,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1406,7 +1407,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1425,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252271</v>
+        <v>130252259</v>
       </c>
       <c r="B9" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497241</v>
+        <v>497236</v>
       </c>
       <c r="R9" t="n">
-        <v>6830507</v>
+        <v>6830502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3146,32 +3146,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130252267</v>
+        <v>130252253</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497178</v>
+        <v>497334</v>
       </c>
       <c r="R25" t="n">
-        <v>6830332</v>
+        <v>6830121</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3253,32 +3253,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252698</v>
+        <v>130252685</v>
       </c>
       <c r="B26" t="n">
-        <v>93047</v>
+        <v>78969</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497112</v>
+        <v>497071</v>
       </c>
       <c r="R26" t="n">
-        <v>6830192</v>
+        <v>6830207</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,7 +3342,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3361,7 +3360,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130252685</v>
+        <v>130252684</v>
       </c>
       <c r="B27" t="n">
         <v>78969</v>
@@ -3396,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497071</v>
+        <v>497063</v>
       </c>
       <c r="R27" t="n">
-        <v>6830207</v>
+        <v>6830346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3441,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252684</v>
+        <v>130252267</v>
       </c>
       <c r="B28" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,21 +3478,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497063</v>
+        <v>497178</v>
       </c>
       <c r="R28" t="n">
-        <v>6830346</v>
+        <v>6830332</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,7 +3537,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3548,7 +3547,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,22 +3562,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252253</v>
+        <v>130252698</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>93047</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3586,21 +3585,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3610,10 +3609,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497334</v>
+        <v>497112</v>
       </c>
       <c r="R29" t="n">
-        <v>6830121</v>
+        <v>6830192</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,7 +3644,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3655,7 +3654,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3664,18 +3663,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4110,32 +4110,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252682</v>
+        <v>130252697</v>
       </c>
       <c r="B34" t="n">
-        <v>78969</v>
+        <v>93047</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497144</v>
+        <v>497086</v>
       </c>
       <c r="R34" t="n">
-        <v>6830357</v>
+        <v>6830210</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4199,6 +4199,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4217,32 +4218,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130252697</v>
+        <v>130252682</v>
       </c>
       <c r="B35" t="n">
-        <v>93047</v>
+        <v>78969</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4252,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497086</v>
+        <v>497144</v>
       </c>
       <c r="R35" t="n">
-        <v>6830210</v>
+        <v>6830357</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4287,7 +4288,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4297,7 +4298,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4306,7 +4307,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130256297</v>
+        <v>130256288</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>78969</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497115</v>
+        <v>497067</v>
       </c>
       <c r="R47" t="n">
-        <v>6830196</v>
+        <v>6830217</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5648,10 +5648,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130257279</v>
+        <v>130256297</v>
       </c>
       <c r="B48" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5659,21 +5659,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497320</v>
+        <v>497115</v>
       </c>
       <c r="R48" t="n">
-        <v>6830386</v>
+        <v>6830196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5716,9 +5716,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5733,22 +5743,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130256288</v>
+        <v>130257279</v>
       </c>
       <c r="B49" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5756,21 +5766,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5780,10 +5790,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497067</v>
+        <v>497320</v>
       </c>
       <c r="R49" t="n">
-        <v>6830217</v>
+        <v>6830386</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5813,19 +5823,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5840,22 +5840,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130257295</v>
+        <v>130257265</v>
       </c>
       <c r="B50" t="n">
-        <v>78218</v>
+        <v>91782</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5863,21 +5863,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6487</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497072</v>
+        <v>497131</v>
       </c>
       <c r="R50" t="n">
-        <v>6830261</v>
+        <v>6830311</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130257276</v>
+        <v>130257295</v>
       </c>
       <c r="B51" t="n">
-        <v>78968</v>
+        <v>78218</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497082</v>
+        <v>497072</v>
       </c>
       <c r="R51" t="n">
-        <v>6830202</v>
+        <v>6830261</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6046,7 +6046,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130257271</v>
+        <v>130257276</v>
       </c>
       <c r="B52" t="n">
         <v>78968</v>
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497270</v>
+        <v>497082</v>
       </c>
       <c r="R52" t="n">
-        <v>6830422</v>
+        <v>6830202</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130257265</v>
+        <v>130257271</v>
       </c>
       <c r="B53" t="n">
-        <v>91782</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497131</v>
+        <v>497270</v>
       </c>
       <c r="R53" t="n">
-        <v>6830311</v>
+        <v>6830422</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7551,45 +7551,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130257281</v>
+        <v>130257270</v>
       </c>
       <c r="B67" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497275</v>
+        <v>497113</v>
       </c>
       <c r="R67" t="n">
-        <v>6830388</v>
+        <v>6830234</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7630,6 +7639,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7648,10 +7658,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130256291</v>
+        <v>130257281</v>
       </c>
       <c r="B68" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7659,21 +7669,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7683,10 +7693,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497251</v>
+        <v>497275</v>
       </c>
       <c r="R68" t="n">
-        <v>6830491</v>
+        <v>6830388</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7716,19 +7726,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7743,44 +7743,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130257293</v>
+        <v>130256291</v>
       </c>
       <c r="B69" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497087</v>
+        <v>497251</v>
       </c>
       <c r="R69" t="n">
-        <v>6830238</v>
+        <v>6830491</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7823,9 +7823,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7840,22 +7850,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130257270</v>
+        <v>130257293</v>
       </c>
       <c r="B70" t="n">
-        <v>8451</v>
+        <v>93047</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7863,43 +7873,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497113</v>
+        <v>497087</v>
       </c>
       <c r="R70" t="n">
-        <v>6830234</v>
+        <v>6830238</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7940,7 +7941,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7959,56 +7959,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256314</v>
+        <v>130257263</v>
       </c>
       <c r="B71" t="n">
-        <v>93047</v>
+        <v>79801</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497242</v>
+        <v>497069</v>
       </c>
       <c r="R71" t="n">
-        <v>6830510</v>
+        <v>6830264</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8038,50 +8027,39 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130257263</v>
+        <v>130256303</v>
       </c>
       <c r="B72" t="n">
-        <v>79801</v>
+        <v>79211</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,21 +8067,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8113,10 +8091,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497069</v>
+        <v>497291</v>
       </c>
       <c r="R72" t="n">
-        <v>6830264</v>
+        <v>6830488</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8146,9 +8124,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8163,57 +8151,68 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130256303</v>
+        <v>130256314</v>
       </c>
       <c r="B73" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497291</v>
+        <v>497242</v>
       </c>
       <c r="R73" t="n">
-        <v>6830488</v>
+        <v>6830510</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8245,7 +8244,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8255,7 +8254,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8264,6 +8263,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9110,10 +9110,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130257289</v>
+        <v>130257266</v>
       </c>
       <c r="B82" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9121,34 +9121,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497222</v>
+        <v>497142</v>
       </c>
       <c r="R82" t="n">
-        <v>6830325</v>
+        <v>6830327</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9207,10 +9215,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130257261</v>
+        <v>130257289</v>
       </c>
       <c r="B83" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9218,21 +9226,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9242,10 +9250,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497107</v>
+        <v>497222</v>
       </c>
       <c r="R83" t="n">
-        <v>6830221</v>
+        <v>6830325</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9304,10 +9312,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130256302</v>
+        <v>130257261</v>
       </c>
       <c r="B84" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9315,21 +9323,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9339,10 +9347,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497273</v>
+        <v>497107</v>
       </c>
       <c r="R84" t="n">
-        <v>6830394</v>
+        <v>6830221</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9372,19 +9380,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9399,22 +9397,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130257266</v>
+        <v>130256302</v>
       </c>
       <c r="B85" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9422,42 +9420,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497142</v>
+        <v>497273</v>
       </c>
       <c r="R85" t="n">
-        <v>6830327</v>
+        <v>6830394</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9487,9 +9477,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9504,22 +9504,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130256315</v>
+        <v>130256289</v>
       </c>
       <c r="B86" t="n">
-        <v>93047</v>
+        <v>8451</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9527,34 +9527,32 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9562,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497261</v>
+        <v>497101</v>
       </c>
       <c r="R86" t="n">
-        <v>6830529</v>
+        <v>6830183</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9597,7 +9595,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9607,7 +9605,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9635,10 +9633,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130257268</v>
+        <v>130257274</v>
       </c>
       <c r="B87" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9646,21 +9644,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9670,10 +9668,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497074</v>
+        <v>497107</v>
       </c>
       <c r="R87" t="n">
-        <v>6830292</v>
+        <v>6830221</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9732,10 +9730,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130257274</v>
+        <v>130257268</v>
       </c>
       <c r="B88" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9743,21 +9741,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9767,10 +9765,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497107</v>
+        <v>497074</v>
       </c>
       <c r="R88" t="n">
-        <v>6830221</v>
+        <v>6830292</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9926,10 +9924,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130256289</v>
+        <v>130256315</v>
       </c>
       <c r="B90" t="n">
-        <v>8451</v>
+        <v>93047</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9937,32 +9935,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497101</v>
+        <v>497261</v>
       </c>
       <c r="R90" t="n">
-        <v>6830183</v>
+        <v>6830529</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10043,7 +10043,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130256305</v>
+        <v>130256300</v>
       </c>
       <c r="B91" t="n">
         <v>79211</v>
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497258</v>
+        <v>497391</v>
       </c>
       <c r="R91" t="n">
-        <v>6830560</v>
+        <v>6830230</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10150,10 +10150,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130256300</v>
+        <v>130256293</v>
       </c>
       <c r="B92" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10161,21 +10161,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497391</v>
+        <v>497117</v>
       </c>
       <c r="R92" t="n">
-        <v>6830230</v>
+        <v>6830376</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10257,10 +10257,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130256293</v>
+        <v>130256305</v>
       </c>
       <c r="B93" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10268,21 +10268,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497117</v>
+        <v>497258</v>
       </c>
       <c r="R93" t="n">
-        <v>6830376</v>
+        <v>6830560</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11168,10 +11168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256312</v>
+        <v>130256292</v>
       </c>
       <c r="B102" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497244</v>
+        <v>497168</v>
       </c>
       <c r="R102" t="n">
-        <v>6830538</v>
+        <v>6830310</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11275,10 +11275,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256286</v>
+        <v>130256312</v>
       </c>
       <c r="B103" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497251</v>
+        <v>497244</v>
       </c>
       <c r="R103" t="n">
-        <v>6830494</v>
+        <v>6830538</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11382,10 +11382,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256292</v>
+        <v>130256286</v>
       </c>
       <c r="B104" t="n">
-        <v>78968</v>
+        <v>78969</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11393,21 +11393,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497168</v>
+        <v>497251</v>
       </c>
       <c r="R104" t="n">
-        <v>6830310</v>
+        <v>6830494</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -1318,32 +1318,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130252271</v>
+        <v>130252259</v>
       </c>
       <c r="B8" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497241</v>
+        <v>497236</v>
       </c>
       <c r="R8" t="n">
-        <v>6830507</v>
+        <v>6830502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252259</v>
+        <v>130252271</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497236</v>
+        <v>497241</v>
       </c>
       <c r="R9" t="n">
-        <v>6830502</v>
+        <v>6830507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252251</v>
+        <v>130252244</v>
       </c>
       <c r="B11" t="n">
-        <v>58013</v>
+        <v>79830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,42 +1650,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497063</v>
+        <v>497260</v>
       </c>
       <c r="R11" t="n">
-        <v>6830279</v>
+        <v>6830494</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1727,7 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252244</v>
+        <v>130252695</v>
       </c>
       <c r="B12" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1789,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497260</v>
+        <v>497166</v>
       </c>
       <c r="R12" t="n">
-        <v>6830494</v>
+        <v>6830368</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1816,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1834,7 +1826,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,22 +1841,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252695</v>
+        <v>130252251</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>58013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,34 +1864,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497166</v>
+        <v>497063</v>
       </c>
       <c r="R13" t="n">
-        <v>6830368</v>
+        <v>6830279</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,12 +1956,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252252</v>
+        <v>130252693</v>
       </c>
       <c r="B19" t="n">
-        <v>78969</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497077</v>
+        <v>497066</v>
       </c>
       <c r="R19" t="n">
-        <v>6830219</v>
+        <v>6830179</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,29 +2592,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252693</v>
+        <v>130252252</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78969</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497066</v>
+        <v>497077</v>
       </c>
       <c r="R20" t="n">
-        <v>6830179</v>
+        <v>6830219</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,50 +2699,51 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252696</v>
+        <v>130252272</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497147</v>
+        <v>497084</v>
       </c>
       <c r="R21" t="n">
-        <v>6830398</v>
+        <v>6830218</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,22 +2813,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252691</v>
+        <v>130252696</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497108</v>
+        <v>497147</v>
       </c>
       <c r="R22" t="n">
-        <v>6830371</v>
+        <v>6830398</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2932,10 +2932,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252264</v>
+        <v>130252691</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,21 +2943,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497334</v>
+        <v>497108</v>
       </c>
       <c r="R23" t="n">
-        <v>6830124</v>
+        <v>6830371</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,44 +3027,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252272</v>
+        <v>130252264</v>
       </c>
       <c r="B24" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497084</v>
+        <v>497334</v>
       </c>
       <c r="R24" t="n">
-        <v>6830218</v>
+        <v>6830124</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,10 +3146,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130252253</v>
+        <v>130252698</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>93047</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,21 +3157,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497334</v>
+        <v>497112</v>
       </c>
       <c r="R25" t="n">
-        <v>6830121</v>
+        <v>6830192</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,28 +3235,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252685</v>
+        <v>130252267</v>
       </c>
       <c r="B26" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,21 +3265,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497071</v>
+        <v>497178</v>
       </c>
       <c r="R26" t="n">
-        <v>6830207</v>
+        <v>6830332</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3324,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3334,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,44 +3349,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130252684</v>
+        <v>130252253</v>
       </c>
       <c r="B27" t="n">
-        <v>78969</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3395,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497063</v>
+        <v>497334</v>
       </c>
       <c r="R27" t="n">
-        <v>6830346</v>
+        <v>6830121</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3431,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3440,7 +3441,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3455,22 +3456,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252267</v>
+        <v>130252684</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3478,21 +3479,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3502,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497178</v>
+        <v>497063</v>
       </c>
       <c r="R28" t="n">
-        <v>6830332</v>
+        <v>6830346</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,7 +3538,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3547,7 +3548,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,44 +3563,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252698</v>
+        <v>130252685</v>
       </c>
       <c r="B29" t="n">
-        <v>93047</v>
+        <v>78969</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3609,10 +3610,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497112</v>
+        <v>497071</v>
       </c>
       <c r="R29" t="n">
-        <v>6830192</v>
+        <v>6830207</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,7 +3645,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3654,7 +3655,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3663,7 +3664,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -5100,10 +5100,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252248</v>
+        <v>130252254</v>
       </c>
       <c r="B43" t="n">
-        <v>57044</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5111,32 +5111,24 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
@@ -5146,7 +5138,7 @@
         <v>497253</v>
       </c>
       <c r="R43" t="n">
-        <v>6830469</v>
+        <v>6830488</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5178,7 +5170,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5188,12 +5180,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5220,10 +5207,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252690</v>
+        <v>130252686</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>78969</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5231,21 +5218,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5255,10 +5242,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497163</v>
+        <v>497085</v>
       </c>
       <c r="R44" t="n">
-        <v>6830392</v>
+        <v>6830215</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5290,7 +5277,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5300,7 +5287,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,32 +5314,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252254</v>
+        <v>130252690</v>
       </c>
       <c r="B45" t="n">
-        <v>8451</v>
+        <v>78968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5362,10 +5349,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497253</v>
+        <v>497163</v>
       </c>
       <c r="R45" t="n">
-        <v>6830488</v>
+        <v>6830392</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5397,7 +5384,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5407,7 +5394,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5422,57 +5409,65 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252686</v>
+        <v>130252248</v>
       </c>
       <c r="B46" t="n">
-        <v>78969</v>
+        <v>57044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497085</v>
+        <v>497253</v>
       </c>
       <c r="R46" t="n">
-        <v>6830215</v>
+        <v>6830469</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,7 +5499,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5514,7 +5509,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5529,22 +5529,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130256288</v>
+        <v>130256297</v>
       </c>
       <c r="B47" t="n">
-        <v>78969</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497067</v>
+        <v>497115</v>
       </c>
       <c r="R47" t="n">
-        <v>6830217</v>
+        <v>6830196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5648,10 +5648,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130256297</v>
+        <v>130257279</v>
       </c>
       <c r="B48" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5659,21 +5659,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497115</v>
+        <v>497320</v>
       </c>
       <c r="R48" t="n">
-        <v>6830196</v>
+        <v>6830386</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5716,19 +5716,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5743,22 +5733,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130257279</v>
+        <v>130256288</v>
       </c>
       <c r="B49" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5766,21 +5756,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5790,10 +5780,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497320</v>
+        <v>497067</v>
       </c>
       <c r="R49" t="n">
-        <v>6830386</v>
+        <v>6830217</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5823,9 +5813,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5840,22 +5840,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130257265</v>
+        <v>130257295</v>
       </c>
       <c r="B50" t="n">
-        <v>91782</v>
+        <v>78218</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5863,21 +5863,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6487</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497131</v>
+        <v>497072</v>
       </c>
       <c r="R50" t="n">
-        <v>6830311</v>
+        <v>6830261</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130257295</v>
+        <v>130257276</v>
       </c>
       <c r="B51" t="n">
-        <v>78218</v>
+        <v>78968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497072</v>
+        <v>497082</v>
       </c>
       <c r="R51" t="n">
-        <v>6830261</v>
+        <v>6830202</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6046,7 +6046,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130257276</v>
+        <v>130257271</v>
       </c>
       <c r="B52" t="n">
         <v>78968</v>
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497082</v>
+        <v>497270</v>
       </c>
       <c r="R52" t="n">
-        <v>6830202</v>
+        <v>6830422</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130257271</v>
+        <v>130257265</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>91782</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497270</v>
+        <v>497131</v>
       </c>
       <c r="R53" t="n">
-        <v>6830422</v>
+        <v>6830311</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130257270</v>
+        <v>130257293</v>
       </c>
       <c r="B67" t="n">
-        <v>8451</v>
+        <v>93047</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7562,43 +7562,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497113</v>
+        <v>497087</v>
       </c>
       <c r="R67" t="n">
-        <v>6830234</v>
+        <v>6830238</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7639,7 +7630,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7862,10 +7852,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130257293</v>
+        <v>130257270</v>
       </c>
       <c r="B70" t="n">
-        <v>93047</v>
+        <v>8451</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7873,34 +7863,43 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497087</v>
+        <v>497113</v>
       </c>
       <c r="R70" t="n">
-        <v>6830238</v>
+        <v>6830234</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7941,6 +7940,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7959,45 +7959,56 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130257263</v>
+        <v>130256314</v>
       </c>
       <c r="B71" t="n">
-        <v>79801</v>
+        <v>93047</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497069</v>
+        <v>497242</v>
       </c>
       <c r="R71" t="n">
-        <v>6830264</v>
+        <v>6830510</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8027,29 +8038,40 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8163,56 +8185,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130256314</v>
+        <v>130257263</v>
       </c>
       <c r="B73" t="n">
-        <v>93047</v>
+        <v>79801</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497242</v>
+        <v>497069</v>
       </c>
       <c r="R73" t="n">
-        <v>6830510</v>
+        <v>6830264</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8242,85 +8253,85 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130257275</v>
+        <v>130256313</v>
       </c>
       <c r="B74" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497096</v>
+        <v>497260</v>
       </c>
       <c r="R74" t="n">
-        <v>6830218</v>
+        <v>6830540</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8350,39 +8361,50 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130256306</v>
+        <v>130257275</v>
       </c>
       <c r="B75" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8390,21 +8412,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8414,10 +8436,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497253</v>
+        <v>497096</v>
       </c>
       <c r="R75" t="n">
-        <v>6830351</v>
+        <v>6830218</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8447,19 +8469,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8474,68 +8486,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130256313</v>
+        <v>130256306</v>
       </c>
       <c r="B76" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497260</v>
+        <v>497253</v>
       </c>
       <c r="R76" t="n">
-        <v>6830540</v>
+        <v>6830351</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8567,7 +8568,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8577,7 +8578,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8586,7 +8587,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9110,10 +9110,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130257266</v>
+        <v>130257289</v>
       </c>
       <c r="B82" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9121,42 +9121,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497142</v>
+        <v>497222</v>
       </c>
       <c r="R82" t="n">
-        <v>6830327</v>
+        <v>6830325</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9215,10 +9207,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130257289</v>
+        <v>130257261</v>
       </c>
       <c r="B83" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9226,21 +9218,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9250,10 +9242,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497222</v>
+        <v>497107</v>
       </c>
       <c r="R83" t="n">
-        <v>6830325</v>
+        <v>6830221</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9312,10 +9304,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130257261</v>
+        <v>130256302</v>
       </c>
       <c r="B84" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9323,21 +9315,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9347,10 +9339,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497107</v>
+        <v>497273</v>
       </c>
       <c r="R84" t="n">
-        <v>6830221</v>
+        <v>6830394</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9380,9 +9372,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9397,22 +9399,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130256302</v>
+        <v>130257266</v>
       </c>
       <c r="B85" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9420,34 +9422,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497273</v>
+        <v>497142</v>
       </c>
       <c r="R85" t="n">
-        <v>6830394</v>
+        <v>6830327</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9477,19 +9487,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9504,22 +9504,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130256289</v>
+        <v>130256315</v>
       </c>
       <c r="B86" t="n">
-        <v>8451</v>
+        <v>93047</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9527,32 +9527,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9560,10 +9562,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497101</v>
+        <v>497261</v>
       </c>
       <c r="R86" t="n">
-        <v>6830183</v>
+        <v>6830529</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9595,7 +9597,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9605,7 +9607,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9633,45 +9635,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130257274</v>
+        <v>130256289</v>
       </c>
       <c r="B87" t="n">
-        <v>78968</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497107</v>
+        <v>497101</v>
       </c>
       <c r="R87" t="n">
-        <v>6830221</v>
+        <v>6830183</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9701,39 +9712,50 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130257268</v>
+        <v>130257274</v>
       </c>
       <c r="B88" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9741,21 +9763,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9765,10 +9787,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497074</v>
+        <v>497107</v>
       </c>
       <c r="R88" t="n">
-        <v>6830292</v>
+        <v>6830221</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9827,7 +9849,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130257283</v>
+        <v>130257268</v>
       </c>
       <c r="B89" t="n">
         <v>79211</v>
@@ -9862,10 +9884,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497244</v>
+        <v>497074</v>
       </c>
       <c r="R89" t="n">
-        <v>6830388</v>
+        <v>6830292</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9924,56 +9946,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130256315</v>
+        <v>130257283</v>
       </c>
       <c r="B90" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497261</v>
+        <v>497244</v>
       </c>
       <c r="R90" t="n">
-        <v>6830529</v>
+        <v>6830388</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10003,40 +10014,29 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11168,10 +11168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256292</v>
+        <v>130256286</v>
       </c>
       <c r="B102" t="n">
-        <v>78968</v>
+        <v>78969</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497168</v>
+        <v>497251</v>
       </c>
       <c r="R102" t="n">
-        <v>6830310</v>
+        <v>6830494</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11275,10 +11275,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256312</v>
+        <v>130256292</v>
       </c>
       <c r="B103" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497244</v>
+        <v>497168</v>
       </c>
       <c r="R103" t="n">
-        <v>6830538</v>
+        <v>6830310</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11382,10 +11382,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256286</v>
+        <v>130256312</v>
       </c>
       <c r="B104" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11393,21 +11393,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497251</v>
+        <v>497244</v>
       </c>
       <c r="R104" t="n">
-        <v>6830494</v>
+        <v>6830538</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130252255</v>
+        <v>130252273</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>93047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497263</v>
+        <v>497114</v>
       </c>
       <c r="R2" t="n">
-        <v>6830449</v>
+        <v>6830195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252273</v>
+        <v>130252255</v>
       </c>
       <c r="B3" t="n">
-        <v>93047</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497114</v>
+        <v>497263</v>
       </c>
       <c r="R3" t="n">
-        <v>6830195</v>
+        <v>6830449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252262</v>
+        <v>130252271</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497260</v>
+        <v>497241</v>
       </c>
       <c r="R7" t="n">
-        <v>6830494</v>
+        <v>6830507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,7 +1299,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1318,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130252259</v>
+        <v>130252262</v>
       </c>
       <c r="B8" t="n">
         <v>78968</v>
@@ -1353,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497236</v>
+        <v>497260</v>
       </c>
       <c r="R8" t="n">
-        <v>6830502</v>
+        <v>6830494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1398,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,6 +1406,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1425,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252271</v>
+        <v>130252259</v>
       </c>
       <c r="B9" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497241</v>
+        <v>497236</v>
       </c>
       <c r="R9" t="n">
-        <v>6830507</v>
+        <v>6830502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252244</v>
+        <v>130252251</v>
       </c>
       <c r="B11" t="n">
-        <v>79830</v>
+        <v>58013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,34 +1650,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497260</v>
+        <v>497063</v>
       </c>
       <c r="R11" t="n">
-        <v>6830494</v>
+        <v>6830279</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252251</v>
+        <v>130252244</v>
       </c>
       <c r="B13" t="n">
-        <v>58013</v>
+        <v>79830</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,42 +1872,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497063</v>
+        <v>497260</v>
       </c>
       <c r="R13" t="n">
-        <v>6830279</v>
+        <v>6830494</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2289,32 +2289,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252261</v>
+        <v>130252257</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497167</v>
+        <v>497076</v>
       </c>
       <c r="R17" t="n">
-        <v>6830200</v>
+        <v>6830213</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252257</v>
+        <v>130252261</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497076</v>
+        <v>497167</v>
       </c>
       <c r="R18" t="n">
-        <v>6830213</v>
+        <v>6830200</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2932,10 +2932,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252691</v>
+        <v>130252264</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,21 +2943,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497108</v>
+        <v>497334</v>
       </c>
       <c r="R23" t="n">
-        <v>6830371</v>
+        <v>6830124</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,22 +3027,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252264</v>
+        <v>130252691</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3050,21 +3050,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497334</v>
+        <v>497108</v>
       </c>
       <c r="R24" t="n">
-        <v>6830124</v>
+        <v>6830371</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,44 +3134,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130252698</v>
+        <v>130252267</v>
       </c>
       <c r="B25" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497112</v>
+        <v>497178</v>
       </c>
       <c r="R25" t="n">
-        <v>6830192</v>
+        <v>6830332</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,51 +3235,50 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252267</v>
+        <v>130252698</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497178</v>
+        <v>497112</v>
       </c>
       <c r="R26" t="n">
-        <v>6830332</v>
+        <v>6830192</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3324,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3334,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,50 +3342,51 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130252253</v>
+        <v>130252685</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>78969</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497334</v>
+        <v>497071</v>
       </c>
       <c r="R27" t="n">
-        <v>6830121</v>
+        <v>6830207</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3456,12 +3456,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3575,32 +3575,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252685</v>
+        <v>130252253</v>
       </c>
       <c r="B29" t="n">
-        <v>78969</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497071</v>
+        <v>497334</v>
       </c>
       <c r="R29" t="n">
-        <v>6830207</v>
+        <v>6830121</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3670,12 +3670,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252260</v>
+        <v>130252263</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,34 +4550,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497077</v>
+        <v>497344</v>
       </c>
       <c r="R38" t="n">
-        <v>6830219</v>
+        <v>6830116</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4609,7 +4612,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4619,7 +4622,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4628,6 +4636,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4646,10 +4655,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130252263</v>
+        <v>130252260</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4657,37 +4666,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497344</v>
+        <v>497077</v>
       </c>
       <c r="R39" t="n">
-        <v>6830116</v>
+        <v>6830219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4719,7 +4725,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4729,12 +4735,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,7 +4744,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4762,10 +4762,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252250</v>
+        <v>130252683</v>
       </c>
       <c r="B40" t="n">
-        <v>58013</v>
+        <v>78969</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4773,46 +4773,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497113</v>
+        <v>497089</v>
       </c>
       <c r="R40" t="n">
-        <v>6830338</v>
+        <v>6830358</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4844,7 +4832,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4854,12 +4842,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Var i ett meståg med bla. trädkrypare</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4874,22 +4857,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252683</v>
+        <v>130252250</v>
       </c>
       <c r="B41" t="n">
-        <v>78969</v>
+        <v>58013</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,34 +4880,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497089</v>
+        <v>497113</v>
       </c>
       <c r="R41" t="n">
-        <v>6830358</v>
+        <v>6830338</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4956,7 +4951,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4966,7 +4961,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Var i ett meståg med bla. trädkrypare</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4981,12 +4981,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252254</v>
+        <v>130252690</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497253</v>
+        <v>497163</v>
       </c>
       <c r="R43" t="n">
-        <v>6830488</v>
+        <v>6830392</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,57 +5195,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252686</v>
+        <v>130252248</v>
       </c>
       <c r="B44" t="n">
-        <v>78969</v>
+        <v>57044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497085</v>
+        <v>497253</v>
       </c>
       <c r="R44" t="n">
-        <v>6830215</v>
+        <v>6830469</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5277,7 +5285,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5287,7 +5295,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5302,44 +5315,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252690</v>
+        <v>130252254</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>8451</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5349,10 +5362,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497163</v>
+        <v>497253</v>
       </c>
       <c r="R45" t="n">
-        <v>6830392</v>
+        <v>6830488</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5384,7 +5397,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5394,7 +5407,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5409,65 +5422,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252248</v>
+        <v>130252686</v>
       </c>
       <c r="B46" t="n">
-        <v>57044</v>
+        <v>78969</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497253</v>
+        <v>497085</v>
       </c>
       <c r="R46" t="n">
-        <v>6830469</v>
+        <v>6830215</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5499,7 +5504,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5509,12 +5514,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5529,12 +5529,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5852,10 +5852,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130257295</v>
+        <v>130257265</v>
       </c>
       <c r="B50" t="n">
-        <v>78218</v>
+        <v>91782</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5863,21 +5863,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6487</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497072</v>
+        <v>497131</v>
       </c>
       <c r="R50" t="n">
-        <v>6830261</v>
+        <v>6830311</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130257276</v>
+        <v>130257295</v>
       </c>
       <c r="B51" t="n">
-        <v>78968</v>
+        <v>78218</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497082</v>
+        <v>497072</v>
       </c>
       <c r="R51" t="n">
-        <v>6830202</v>
+        <v>6830261</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6046,7 +6046,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130257271</v>
+        <v>130257276</v>
       </c>
       <c r="B52" t="n">
         <v>78968</v>
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497270</v>
+        <v>497082</v>
       </c>
       <c r="R52" t="n">
-        <v>6830422</v>
+        <v>6830202</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130257265</v>
+        <v>130257271</v>
       </c>
       <c r="B53" t="n">
-        <v>91782</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497131</v>
+        <v>497270</v>
       </c>
       <c r="R53" t="n">
-        <v>6830311</v>
+        <v>6830422</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6939,10 +6939,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130257262</v>
+        <v>130256307</v>
       </c>
       <c r="B61" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6950,21 +6950,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497128</v>
+        <v>497221</v>
       </c>
       <c r="R61" t="n">
-        <v>6830348</v>
+        <v>6830314</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7007,9 +7007,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7024,22 +7034,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130256304</v>
+        <v>130257262</v>
       </c>
       <c r="B62" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7047,21 +7057,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7071,10 +7081,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497247</v>
+        <v>497128</v>
       </c>
       <c r="R62" t="n">
-        <v>6830499</v>
+        <v>6830348</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7104,19 +7114,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7131,19 +7131,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130256309</v>
+        <v>130256304</v>
       </c>
       <c r="B63" t="n">
         <v>79211</v>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497156</v>
+        <v>497247</v>
       </c>
       <c r="R63" t="n">
-        <v>6830327</v>
+        <v>6830499</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7250,7 +7250,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130257287</v>
+        <v>130256309</v>
       </c>
       <c r="B64" t="n">
         <v>79211</v>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497234</v>
+        <v>497156</v>
       </c>
       <c r="R64" t="n">
-        <v>6830313</v>
+        <v>6830327</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7318,9 +7318,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7335,19 +7345,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130256307</v>
+        <v>130257287</v>
       </c>
       <c r="B65" t="n">
         <v>79211</v>
@@ -7382,10 +7392,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497221</v>
+        <v>497234</v>
       </c>
       <c r="R65" t="n">
-        <v>6830314</v>
+        <v>6830313</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7415,19 +7425,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7442,12 +7442,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7551,32 +7551,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130257293</v>
+        <v>130257281</v>
       </c>
       <c r="B67" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497087</v>
+        <v>497275</v>
       </c>
       <c r="R67" t="n">
-        <v>6830238</v>
+        <v>6830388</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7648,10 +7648,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130257281</v>
+        <v>130256291</v>
       </c>
       <c r="B68" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7659,21 +7659,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497275</v>
+        <v>497251</v>
       </c>
       <c r="R68" t="n">
-        <v>6830388</v>
+        <v>6830491</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7716,9 +7716,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7733,44 +7743,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130256291</v>
+        <v>130257293</v>
       </c>
       <c r="B69" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7780,10 +7790,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497251</v>
+        <v>497087</v>
       </c>
       <c r="R69" t="n">
-        <v>6830491</v>
+        <v>6830238</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7813,19 +7823,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7840,12 +7840,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8401,10 +8401,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130257275</v>
+        <v>130256306</v>
       </c>
       <c r="B75" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8412,21 +8412,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497096</v>
+        <v>497253</v>
       </c>
       <c r="R75" t="n">
-        <v>6830218</v>
+        <v>6830351</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8469,9 +8469,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8486,22 +8496,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130256306</v>
+        <v>130257275</v>
       </c>
       <c r="B76" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8509,21 +8519,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8533,10 +8543,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497253</v>
+        <v>497096</v>
       </c>
       <c r="R76" t="n">
-        <v>6830351</v>
+        <v>6830218</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8566,19 +8576,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8593,12 +8593,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9207,10 +9207,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130257261</v>
+        <v>130256302</v>
       </c>
       <c r="B83" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497107</v>
+        <v>497273</v>
       </c>
       <c r="R83" t="n">
-        <v>6830221</v>
+        <v>6830394</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9275,9 +9275,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9292,22 +9302,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130256302</v>
+        <v>130257266</v>
       </c>
       <c r="B84" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9315,34 +9325,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497273</v>
+        <v>497142</v>
       </c>
       <c r="R84" t="n">
-        <v>6830394</v>
+        <v>6830327</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9372,19 +9390,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9399,22 +9407,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130257266</v>
+        <v>130257261</v>
       </c>
       <c r="B85" t="n">
-        <v>57854</v>
+        <v>79830</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9422,42 +9430,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497142</v>
+        <v>497107</v>
       </c>
       <c r="R85" t="n">
-        <v>6830327</v>
+        <v>6830221</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9516,56 +9516,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130256315</v>
+        <v>130257274</v>
       </c>
       <c r="B86" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497261</v>
+        <v>497107</v>
       </c>
       <c r="R86" t="n">
-        <v>6830529</v>
+        <v>6830221</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9595,40 +9584,29 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9752,45 +9730,56 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130257274</v>
+        <v>130256315</v>
       </c>
       <c r="B88" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497107</v>
+        <v>497261</v>
       </c>
       <c r="R88" t="n">
-        <v>6830221</v>
+        <v>6830529</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9820,29 +9809,40 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10150,10 +10150,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130256293</v>
+        <v>130256305</v>
       </c>
       <c r="B92" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10161,21 +10161,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497117</v>
+        <v>497258</v>
       </c>
       <c r="R92" t="n">
-        <v>6830376</v>
+        <v>6830560</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10257,7 +10257,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130256305</v>
+        <v>130256308</v>
       </c>
       <c r="B93" t="n">
         <v>79211</v>
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497258</v>
+        <v>497137</v>
       </c>
       <c r="R93" t="n">
-        <v>6830560</v>
+        <v>6830325</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10364,10 +10364,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130256308</v>
+        <v>130256293</v>
       </c>
       <c r="B94" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10375,21 +10375,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10399,10 +10399,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497137</v>
+        <v>497117</v>
       </c>
       <c r="R94" t="n">
-        <v>6830325</v>
+        <v>6830376</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11168,10 +11168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256286</v>
+        <v>130256292</v>
       </c>
       <c r="B102" t="n">
-        <v>78969</v>
+        <v>78968</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497251</v>
+        <v>497168</v>
       </c>
       <c r="R102" t="n">
-        <v>6830494</v>
+        <v>6830310</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11275,10 +11275,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256292</v>
+        <v>130256312</v>
       </c>
       <c r="B103" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497168</v>
+        <v>497244</v>
       </c>
       <c r="R103" t="n">
-        <v>6830310</v>
+        <v>6830538</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11382,10 +11382,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256312</v>
+        <v>130256286</v>
       </c>
       <c r="B104" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11393,21 +11393,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497244</v>
+        <v>497251</v>
       </c>
       <c r="R104" t="n">
-        <v>6830538</v>
+        <v>6830494</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -5541,10 +5541,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130256297</v>
+        <v>130256288</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497115</v>
+        <v>497067</v>
       </c>
       <c r="R47" t="n">
-        <v>6830196</v>
+        <v>6830217</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5648,10 +5648,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130257279</v>
+        <v>130256297</v>
       </c>
       <c r="B48" t="n">
-        <v>79211</v>
+        <v>78976</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5659,21 +5659,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497320</v>
+        <v>497115</v>
       </c>
       <c r="R48" t="n">
-        <v>6830386</v>
+        <v>6830196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5716,9 +5716,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5733,22 +5743,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130256288</v>
+        <v>130257279</v>
       </c>
       <c r="B49" t="n">
-        <v>78969</v>
+        <v>79219</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5756,21 +5766,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5780,10 +5790,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497067</v>
+        <v>497320</v>
       </c>
       <c r="R49" t="n">
-        <v>6830217</v>
+        <v>6830386</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5813,19 +5823,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5840,22 +5840,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130257265</v>
+        <v>130257271</v>
       </c>
       <c r="B50" t="n">
-        <v>91782</v>
+        <v>78976</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5863,21 +5863,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497131</v>
+        <v>497270</v>
       </c>
       <c r="R50" t="n">
-        <v>6830311</v>
+        <v>6830422</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130257295</v>
+        <v>130257276</v>
       </c>
       <c r="B51" t="n">
-        <v>78218</v>
+        <v>78976</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497072</v>
+        <v>497082</v>
       </c>
       <c r="R51" t="n">
-        <v>6830261</v>
+        <v>6830202</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130257276</v>
+        <v>130257265</v>
       </c>
       <c r="B52" t="n">
-        <v>78968</v>
+        <v>91795</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6057,21 +6057,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497082</v>
+        <v>497131</v>
       </c>
       <c r="R52" t="n">
-        <v>6830202</v>
+        <v>6830311</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130257271</v>
+        <v>130257295</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>78226</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497270</v>
+        <v>497072</v>
       </c>
       <c r="R53" t="n">
-        <v>6830422</v>
+        <v>6830261</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130257280</v>
+        <v>130257291</v>
       </c>
       <c r="B54" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497302</v>
+        <v>497164</v>
       </c>
       <c r="R54" t="n">
-        <v>6830384</v>
+        <v>6830343</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130257291</v>
+        <v>130257280</v>
       </c>
       <c r="B55" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497164</v>
+        <v>497302</v>
       </c>
       <c r="R55" t="n">
-        <v>6830343</v>
+        <v>6830384</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6437,7 +6437,7 @@
         <v>130257277</v>
       </c>
       <c r="B56" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>130256299</v>
       </c>
       <c r="B57" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>130257284</v>
       </c>
       <c r="B58" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>130256311</v>
       </c>
       <c r="B59" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>130257278</v>
       </c>
       <c r="B60" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>130256307</v>
       </c>
       <c r="B61" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7046,10 +7046,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130257262</v>
+        <v>130257287</v>
       </c>
       <c r="B62" t="n">
-        <v>79830</v>
+        <v>79219</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7057,21 +7057,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7081,10 +7081,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497128</v>
+        <v>497234</v>
       </c>
       <c r="R62" t="n">
-        <v>6830348</v>
+        <v>6830313</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7143,10 +7143,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130256304</v>
+        <v>130256309</v>
       </c>
       <c r="B63" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497247</v>
+        <v>497156</v>
       </c>
       <c r="R63" t="n">
-        <v>6830499</v>
+        <v>6830327</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7250,10 +7250,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130256309</v>
+        <v>130256304</v>
       </c>
       <c r="B64" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497156</v>
+        <v>497247</v>
       </c>
       <c r="R64" t="n">
-        <v>6830327</v>
+        <v>6830499</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7357,10 +7357,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130257287</v>
+        <v>130257297</v>
       </c>
       <c r="B65" t="n">
-        <v>79211</v>
+        <v>78622</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7368,21 +7368,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497234</v>
+        <v>497072</v>
       </c>
       <c r="R65" t="n">
-        <v>6830313</v>
+        <v>6830261</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7454,10 +7454,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130257297</v>
+        <v>130257262</v>
       </c>
       <c r="B66" t="n">
-        <v>78614</v>
+        <v>79838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7465,21 +7465,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497072</v>
+        <v>497128</v>
       </c>
       <c r="R66" t="n">
-        <v>6830261</v>
+        <v>6830348</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7551,32 +7551,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130257281</v>
+        <v>130257293</v>
       </c>
       <c r="B67" t="n">
-        <v>79211</v>
+        <v>93060</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497275</v>
+        <v>497087</v>
       </c>
       <c r="R67" t="n">
-        <v>6830388</v>
+        <v>6830238</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7648,10 +7648,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130256291</v>
+        <v>130257281</v>
       </c>
       <c r="B68" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7659,21 +7659,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497251</v>
+        <v>497275</v>
       </c>
       <c r="R68" t="n">
-        <v>6830491</v>
+        <v>6830388</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7716,19 +7716,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7743,44 +7733,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130257293</v>
+        <v>130256291</v>
       </c>
       <c r="B69" t="n">
-        <v>93047</v>
+        <v>78976</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7790,10 +7780,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497087</v>
+        <v>497251</v>
       </c>
       <c r="R69" t="n">
-        <v>6830238</v>
+        <v>6830491</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7823,9 +7813,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7840,12 +7840,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7962,7 +7962,7 @@
         <v>130256314</v>
       </c>
       <c r="B71" t="n">
-        <v>93047</v>
+        <v>93060</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8078,10 +8078,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130256303</v>
+        <v>130257263</v>
       </c>
       <c r="B72" t="n">
-        <v>79211</v>
+        <v>79809</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,21 +8089,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497291</v>
+        <v>497069</v>
       </c>
       <c r="R72" t="n">
-        <v>6830488</v>
+        <v>6830264</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8146,19 +8146,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8173,22 +8163,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130257263</v>
+        <v>130256303</v>
       </c>
       <c r="B73" t="n">
-        <v>79801</v>
+        <v>79219</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8196,21 +8186,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8220,10 +8210,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497069</v>
+        <v>497291</v>
       </c>
       <c r="R73" t="n">
-        <v>6830264</v>
+        <v>6830488</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8253,9 +8243,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8270,68 +8270,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130256313</v>
+        <v>130257275</v>
       </c>
       <c r="B74" t="n">
-        <v>93047</v>
+        <v>78976</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497260</v>
+        <v>497096</v>
       </c>
       <c r="R74" t="n">
-        <v>6830540</v>
+        <v>6830218</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8361,40 +8350,29 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8404,7 +8382,7 @@
         <v>130256306</v>
       </c>
       <c r="B75" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8508,45 +8486,56 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130257275</v>
+        <v>130256313</v>
       </c>
       <c r="B76" t="n">
-        <v>78968</v>
+        <v>93060</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497096</v>
+        <v>497260</v>
       </c>
       <c r="R76" t="n">
-        <v>6830218</v>
+        <v>6830540</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8576,39 +8565,50 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130257282</v>
+        <v>130257285</v>
       </c>
       <c r="B77" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497252</v>
+        <v>497250</v>
       </c>
       <c r="R77" t="n">
-        <v>6830372</v>
+        <v>6830356</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8702,10 +8702,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130257285</v>
+        <v>130257292</v>
       </c>
       <c r="B78" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8737,10 +8737,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497250</v>
+        <v>497138</v>
       </c>
       <c r="R78" t="n">
-        <v>6830356</v>
+        <v>6830320</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8799,10 +8799,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130257292</v>
+        <v>130257282</v>
       </c>
       <c r="B79" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497138</v>
+        <v>497252</v>
       </c>
       <c r="R79" t="n">
-        <v>6830320</v>
+        <v>6830372</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8899,7 +8899,7 @@
         <v>130256310</v>
       </c>
       <c r="B80" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>130256301</v>
       </c>
       <c r="B81" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9110,10 +9110,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130257289</v>
+        <v>130256302</v>
       </c>
       <c r="B82" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497222</v>
+        <v>497273</v>
       </c>
       <c r="R82" t="n">
-        <v>6830325</v>
+        <v>6830394</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9178,9 +9178,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9195,22 +9205,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130256302</v>
+        <v>130257289</v>
       </c>
       <c r="B83" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9242,10 +9252,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497273</v>
+        <v>497222</v>
       </c>
       <c r="R83" t="n">
-        <v>6830394</v>
+        <v>6830325</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9275,19 +9285,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9302,22 +9302,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130257266</v>
+        <v>130257261</v>
       </c>
       <c r="B84" t="n">
-        <v>57854</v>
+        <v>79838</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9325,42 +9325,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497142</v>
+        <v>497107</v>
       </c>
       <c r="R84" t="n">
-        <v>6830327</v>
+        <v>6830221</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9419,10 +9411,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130257261</v>
+        <v>130257266</v>
       </c>
       <c r="B85" t="n">
-        <v>79830</v>
+        <v>57862</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9430,34 +9422,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497107</v>
+        <v>497142</v>
       </c>
       <c r="R85" t="n">
-        <v>6830221</v>
+        <v>6830327</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9516,10 +9516,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130257274</v>
+        <v>130257268</v>
       </c>
       <c r="B86" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9527,21 +9527,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9551,10 +9551,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497107</v>
+        <v>497074</v>
       </c>
       <c r="R86" t="n">
-        <v>6830221</v>
+        <v>6830292</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9613,54 +9613,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130256289</v>
+        <v>130257283</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497101</v>
+        <v>497244</v>
       </c>
       <c r="R87" t="n">
-        <v>6830183</v>
+        <v>6830388</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9690,96 +9681,74 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130256315</v>
+        <v>130257274</v>
       </c>
       <c r="B88" t="n">
-        <v>93047</v>
+        <v>78976</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497261</v>
+        <v>497107</v>
       </c>
       <c r="R88" t="n">
-        <v>6830529</v>
+        <v>6830221</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9809,85 +9778,85 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130257268</v>
+        <v>130256315</v>
       </c>
       <c r="B89" t="n">
-        <v>79211</v>
+        <v>93060</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497074</v>
+        <v>497261</v>
       </c>
       <c r="R89" t="n">
-        <v>6830292</v>
+        <v>6830529</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9917,74 +9886,94 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130257283</v>
+        <v>130256289</v>
       </c>
       <c r="B90" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497244</v>
+        <v>497101</v>
       </c>
       <c r="R90" t="n">
-        <v>6830388</v>
+        <v>6830183</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10014,39 +10003,50 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130256300</v>
+        <v>130256293</v>
       </c>
       <c r="B91" t="n">
-        <v>79211</v>
+        <v>78976</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10054,21 +10054,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497391</v>
+        <v>497117</v>
       </c>
       <c r="R91" t="n">
-        <v>6830230</v>
+        <v>6830376</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10153,7 +10153,7 @@
         <v>130256305</v>
       </c>
       <c r="B92" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>130256308</v>
       </c>
       <c r="B93" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10364,10 +10364,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130256293</v>
+        <v>130256300</v>
       </c>
       <c r="B94" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10375,21 +10375,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10399,10 +10399,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497117</v>
+        <v>497391</v>
       </c>
       <c r="R94" t="n">
-        <v>6830376</v>
+        <v>6830230</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10471,10 +10471,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130257272</v>
+        <v>130257288</v>
       </c>
       <c r="B95" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10482,21 +10482,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497128</v>
+        <v>497224</v>
       </c>
       <c r="R95" t="n">
-        <v>6830345</v>
+        <v>6830319</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10568,10 +10568,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130257288</v>
+        <v>130257272</v>
       </c>
       <c r="B96" t="n">
-        <v>79211</v>
+        <v>78976</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10579,21 +10579,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497224</v>
+        <v>497128</v>
       </c>
       <c r="R96" t="n">
-        <v>6830319</v>
+        <v>6830345</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10668,7 +10668,7 @@
         <v>130257269</v>
       </c>
       <c r="B97" t="n">
-        <v>57047</v>
+        <v>57055</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10770,10 +10770,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130256296</v>
+        <v>130257286</v>
       </c>
       <c r="B98" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10781,21 +10781,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10805,10 +10805,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497074</v>
+        <v>497240</v>
       </c>
       <c r="R98" t="n">
-        <v>6830224</v>
+        <v>6830306</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10838,19 +10838,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>09:40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10865,22 +10855,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130257294</v>
+        <v>130256296</v>
       </c>
       <c r="B99" t="n">
-        <v>78218</v>
+        <v>78976</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10888,21 +10878,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10912,10 +10902,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497072</v>
+        <v>497074</v>
       </c>
       <c r="R99" t="n">
-        <v>6830282</v>
+        <v>6830224</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10945,9 +10935,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10962,12 +10962,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10977,7 +10977,7 @@
         <v>130257290</v>
       </c>
       <c r="B100" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130257286</v>
+        <v>130257294</v>
       </c>
       <c r="B101" t="n">
-        <v>79211</v>
+        <v>78226</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11082,21 +11082,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497240</v>
+        <v>497072</v>
       </c>
       <c r="R101" t="n">
-        <v>6830306</v>
+        <v>6830282</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11168,10 +11168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256292</v>
+        <v>130256286</v>
       </c>
       <c r="B102" t="n">
-        <v>78968</v>
+        <v>78977</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497168</v>
+        <v>497251</v>
       </c>
       <c r="R102" t="n">
-        <v>6830310</v>
+        <v>6830494</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11278,7 +11278,7 @@
         <v>130256312</v>
       </c>
       <c r="B103" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11382,10 +11382,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256286</v>
+        <v>130256292</v>
       </c>
       <c r="B104" t="n">
-        <v>78969</v>
+        <v>78976</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11393,21 +11393,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497251</v>
+        <v>497168</v>
       </c>
       <c r="R104" t="n">
-        <v>6830494</v>
+        <v>6830310</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY104"/>
+  <dimension ref="A1:AY106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130252273</v>
+        <v>130252271</v>
       </c>
       <c r="B2" t="n">
-        <v>93047</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497114</v>
+        <v>497241</v>
       </c>
       <c r="R2" t="n">
-        <v>6830195</v>
+        <v>6830507</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252255</v>
+        <v>130252272</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497263</v>
+        <v>497084</v>
       </c>
       <c r="R3" t="n">
-        <v>6830449</v>
+        <v>6830218</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252694</v>
+        <v>130252273</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497321</v>
+        <v>497114</v>
       </c>
       <c r="R4" t="n">
-        <v>6830343</v>
+        <v>6830195</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252270</v>
+        <v>130252697</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497118</v>
+        <v>497086</v>
       </c>
       <c r="R5" t="n">
-        <v>6830323</v>
+        <v>6830210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,50 +1085,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252256</v>
+        <v>130252698</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497168</v>
+        <v>497112</v>
       </c>
       <c r="R6" t="n">
-        <v>6830390</v>
+        <v>6830192</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1174,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1184,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,32 +1193,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252271</v>
+        <v>130256313</v>
       </c>
       <c r="B7" t="n">
-        <v>93047</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1238,17 +1240,28 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497241</v>
+        <v>497260</v>
       </c>
       <c r="R7" t="n">
-        <v>6830507</v>
+        <v>6830540</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,28 +1312,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130252262</v>
+        <v>130256314</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1342,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497260</v>
+        <v>497242</v>
       </c>
       <c r="R8" t="n">
-        <v>6830494</v>
+        <v>6830510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,22 +1438,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252259</v>
+        <v>130256315</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1436,34 +1461,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497236</v>
+        <v>497261</v>
       </c>
       <c r="R9" t="n">
-        <v>6830502</v>
+        <v>6830529</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1531,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1541,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,28 +1550,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130252269</v>
+        <v>130257293</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1543,21 +1580,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497128</v>
+        <v>497087</v>
       </c>
       <c r="R10" t="n">
-        <v>6830401</v>
+        <v>6830238</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,19 +1637,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,22 +1654,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252251</v>
+        <v>130257265</v>
       </c>
       <c r="B11" t="n">
-        <v>58013</v>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,42 +1677,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497063</v>
+        <v>497131</v>
       </c>
       <c r="R11" t="n">
-        <v>6830279</v>
+        <v>6830311</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,19 +1734,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,26 +1751,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252695</v>
+        <v>130252263</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1783,16 +1792,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497166</v>
+        <v>497344</v>
       </c>
       <c r="R12" t="n">
-        <v>6830368</v>
+        <v>6830116</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1836,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1834,7 +1846,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,50 +1860,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252244</v>
+        <v>130252264</v>
       </c>
       <c r="B13" t="n">
-        <v>79830</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497260</v>
+        <v>497334</v>
       </c>
       <c r="R13" t="n">
-        <v>6830494</v>
+        <v>6830124</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1949,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1959,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,32 +1986,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252258</v>
+        <v>130252265</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2003,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497245</v>
+        <v>497328</v>
       </c>
       <c r="R14" t="n">
-        <v>6830449</v>
+        <v>6830125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2056,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2066,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,32 +2093,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252245</v>
+        <v>130252266</v>
       </c>
       <c r="B15" t="n">
-        <v>79830</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497169</v>
+        <v>497268</v>
       </c>
       <c r="R15" t="n">
-        <v>6830390</v>
+        <v>6830469</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2163,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2173,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,32 +2200,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252688</v>
+        <v>130252267</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497300</v>
+        <v>497178</v>
       </c>
       <c r="R16" t="n">
-        <v>6830438</v>
+        <v>6830332</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2270,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2280,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,44 +2295,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252257</v>
+        <v>130252268</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497076</v>
+        <v>497175</v>
       </c>
       <c r="R17" t="n">
-        <v>6830213</v>
+        <v>6830390</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2377,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2387,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,32 +2414,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252261</v>
+        <v>130252269</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497167</v>
+        <v>497128</v>
       </c>
       <c r="R18" t="n">
-        <v>6830200</v>
+        <v>6830401</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2484,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2494,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,32 +2521,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252693</v>
+        <v>130252270</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497066</v>
+        <v>497118</v>
       </c>
       <c r="R19" t="n">
-        <v>6830179</v>
+        <v>6830323</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2591,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2601,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,44 +2616,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252252</v>
+        <v>130252694</v>
       </c>
       <c r="B20" t="n">
-        <v>78969</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497077</v>
+        <v>497321</v>
       </c>
       <c r="R20" t="n">
-        <v>6830219</v>
+        <v>6830343</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2699,51 +2717,50 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252272</v>
+        <v>130252695</v>
       </c>
       <c r="B21" t="n">
-        <v>93047</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2770,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497084</v>
+        <v>497166</v>
       </c>
       <c r="R21" t="n">
-        <v>6830218</v>
+        <v>6830368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,12 +2830,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2828,11 +2845,11 @@
         <v>130252696</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2932,14 +2949,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252264</v>
+        <v>130256299</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2967,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497334</v>
+        <v>497390</v>
       </c>
       <c r="R23" t="n">
-        <v>6830124</v>
+        <v>6830226</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3019,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3029,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,44 +3044,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252691</v>
+        <v>130256300</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497108</v>
+        <v>497391</v>
       </c>
       <c r="R24" t="n">
-        <v>6830371</v>
+        <v>6830230</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3126,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3136,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,26 +3151,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130252267</v>
+        <v>130256301</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3181,10 +3198,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497178</v>
+        <v>497384</v>
       </c>
       <c r="R25" t="n">
-        <v>6830332</v>
+        <v>6830217</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3233,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3243,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,44 +3258,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252698</v>
+        <v>130256302</v>
       </c>
       <c r="B26" t="n">
-        <v>93047</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3305,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497112</v>
+        <v>497273</v>
       </c>
       <c r="R26" t="n">
-        <v>6830192</v>
+        <v>6830394</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3340,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3350,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,51 +3359,50 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130252685</v>
+        <v>130256303</v>
       </c>
       <c r="B27" t="n">
-        <v>78969</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3396,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497071</v>
+        <v>497291</v>
       </c>
       <c r="R27" t="n">
-        <v>6830207</v>
+        <v>6830488</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,7 +3447,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3441,7 +3457,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3456,44 +3472,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252684</v>
+        <v>130256304</v>
       </c>
       <c r="B28" t="n">
-        <v>78969</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3519,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497063</v>
+        <v>497247</v>
       </c>
       <c r="R28" t="n">
-        <v>6830346</v>
+        <v>6830499</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,7 +3554,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3548,7 +3564,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,44 +3579,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252253</v>
+        <v>130256305</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3610,10 +3626,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497334</v>
+        <v>497258</v>
       </c>
       <c r="R29" t="n">
-        <v>6830121</v>
+        <v>6830560</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,7 +3661,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3655,7 +3671,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3670,26 +3686,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252268</v>
+        <v>130256306</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3717,10 +3733,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497175</v>
+        <v>497253</v>
       </c>
       <c r="R30" t="n">
-        <v>6830390</v>
+        <v>6830351</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,7 +3768,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3762,7 +3778,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,44 +3793,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252689</v>
+        <v>130256307</v>
       </c>
       <c r="B31" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3824,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497261</v>
+        <v>497221</v>
       </c>
       <c r="R31" t="n">
-        <v>6830425</v>
+        <v>6830314</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3859,7 +3875,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3869,7 +3885,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3884,26 +3900,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252265</v>
+        <v>130256308</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3931,10 +3947,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497328</v>
+        <v>497137</v>
       </c>
       <c r="R32" t="n">
-        <v>6830125</v>
+        <v>6830325</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3966,7 +3982,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3976,7 +3992,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3991,44 +4007,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130252687</v>
+        <v>130256309</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4038,10 +4054,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497050</v>
+        <v>497156</v>
       </c>
       <c r="R33" t="n">
-        <v>6830313</v>
+        <v>6830327</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4073,7 +4089,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4083,7 +4099,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4098,44 +4114,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252697</v>
+        <v>130256310</v>
       </c>
       <c r="B34" t="n">
-        <v>93047</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4145,10 +4161,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497086</v>
+        <v>497160</v>
       </c>
       <c r="R34" t="n">
-        <v>6830210</v>
+        <v>6830342</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4180,7 +4196,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4190,7 +4206,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4199,51 +4215,50 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130252682</v>
+        <v>130256311</v>
       </c>
       <c r="B35" t="n">
-        <v>78969</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497144</v>
+        <v>497159</v>
       </c>
       <c r="R35" t="n">
-        <v>6830357</v>
+        <v>6830345</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4288,7 +4303,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4298,7 +4313,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,44 +4328,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130252692</v>
+        <v>130256312</v>
       </c>
       <c r="B36" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4360,10 +4375,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497090</v>
+        <v>497244</v>
       </c>
       <c r="R36" t="n">
-        <v>6830366</v>
+        <v>6830538</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4395,7 +4410,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4405,7 +4420,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,44 +4435,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130252246</v>
+        <v>130257268</v>
       </c>
       <c r="B37" t="n">
-        <v>79801</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4467,10 +4482,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497268</v>
+        <v>497074</v>
       </c>
       <c r="R37" t="n">
-        <v>6830458</v>
+        <v>6830292</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4500,19 +4515,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,26 +4532,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252263</v>
+        <v>130257278</v>
       </c>
       <c r="B38" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4568,19 +4573,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497344</v>
+        <v>497327</v>
       </c>
       <c r="R38" t="n">
-        <v>6830116</v>
+        <v>6830133</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,77 +4612,61 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130252260</v>
+        <v>130257279</v>
       </c>
       <c r="B39" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4690,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497077</v>
+        <v>497320</v>
       </c>
       <c r="R39" t="n">
-        <v>6830219</v>
+        <v>6830386</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4723,19 +4709,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4750,44 +4726,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252683</v>
+        <v>130257280</v>
       </c>
       <c r="B40" t="n">
-        <v>78969</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4797,10 +4773,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497089</v>
+        <v>497302</v>
       </c>
       <c r="R40" t="n">
-        <v>6830358</v>
+        <v>6830384</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,19 +4806,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4857,69 +4823,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252250</v>
+        <v>130257281</v>
       </c>
       <c r="B41" t="n">
-        <v>58013</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497113</v>
+        <v>497275</v>
       </c>
       <c r="R41" t="n">
-        <v>6830338</v>
+        <v>6830388</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4949,24 +4903,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Var i ett meståg med bla. trädkrypare</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4981,26 +4920,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130252266</v>
+        <v>130257282</v>
       </c>
       <c r="B42" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5028,10 +4967,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497268</v>
+        <v>497252</v>
       </c>
       <c r="R42" t="n">
-        <v>6830469</v>
+        <v>6830372</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5061,19 +5000,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5088,44 +5017,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252690</v>
+        <v>130257283</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5135,10 +5064,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497163</v>
+        <v>497244</v>
       </c>
       <c r="R43" t="n">
-        <v>6830392</v>
+        <v>6830388</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5168,19 +5097,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,65 +5114,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252248</v>
+        <v>130257284</v>
       </c>
       <c r="B44" t="n">
-        <v>57044</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497253</v>
+        <v>497256</v>
       </c>
       <c r="R44" t="n">
-        <v>6830469</v>
+        <v>6830376</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5283,24 +5194,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5315,44 +5211,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252254</v>
+        <v>130257285</v>
       </c>
       <c r="B45" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5362,10 +5258,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497253</v>
+        <v>497250</v>
       </c>
       <c r="R45" t="n">
-        <v>6830488</v>
+        <v>6830356</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5395,19 +5291,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5422,44 +5308,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252686</v>
+        <v>130257286</v>
       </c>
       <c r="B46" t="n">
-        <v>78969</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5469,10 +5355,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497085</v>
+        <v>497240</v>
       </c>
       <c r="R46" t="n">
-        <v>6830215</v>
+        <v>6830306</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5502,19 +5388,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5529,44 +5405,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130256288</v>
+        <v>130257287</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5576,10 +5452,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497067</v>
+        <v>497234</v>
       </c>
       <c r="R47" t="n">
-        <v>6830217</v>
+        <v>6830313</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5609,19 +5485,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5636,44 +5502,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130256297</v>
+        <v>130257288</v>
       </c>
       <c r="B48" t="n">
-        <v>78976</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5683,10 +5549,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497115</v>
+        <v>497224</v>
       </c>
       <c r="R48" t="n">
-        <v>6830196</v>
+        <v>6830319</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5716,19 +5582,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5743,26 +5599,26 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130257279</v>
+        <v>130257289</v>
       </c>
       <c r="B49" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5790,10 +5646,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497320</v>
+        <v>497222</v>
       </c>
       <c r="R49" t="n">
-        <v>6830386</v>
+        <v>6830325</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5852,32 +5708,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130257271</v>
+        <v>130257290</v>
       </c>
       <c r="B50" t="n">
-        <v>78976</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5743,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497270</v>
+        <v>497200</v>
       </c>
       <c r="R50" t="n">
-        <v>6830422</v>
+        <v>6830326</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,32 +5805,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130257276</v>
+        <v>130257291</v>
       </c>
       <c r="B51" t="n">
-        <v>78976</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5984,10 +5840,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497082</v>
+        <v>497164</v>
       </c>
       <c r="R51" t="n">
-        <v>6830202</v>
+        <v>6830343</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6046,32 +5902,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130257265</v>
+        <v>130257292</v>
       </c>
       <c r="B52" t="n">
-        <v>91795</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6081,10 +5937,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497131</v>
+        <v>497138</v>
       </c>
       <c r="R52" t="n">
-        <v>6830311</v>
+        <v>6830320</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,10 +5999,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130257295</v>
+        <v>130257297</v>
       </c>
       <c r="B53" t="n">
-        <v>78226</v>
+        <v>78730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6154,21 +6010,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6240,10 +6096,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130257291</v>
+        <v>130252258</v>
       </c>
       <c r="B54" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6251,21 +6107,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6275,10 +6131,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497164</v>
+        <v>497245</v>
       </c>
       <c r="R54" t="n">
-        <v>6830343</v>
+        <v>6830449</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6308,9 +6164,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6325,22 +6191,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130257280</v>
+        <v>130252259</v>
       </c>
       <c r="B55" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6348,21 +6214,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6372,10 +6238,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497302</v>
+        <v>497236</v>
       </c>
       <c r="R55" t="n">
-        <v>6830384</v>
+        <v>6830502</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6405,9 +6271,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6422,22 +6298,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130257277</v>
+        <v>130252260</v>
       </c>
       <c r="B56" t="n">
-        <v>78976</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6469,10 +6345,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497092</v>
+        <v>497077</v>
       </c>
       <c r="R56" t="n">
-        <v>6830180</v>
+        <v>6830219</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6502,9 +6378,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6519,22 +6405,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130256299</v>
+        <v>130252261</v>
       </c>
       <c r="B57" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6542,21 +6428,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6566,10 +6452,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497390</v>
+        <v>497167</v>
       </c>
       <c r="R57" t="n">
-        <v>6830226</v>
+        <v>6830200</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6601,7 +6487,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6611,7 +6497,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6626,22 +6512,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130257284</v>
+        <v>130252262</v>
       </c>
       <c r="B58" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6649,21 +6535,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6673,10 +6559,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497256</v>
+        <v>497260</v>
       </c>
       <c r="R58" t="n">
-        <v>6830376</v>
+        <v>6830494</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6706,39 +6592,50 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130256311</v>
+        <v>130252688</v>
       </c>
       <c r="B59" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6746,21 +6643,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6770,10 +6667,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497159</v>
+        <v>497300</v>
       </c>
       <c r="R59" t="n">
-        <v>6830345</v>
+        <v>6830438</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6805,7 +6702,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6815,7 +6712,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6830,22 +6727,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130257278</v>
+        <v>130252689</v>
       </c>
       <c r="B60" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6853,21 +6750,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6877,10 +6774,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497327</v>
+        <v>497261</v>
       </c>
       <c r="R60" t="n">
-        <v>6830133</v>
+        <v>6830425</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6910,9 +6807,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6927,22 +6834,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130256307</v>
+        <v>130252690</v>
       </c>
       <c r="B61" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6950,21 +6857,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6974,10 +6881,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497221</v>
+        <v>497163</v>
       </c>
       <c r="R61" t="n">
-        <v>6830314</v>
+        <v>6830392</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7009,7 +6916,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7019,7 +6926,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7034,22 +6941,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130257287</v>
+        <v>130252691</v>
       </c>
       <c r="B62" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7057,21 +6964,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7081,10 +6988,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497234</v>
+        <v>497108</v>
       </c>
       <c r="R62" t="n">
-        <v>6830313</v>
+        <v>6830371</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7114,9 +7021,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7131,22 +7048,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130256309</v>
+        <v>130252692</v>
       </c>
       <c r="B63" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7154,21 +7071,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7178,10 +7095,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497156</v>
+        <v>497090</v>
       </c>
       <c r="R63" t="n">
-        <v>6830327</v>
+        <v>6830366</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7213,7 +7130,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7223,7 +7140,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7238,22 +7155,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130256304</v>
+        <v>130252693</v>
       </c>
       <c r="B64" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7261,21 +7178,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7285,10 +7202,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497247</v>
+        <v>497066</v>
       </c>
       <c r="R64" t="n">
-        <v>6830499</v>
+        <v>6830179</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7320,7 +7237,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7330,7 +7247,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7345,22 +7262,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130257297</v>
+        <v>130256291</v>
       </c>
       <c r="B65" t="n">
-        <v>78622</v>
+        <v>79084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7368,21 +7285,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7392,10 +7309,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497072</v>
+        <v>497251</v>
       </c>
       <c r="R65" t="n">
-        <v>6830261</v>
+        <v>6830491</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7425,9 +7342,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7442,22 +7369,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130257262</v>
+        <v>130256292</v>
       </c>
       <c r="B66" t="n">
-        <v>79838</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7465,21 +7392,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7489,10 +7416,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497128</v>
+        <v>497168</v>
       </c>
       <c r="R66" t="n">
-        <v>6830348</v>
+        <v>6830310</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7522,9 +7449,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7539,44 +7476,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130257293</v>
+        <v>130256293</v>
       </c>
       <c r="B67" t="n">
-        <v>93060</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7586,10 +7523,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497087</v>
+        <v>497117</v>
       </c>
       <c r="R67" t="n">
-        <v>6830238</v>
+        <v>6830376</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7619,9 +7556,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7636,22 +7583,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130257281</v>
+        <v>130256295</v>
       </c>
       <c r="B68" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7659,21 +7606,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7683,10 +7630,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497275</v>
+        <v>497019</v>
       </c>
       <c r="R68" t="n">
-        <v>6830388</v>
+        <v>6830205</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7716,9 +7663,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7733,22 +7690,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130256291</v>
+        <v>130256296</v>
       </c>
       <c r="B69" t="n">
-        <v>78976</v>
+        <v>79084</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7780,10 +7737,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497251</v>
+        <v>497074</v>
       </c>
       <c r="R69" t="n">
-        <v>6830491</v>
+        <v>6830224</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7815,7 +7772,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7825,7 +7782,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7852,54 +7809,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130257270</v>
+        <v>130256297</v>
       </c>
       <c r="B70" t="n">
-        <v>8451</v>
+        <v>79084</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497113</v>
+        <v>497115</v>
       </c>
       <c r="R70" t="n">
-        <v>6830234</v>
+        <v>6830196</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7929,86 +7877,84 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256314</v>
+        <v>130257271</v>
       </c>
       <c r="B71" t="n">
-        <v>93060</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497242</v>
+        <v>497270</v>
       </c>
       <c r="R71" t="n">
-        <v>6830510</v>
+        <v>6830422</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8038,50 +7984,39 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130257263</v>
+        <v>130257272</v>
       </c>
       <c r="B72" t="n">
-        <v>79809</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,21 +8024,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8113,10 +8048,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497069</v>
+        <v>497128</v>
       </c>
       <c r="R72" t="n">
-        <v>6830264</v>
+        <v>6830345</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8175,10 +8110,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130256303</v>
+        <v>130257274</v>
       </c>
       <c r="B73" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8186,21 +8121,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8210,10 +8145,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497291</v>
+        <v>497107</v>
       </c>
       <c r="R73" t="n">
-        <v>6830488</v>
+        <v>6830221</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8243,19 +8178,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8270,12 +8195,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8285,7 +8210,7 @@
         <v>130257275</v>
       </c>
       <c r="B74" t="n">
-        <v>78976</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8379,10 +8304,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130256306</v>
+        <v>130257276</v>
       </c>
       <c r="B75" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8390,21 +8315,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8414,10 +8339,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497253</v>
+        <v>497082</v>
       </c>
       <c r="R75" t="n">
-        <v>6830351</v>
+        <v>6830202</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8447,19 +8372,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8474,68 +8389,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130256313</v>
+        <v>130257277</v>
       </c>
       <c r="B76" t="n">
-        <v>93060</v>
+        <v>79084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497260</v>
+        <v>497092</v>
       </c>
       <c r="R76" t="n">
-        <v>6830540</v>
+        <v>6830180</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8565,50 +8469,39 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130257285</v>
+        <v>130252244</v>
       </c>
       <c r="B77" t="n">
-        <v>79219</v>
+        <v>79946</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8616,21 +8509,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8640,10 +8533,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497250</v>
+        <v>497260</v>
       </c>
       <c r="R77" t="n">
-        <v>6830356</v>
+        <v>6830494</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8673,9 +8566,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8690,22 +8593,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130257292</v>
+        <v>130252245</v>
       </c>
       <c r="B78" t="n">
-        <v>79219</v>
+        <v>79946</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8713,21 +8616,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8737,10 +8640,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497138</v>
+        <v>497169</v>
       </c>
       <c r="R78" t="n">
-        <v>6830320</v>
+        <v>6830390</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8770,9 +8673,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8787,22 +8700,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130257282</v>
+        <v>130257261</v>
       </c>
       <c r="B79" t="n">
-        <v>79219</v>
+        <v>79946</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8810,21 +8723,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8834,10 +8747,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497252</v>
+        <v>497107</v>
       </c>
       <c r="R79" t="n">
-        <v>6830372</v>
+        <v>6830221</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8896,10 +8809,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130256310</v>
+        <v>130257262</v>
       </c>
       <c r="B80" t="n">
-        <v>79219</v>
+        <v>79946</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8907,21 +8820,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8931,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497160</v>
+        <v>497128</v>
       </c>
       <c r="R80" t="n">
-        <v>6830342</v>
+        <v>6830348</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8964,19 +8877,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8991,22 +8894,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130256301</v>
+        <v>130257294</v>
       </c>
       <c r="B81" t="n">
-        <v>79219</v>
+        <v>78334</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9014,21 +8917,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9038,10 +8941,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497384</v>
+        <v>497072</v>
       </c>
       <c r="R81" t="n">
-        <v>6830217</v>
+        <v>6830282</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9071,19 +8974,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9098,22 +8991,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130256302</v>
+        <v>130257295</v>
       </c>
       <c r="B82" t="n">
-        <v>79219</v>
+        <v>78334</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9121,21 +9014,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9145,10 +9038,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497273</v>
+        <v>497072</v>
       </c>
       <c r="R82" t="n">
-        <v>6830394</v>
+        <v>6830261</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9178,19 +9071,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9205,22 +9088,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130257289</v>
+        <v>130257266</v>
       </c>
       <c r="B83" t="n">
-        <v>79219</v>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9228,34 +9111,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497222</v>
+        <v>497142</v>
       </c>
       <c r="R83" t="n">
-        <v>6830325</v>
+        <v>6830327</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9314,45 +9205,53 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130257261</v>
+        <v>130252248</v>
       </c>
       <c r="B84" t="n">
-        <v>79838</v>
+        <v>57141</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497107</v>
+        <v>497253</v>
       </c>
       <c r="R84" t="n">
-        <v>6830221</v>
+        <v>6830469</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9382,9 +9281,24 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9399,39 +9313,39 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130257266</v>
+        <v>130257269</v>
       </c>
       <c r="B85" t="n">
-        <v>57862</v>
+        <v>57144</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9444,7 +9358,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -9454,10 +9368,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497142</v>
+        <v>497271</v>
       </c>
       <c r="R85" t="n">
-        <v>6830327</v>
+        <v>6830418</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9516,10 +9430,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130257268</v>
+        <v>130252250</v>
       </c>
       <c r="B86" t="n">
-        <v>79219</v>
+        <v>58114</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9527,34 +9441,46 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497074</v>
+        <v>497113</v>
       </c>
       <c r="R86" t="n">
-        <v>6830292</v>
+        <v>6830338</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9584,9 +9510,24 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Var i ett meståg med bla. trädkrypare</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9601,22 +9542,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130257283</v>
+        <v>130252251</v>
       </c>
       <c r="B87" t="n">
-        <v>79219</v>
+        <v>58114</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9624,34 +9565,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497244</v>
+        <v>497063</v>
       </c>
       <c r="R87" t="n">
-        <v>6830388</v>
+        <v>6830279</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9681,9 +9630,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9698,44 +9657,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130257274</v>
+        <v>130252253</v>
       </c>
       <c r="B88" t="n">
-        <v>78976</v>
+        <v>8455</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9745,10 +9704,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497107</v>
+        <v>497334</v>
       </c>
       <c r="R88" t="n">
-        <v>6830221</v>
+        <v>6830121</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9778,9 +9737,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9795,22 +9764,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130256315</v>
+        <v>130252254</v>
       </c>
       <c r="B89" t="n">
-        <v>93060</v>
+        <v>8455</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9818,45 +9787,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497261</v>
+        <v>497253</v>
       </c>
       <c r="R89" t="n">
-        <v>6830529</v>
+        <v>6830488</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9888,7 +9846,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9898,7 +9856,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9907,29 +9865,28 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130256289</v>
+        <v>130252255</v>
       </c>
       <c r="B90" t="n">
-        <v>8451</v>
+        <v>8455</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9955,25 +9912,16 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497101</v>
+        <v>497263</v>
       </c>
       <c r="R90" t="n">
-        <v>6830183</v>
+        <v>6830449</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10005,7 +9953,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10015,7 +9963,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10024,51 +9972,50 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130256293</v>
+        <v>130252256</v>
       </c>
       <c r="B91" t="n">
-        <v>78976</v>
+        <v>8455</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10078,10 +10025,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497117</v>
+        <v>497168</v>
       </c>
       <c r="R91" t="n">
-        <v>6830376</v>
+        <v>6830390</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10113,7 +10060,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10123,7 +10070,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10138,44 +10085,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130256305</v>
+        <v>130252257</v>
       </c>
       <c r="B92" t="n">
-        <v>79219</v>
+        <v>8455</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10185,10 +10132,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497258</v>
+        <v>497076</v>
       </c>
       <c r="R92" t="n">
-        <v>6830560</v>
+        <v>6830213</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10220,7 +10167,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10230,7 +10177,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10245,44 +10192,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130256308</v>
+        <v>130252687</v>
       </c>
       <c r="B93" t="n">
-        <v>79219</v>
+        <v>8455</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10292,10 +10239,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497137</v>
+        <v>497050</v>
       </c>
       <c r="R93" t="n">
-        <v>6830325</v>
+        <v>6830313</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10327,7 +10274,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10337,7 +10284,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10352,57 +10299,66 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130256300</v>
+        <v>130256289</v>
       </c>
       <c r="B94" t="n">
-        <v>79219</v>
+        <v>8455</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497391</v>
+        <v>497101</v>
       </c>
       <c r="R94" t="n">
-        <v>6830230</v>
+        <v>6830183</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10434,7 +10390,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10444,7 +10400,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10453,6 +10409,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10471,45 +10428,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130257288</v>
+        <v>130257270</v>
       </c>
       <c r="B95" t="n">
-        <v>79219</v>
+        <v>8455</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497224</v>
+        <v>497113</v>
       </c>
       <c r="R95" t="n">
-        <v>6830319</v>
+        <v>6830234</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10550,6 +10516,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10568,10 +10535,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130257272</v>
+        <v>130252252</v>
       </c>
       <c r="B96" t="n">
-        <v>78976</v>
+        <v>79085</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10579,21 +10546,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10603,10 +10570,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497128</v>
+        <v>497077</v>
       </c>
       <c r="R96" t="n">
-        <v>6830345</v>
+        <v>6830219</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10636,82 +10603,85 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130257269</v>
+        <v>130252682</v>
       </c>
       <c r="B97" t="n">
-        <v>57055</v>
+        <v>79085</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497271</v>
+        <v>497144</v>
       </c>
       <c r="R97" t="n">
-        <v>6830418</v>
+        <v>6830357</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10741,9 +10711,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10758,22 +10738,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130257286</v>
+        <v>130252683</v>
       </c>
       <c r="B98" t="n">
-        <v>79219</v>
+        <v>79085</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10781,21 +10761,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10805,10 +10785,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497240</v>
+        <v>497089</v>
       </c>
       <c r="R98" t="n">
-        <v>6830306</v>
+        <v>6830358</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10838,9 +10818,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10855,22 +10845,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130256296</v>
+        <v>130252684</v>
       </c>
       <c r="B99" t="n">
-        <v>78976</v>
+        <v>79085</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10878,21 +10868,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10902,10 +10892,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497074</v>
+        <v>497063</v>
       </c>
       <c r="R99" t="n">
-        <v>6830224</v>
+        <v>6830346</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10937,7 +10927,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10947,7 +10937,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10962,22 +10952,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130257290</v>
+        <v>130252685</v>
       </c>
       <c r="B100" t="n">
-        <v>79219</v>
+        <v>79085</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10985,21 +10975,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11009,10 +10999,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497200</v>
+        <v>497071</v>
       </c>
       <c r="R100" t="n">
-        <v>6830326</v>
+        <v>6830207</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11042,9 +11032,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11059,22 +11059,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130257294</v>
+        <v>130252686</v>
       </c>
       <c r="B101" t="n">
-        <v>78226</v>
+        <v>79085</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11082,21 +11082,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497072</v>
+        <v>497085</v>
       </c>
       <c r="R101" t="n">
-        <v>6830282</v>
+        <v>6830215</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11139,9 +11139,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11156,12 +11166,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11171,7 +11181,7 @@
         <v>130256286</v>
       </c>
       <c r="B102" t="n">
-        <v>78977</v>
+        <v>79085</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11275,10 +11285,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256312</v>
+        <v>130256287</v>
       </c>
       <c r="B103" t="n">
-        <v>79219</v>
+        <v>79085</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11286,21 +11296,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11310,10 +11320,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497244</v>
+        <v>497019</v>
       </c>
       <c r="R103" t="n">
-        <v>6830538</v>
+        <v>6830205</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11345,7 +11355,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11355,7 +11365,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11382,10 +11392,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256292</v>
+        <v>130256288</v>
       </c>
       <c r="B104" t="n">
-        <v>78976</v>
+        <v>79085</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11393,21 +11403,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11417,10 +11427,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497168</v>
+        <v>497067</v>
       </c>
       <c r="R104" t="n">
-        <v>6830310</v>
+        <v>6830217</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11452,7 +11462,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11462,7 +11472,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11486,6 +11496,210 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>130252246</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>497268</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6830458</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>130257263</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>497069</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6830264</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AY117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130252271</v>
+        <v>134571724</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hötjärnsbäcken, Dlr</t>
+          <t>Hötjärnsbäcken, Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497241</v>
+        <v>497151</v>
       </c>
       <c r="R2" t="n">
-        <v>6830507</v>
+        <v>6830237</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252272</v>
+        <v>134571747</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hötjärnsbäcken, Dlr</t>
+          <t>Hötjärnsbäcken, Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497084</v>
+        <v>497156</v>
       </c>
       <c r="R3" t="n">
-        <v>6830218</v>
+        <v>6830221</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252273</v>
+        <v>130252271</v>
       </c>
       <c r="B4" t="n">
         <v>93197</v>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497114</v>
+        <v>497241</v>
       </c>
       <c r="R4" t="n">
-        <v>6830195</v>
+        <v>6830507</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +939,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +949,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252697</v>
+        <v>130252272</v>
       </c>
       <c r="B5" t="n">
         <v>93197</v>
@@ -1031,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497086</v>
+        <v>497084</v>
       </c>
       <c r="R5" t="n">
-        <v>6830210</v>
+        <v>6830218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1046,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1056,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,26 +1065,25 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252698</v>
+        <v>130252273</v>
       </c>
       <c r="B6" t="n">
         <v>93197</v>
@@ -1139,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497112</v>
+        <v>497114</v>
       </c>
       <c r="R6" t="n">
-        <v>6830192</v>
+        <v>6830195</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,7 +1153,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1184,7 +1163,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,26 +1172,25 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130256313</v>
+        <v>130252697</v>
       </c>
       <c r="B7" t="n">
         <v>93197</v>
@@ -1240,28 +1218,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497260</v>
+        <v>497086</v>
       </c>
       <c r="R7" t="n">
-        <v>6830540</v>
+        <v>6830210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1260,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1270,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,19 +1286,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130256314</v>
+        <v>130252698</v>
       </c>
       <c r="B8" t="n">
         <v>93197</v>
@@ -1359,28 +1326,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497242</v>
+        <v>497112</v>
       </c>
       <c r="R8" t="n">
-        <v>6830510</v>
+        <v>6830192</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1368,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1378,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,19 +1394,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130256315</v>
+        <v>130256313</v>
       </c>
       <c r="B9" t="n">
         <v>93197</v>
@@ -1480,7 +1436,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1496,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497261</v>
+        <v>497260</v>
       </c>
       <c r="R9" t="n">
-        <v>6830529</v>
+        <v>6830540</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1487,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1541,7 +1497,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130257293</v>
+        <v>130256314</v>
       </c>
       <c r="B10" t="n">
         <v>93197</v>
@@ -1597,17 +1553,28 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497087</v>
+        <v>497242</v>
       </c>
       <c r="R10" t="n">
-        <v>6830238</v>
+        <v>6830510</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,39 +1604,50 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130257265</v>
+        <v>130256315</v>
       </c>
       <c r="B11" t="n">
-        <v>91930</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,34 +1655,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497131</v>
+        <v>497261</v>
       </c>
       <c r="R11" t="n">
-        <v>6830311</v>
+        <v>6830529</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,77 +1723,85 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252263</v>
+        <v>130257293</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497344</v>
+        <v>497087</v>
       </c>
       <c r="R12" t="n">
-        <v>6830116</v>
+        <v>6830238</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,93 +1831,77 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252264</v>
+        <v>134571180</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>93271</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hötjärnsbäcken, Dlr</t>
+          <t>Hötjärnsbäcken, Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497334</v>
+        <v>497014</v>
       </c>
       <c r="R13" t="n">
-        <v>6830124</v>
+        <v>6830152</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1944,22 +1925,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,60 +1945,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252265</v>
+        <v>134571398</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>93271</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hötjärnsbäcken, Dlr</t>
+          <t>Hötjärnsbäcken, Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497328</v>
+        <v>497100</v>
       </c>
       <c r="R14" t="n">
-        <v>6830125</v>
+        <v>6830149</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2051,22 +2031,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,60 +2051,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252266</v>
+        <v>134571459</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>93271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hötjärnsbäcken, Dlr</t>
+          <t>Hötjärnsbäcken, Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497268</v>
+        <v>497160</v>
       </c>
       <c r="R15" t="n">
-        <v>6830469</v>
+        <v>6830165</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2158,22 +2137,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,60 +2157,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252267</v>
+        <v>134571697</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>93271</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hötjärnsbäcken, Dlr</t>
+          <t>Hötjärnsbäcken, Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497178</v>
+        <v>497164</v>
       </c>
       <c r="R16" t="n">
-        <v>6830332</v>
+        <v>6830241</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2265,22 +2243,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,44 +2263,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252268</v>
+        <v>130257265</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2342,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497175</v>
+        <v>497131</v>
       </c>
       <c r="R17" t="n">
-        <v>6830390</v>
+        <v>6830311</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,19 +2343,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,19 +2360,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252269</v>
+        <v>130252263</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2443,16 +2401,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497128</v>
+        <v>497344</v>
       </c>
       <c r="R18" t="n">
-        <v>6830401</v>
+        <v>6830116</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,7 +2445,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2494,7 +2455,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,6 +2469,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2521,7 +2488,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252270</v>
+        <v>130252264</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2556,10 +2523,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497118</v>
+        <v>497334</v>
       </c>
       <c r="R19" t="n">
-        <v>6830323</v>
+        <v>6830124</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2558,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2568,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,7 +2595,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252694</v>
+        <v>130252265</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2663,10 +2630,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497321</v>
+        <v>497328</v>
       </c>
       <c r="R20" t="n">
-        <v>6830343</v>
+        <v>6830125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2665,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2675,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,19 +2690,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252695</v>
+        <v>130252266</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2770,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497166</v>
+        <v>497268</v>
       </c>
       <c r="R21" t="n">
-        <v>6830368</v>
+        <v>6830469</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2772,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2782,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,19 +2797,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252696</v>
+        <v>130252267</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2877,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497147</v>
+        <v>497178</v>
       </c>
       <c r="R22" t="n">
-        <v>6830398</v>
+        <v>6830332</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,7 +2879,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2922,7 +2889,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,19 +2904,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130256299</v>
+        <v>130252268</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2984,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497390</v>
+        <v>497175</v>
       </c>
       <c r="R23" t="n">
-        <v>6830226</v>
+        <v>6830390</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,7 +2986,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3029,7 +2996,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,19 +3011,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130256300</v>
+        <v>130252269</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3091,10 +3058,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497391</v>
+        <v>497128</v>
       </c>
       <c r="R24" t="n">
-        <v>6830230</v>
+        <v>6830401</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,7 +3093,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3136,7 +3103,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,19 +3118,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130256301</v>
+        <v>130252270</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3198,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497384</v>
+        <v>497118</v>
       </c>
       <c r="R25" t="n">
-        <v>6830217</v>
+        <v>6830323</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,7 +3200,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3243,7 +3210,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,19 +3225,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130256302</v>
+        <v>130252694</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3305,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497273</v>
+        <v>497321</v>
       </c>
       <c r="R26" t="n">
-        <v>6830394</v>
+        <v>6830343</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3340,7 +3307,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3350,7 +3317,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3365,19 +3332,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130256303</v>
+        <v>130252695</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3412,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497291</v>
+        <v>497166</v>
       </c>
       <c r="R27" t="n">
-        <v>6830488</v>
+        <v>6830368</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3447,7 +3414,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3457,7 +3424,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3472,19 +3439,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130256304</v>
+        <v>130252696</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3519,10 +3486,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497247</v>
+        <v>497147</v>
       </c>
       <c r="R28" t="n">
-        <v>6830499</v>
+        <v>6830398</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3554,7 +3521,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3564,7 +3531,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3579,19 +3546,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130256305</v>
+        <v>130256299</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3626,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497258</v>
+        <v>497390</v>
       </c>
       <c r="R29" t="n">
-        <v>6830560</v>
+        <v>6830226</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3661,7 +3628,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3671,7 +3638,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3698,7 +3665,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130256306</v>
+        <v>130256300</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3733,10 +3700,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497253</v>
+        <v>497391</v>
       </c>
       <c r="R30" t="n">
-        <v>6830351</v>
+        <v>6830230</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,7 +3735,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3778,7 +3745,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3805,7 +3772,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130256307</v>
+        <v>130256301</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3840,10 +3807,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497221</v>
+        <v>497384</v>
       </c>
       <c r="R31" t="n">
-        <v>6830314</v>
+        <v>6830217</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,7 +3842,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3885,7 +3852,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3912,7 +3879,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130256308</v>
+        <v>130256302</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -3947,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497137</v>
+        <v>497273</v>
       </c>
       <c r="R32" t="n">
-        <v>6830325</v>
+        <v>6830394</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3982,7 +3949,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3992,7 +3959,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4019,7 +3986,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130256309</v>
+        <v>130256303</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4054,10 +4021,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497156</v>
+        <v>497291</v>
       </c>
       <c r="R33" t="n">
-        <v>6830327</v>
+        <v>6830488</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4089,7 +4056,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4099,7 +4066,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4126,7 +4093,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130256310</v>
+        <v>130256304</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4161,10 +4128,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497160</v>
+        <v>497247</v>
       </c>
       <c r="R34" t="n">
-        <v>6830342</v>
+        <v>6830499</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4196,7 +4163,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4206,7 +4173,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4233,7 +4200,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130256311</v>
+        <v>130256305</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4268,10 +4235,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497159</v>
+        <v>497258</v>
       </c>
       <c r="R35" t="n">
-        <v>6830345</v>
+        <v>6830560</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4303,7 +4270,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4313,7 +4280,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4340,7 +4307,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130256312</v>
+        <v>130256306</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -4375,10 +4342,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497244</v>
+        <v>497253</v>
       </c>
       <c r="R36" t="n">
-        <v>6830538</v>
+        <v>6830351</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4410,7 +4377,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4420,7 +4387,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4447,7 +4414,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130257268</v>
+        <v>130256307</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -4482,10 +4449,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497074</v>
+        <v>497221</v>
       </c>
       <c r="R37" t="n">
-        <v>6830292</v>
+        <v>6830314</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4515,9 +4482,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4532,19 +4509,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130257278</v>
+        <v>130256308</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -4579,10 +4556,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497327</v>
+        <v>497137</v>
       </c>
       <c r="R38" t="n">
-        <v>6830133</v>
+        <v>6830325</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4612,9 +4589,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4629,19 +4616,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130257279</v>
+        <v>130256309</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -4676,10 +4663,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497320</v>
+        <v>497156</v>
       </c>
       <c r="R39" t="n">
-        <v>6830386</v>
+        <v>6830327</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,9 +4696,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4726,19 +4723,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130257280</v>
+        <v>130256310</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -4773,10 +4770,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497302</v>
+        <v>497160</v>
       </c>
       <c r="R40" t="n">
-        <v>6830384</v>
+        <v>6830342</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4806,9 +4803,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4823,19 +4830,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130257281</v>
+        <v>130256311</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -4870,10 +4877,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497275</v>
+        <v>497159</v>
       </c>
       <c r="R41" t="n">
-        <v>6830388</v>
+        <v>6830345</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,9 +4910,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4920,19 +4937,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130257282</v>
+        <v>130256312</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -4967,10 +4984,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497252</v>
+        <v>497244</v>
       </c>
       <c r="R42" t="n">
-        <v>6830372</v>
+        <v>6830538</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5000,9 +5017,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,19 +5044,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130257283</v>
+        <v>130257268</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -5064,10 +5091,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497244</v>
+        <v>497074</v>
       </c>
       <c r="R43" t="n">
-        <v>6830388</v>
+        <v>6830292</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5126,7 +5153,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130257284</v>
+        <v>130257278</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5161,10 +5188,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497256</v>
+        <v>497327</v>
       </c>
       <c r="R44" t="n">
-        <v>6830376</v>
+        <v>6830133</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5223,7 +5250,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130257285</v>
+        <v>130257279</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5258,10 +5285,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497250</v>
+        <v>497320</v>
       </c>
       <c r="R45" t="n">
-        <v>6830356</v>
+        <v>6830386</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5320,7 +5347,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130257286</v>
+        <v>130257280</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5355,10 +5382,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497240</v>
+        <v>497302</v>
       </c>
       <c r="R46" t="n">
-        <v>6830306</v>
+        <v>6830384</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5417,7 +5444,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130257287</v>
+        <v>130257281</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5452,10 +5479,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497234</v>
+        <v>497275</v>
       </c>
       <c r="R47" t="n">
-        <v>6830313</v>
+        <v>6830388</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5514,7 +5541,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130257288</v>
+        <v>130257282</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5549,10 +5576,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497224</v>
+        <v>497252</v>
       </c>
       <c r="R48" t="n">
-        <v>6830319</v>
+        <v>6830372</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5611,7 +5638,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130257289</v>
+        <v>130257283</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5646,10 +5673,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497222</v>
+        <v>497244</v>
       </c>
       <c r="R49" t="n">
-        <v>6830325</v>
+        <v>6830388</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5708,7 +5735,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130257290</v>
+        <v>130257284</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5743,10 +5770,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497200</v>
+        <v>497256</v>
       </c>
       <c r="R50" t="n">
-        <v>6830326</v>
+        <v>6830376</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5805,7 +5832,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130257291</v>
+        <v>130257285</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5840,10 +5867,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497164</v>
+        <v>497250</v>
       </c>
       <c r="R51" t="n">
-        <v>6830343</v>
+        <v>6830356</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5902,7 +5929,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130257292</v>
+        <v>130257286</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -5937,10 +5964,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497138</v>
+        <v>497240</v>
       </c>
       <c r="R52" t="n">
-        <v>6830320</v>
+        <v>6830306</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5999,32 +6026,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130257297</v>
+        <v>130257287</v>
       </c>
       <c r="B53" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6034,10 +6061,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497072</v>
+        <v>497234</v>
       </c>
       <c r="R53" t="n">
-        <v>6830261</v>
+        <v>6830313</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6096,32 +6123,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130252258</v>
+        <v>130257288</v>
       </c>
       <c r="B54" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6131,10 +6158,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497245</v>
+        <v>497224</v>
       </c>
       <c r="R54" t="n">
-        <v>6830449</v>
+        <v>6830319</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6164,19 +6191,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6191,44 +6208,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130252259</v>
+        <v>130257289</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6238,10 +6255,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497236</v>
+        <v>497222</v>
       </c>
       <c r="R55" t="n">
-        <v>6830502</v>
+        <v>6830325</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6271,19 +6288,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6298,44 +6305,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130252260</v>
+        <v>130257290</v>
       </c>
       <c r="B56" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6345,10 +6352,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497077</v>
+        <v>497200</v>
       </c>
       <c r="R56" t="n">
-        <v>6830219</v>
+        <v>6830326</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6378,19 +6385,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6405,44 +6402,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130252261</v>
+        <v>130257291</v>
       </c>
       <c r="B57" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6452,10 +6449,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497167</v>
+        <v>497164</v>
       </c>
       <c r="R57" t="n">
-        <v>6830200</v>
+        <v>6830343</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6485,19 +6482,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6512,44 +6499,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130252262</v>
+        <v>130257292</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6559,10 +6546,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497260</v>
+        <v>497138</v>
       </c>
       <c r="R58" t="n">
-        <v>6830494</v>
+        <v>6830320</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6592,85 +6579,74 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130252688</v>
+        <v>134571646</v>
       </c>
       <c r="B59" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hötjärnsbäcken, Dlr</t>
+          <t>Hötjärnsbäcken, Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497300</v>
+        <v>497195</v>
       </c>
       <c r="R59" t="n">
-        <v>6830438</v>
+        <v>6830230</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6697,22 +6673,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6727,60 +6693,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130252689</v>
+        <v>134571655</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hötjärnsbäcken, Dlr</t>
+          <t>Hötjärnsbäcken, Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497261</v>
+        <v>497191</v>
       </c>
       <c r="R60" t="n">
-        <v>6830425</v>
+        <v>6830231</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6804,22 +6770,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6834,22 +6790,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130252690</v>
+        <v>130257297</v>
       </c>
       <c r="B61" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6857,21 +6813,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6881,10 +6837,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497163</v>
+        <v>497072</v>
       </c>
       <c r="R61" t="n">
-        <v>6830392</v>
+        <v>6830261</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6914,19 +6870,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6941,19 +6887,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130252691</v>
+        <v>130252258</v>
       </c>
       <c r="B62" t="n">
         <v>79084</v>
@@ -6988,10 +6934,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497108</v>
+        <v>497245</v>
       </c>
       <c r="R62" t="n">
-        <v>6830371</v>
+        <v>6830449</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7023,7 +6969,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7033,7 +6979,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7048,19 +6994,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130252692</v>
+        <v>130252259</v>
       </c>
       <c r="B63" t="n">
         <v>79084</v>
@@ -7095,10 +7041,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497090</v>
+        <v>497236</v>
       </c>
       <c r="R63" t="n">
-        <v>6830366</v>
+        <v>6830502</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7130,7 +7076,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7140,7 +7086,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7155,19 +7101,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130252693</v>
+        <v>130252260</v>
       </c>
       <c r="B64" t="n">
         <v>79084</v>
@@ -7202,10 +7148,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497066</v>
+        <v>497077</v>
       </c>
       <c r="R64" t="n">
-        <v>6830179</v>
+        <v>6830219</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7237,7 +7183,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7247,7 +7193,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7262,19 +7208,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130256291</v>
+        <v>130252261</v>
       </c>
       <c r="B65" t="n">
         <v>79084</v>
@@ -7309,10 +7255,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497251</v>
+        <v>497167</v>
       </c>
       <c r="R65" t="n">
-        <v>6830491</v>
+        <v>6830200</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7344,7 +7290,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7354,7 +7300,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7369,19 +7315,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130256292</v>
+        <v>130252262</v>
       </c>
       <c r="B66" t="n">
         <v>79084</v>
@@ -7416,10 +7362,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497168</v>
+        <v>497260</v>
       </c>
       <c r="R66" t="n">
-        <v>6830310</v>
+        <v>6830494</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7451,7 +7397,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7461,7 +7407,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7470,25 +7416,26 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130256293</v>
+        <v>130252688</v>
       </c>
       <c r="B67" t="n">
         <v>79084</v>
@@ -7523,10 +7470,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497117</v>
+        <v>497300</v>
       </c>
       <c r="R67" t="n">
-        <v>6830376</v>
+        <v>6830438</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7558,7 +7505,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7568,7 +7515,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7583,19 +7530,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130256295</v>
+        <v>130252689</v>
       </c>
       <c r="B68" t="n">
         <v>79084</v>
@@ -7630,10 +7577,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497019</v>
+        <v>497261</v>
       </c>
       <c r="R68" t="n">
-        <v>6830205</v>
+        <v>6830425</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7665,7 +7612,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7675,7 +7622,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7690,19 +7637,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130256296</v>
+        <v>130252690</v>
       </c>
       <c r="B69" t="n">
         <v>79084</v>
@@ -7737,10 +7684,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497074</v>
+        <v>497163</v>
       </c>
       <c r="R69" t="n">
-        <v>6830224</v>
+        <v>6830392</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7772,7 +7719,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7782,7 +7729,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7797,19 +7744,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130256297</v>
+        <v>130252691</v>
       </c>
       <c r="B70" t="n">
         <v>79084</v>
@@ -7844,10 +7791,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497115</v>
+        <v>497108</v>
       </c>
       <c r="R70" t="n">
-        <v>6830196</v>
+        <v>6830371</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7879,7 +7826,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7889,7 +7836,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7904,19 +7851,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130257271</v>
+        <v>130252692</v>
       </c>
       <c r="B71" t="n">
         <v>79084</v>
@@ -7951,10 +7898,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497270</v>
+        <v>497090</v>
       </c>
       <c r="R71" t="n">
-        <v>6830422</v>
+        <v>6830366</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7984,9 +7931,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8001,19 +7958,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130257272</v>
+        <v>130252693</v>
       </c>
       <c r="B72" t="n">
         <v>79084</v>
@@ -8048,10 +8005,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497128</v>
+        <v>497066</v>
       </c>
       <c r="R72" t="n">
-        <v>6830345</v>
+        <v>6830179</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8081,9 +8038,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8098,19 +8065,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130257274</v>
+        <v>130256291</v>
       </c>
       <c r="B73" t="n">
         <v>79084</v>
@@ -8145,10 +8112,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497107</v>
+        <v>497251</v>
       </c>
       <c r="R73" t="n">
-        <v>6830221</v>
+        <v>6830491</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8178,9 +8145,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8195,19 +8172,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130257275</v>
+        <v>130256292</v>
       </c>
       <c r="B74" t="n">
         <v>79084</v>
@@ -8242,10 +8219,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497096</v>
+        <v>497168</v>
       </c>
       <c r="R74" t="n">
-        <v>6830218</v>
+        <v>6830310</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8275,9 +8252,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8292,19 +8279,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130257276</v>
+        <v>130256293</v>
       </c>
       <c r="B75" t="n">
         <v>79084</v>
@@ -8339,10 +8326,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497082</v>
+        <v>497117</v>
       </c>
       <c r="R75" t="n">
-        <v>6830202</v>
+        <v>6830376</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8372,9 +8359,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8389,19 +8386,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130257277</v>
+        <v>130256295</v>
       </c>
       <c r="B76" t="n">
         <v>79084</v>
@@ -8436,10 +8433,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497092</v>
+        <v>497019</v>
       </c>
       <c r="R76" t="n">
-        <v>6830180</v>
+        <v>6830205</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8469,9 +8466,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8486,22 +8493,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130252244</v>
+        <v>130256296</v>
       </c>
       <c r="B77" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8509,21 +8516,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8533,10 +8540,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497260</v>
+        <v>497074</v>
       </c>
       <c r="R77" t="n">
-        <v>6830494</v>
+        <v>6830224</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8568,7 +8575,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8578,7 +8585,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8593,22 +8600,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130252245</v>
+        <v>130256297</v>
       </c>
       <c r="B78" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8616,21 +8623,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8640,10 +8647,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497169</v>
+        <v>497115</v>
       </c>
       <c r="R78" t="n">
-        <v>6830390</v>
+        <v>6830196</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8675,7 +8682,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8685,7 +8692,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8700,22 +8707,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130257261</v>
+        <v>130257271</v>
       </c>
       <c r="B79" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8723,21 +8730,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8747,10 +8754,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497107</v>
+        <v>497270</v>
       </c>
       <c r="R79" t="n">
-        <v>6830221</v>
+        <v>6830422</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8809,10 +8816,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130257262</v>
+        <v>130257272</v>
       </c>
       <c r="B80" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8820,21 +8827,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8847,7 +8854,7 @@
         <v>497128</v>
       </c>
       <c r="R80" t="n">
-        <v>6830348</v>
+        <v>6830345</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8906,10 +8913,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130257294</v>
+        <v>130257274</v>
       </c>
       <c r="B81" t="n">
-        <v>78334</v>
+        <v>79084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8917,21 +8924,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8941,10 +8948,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497072</v>
+        <v>497107</v>
       </c>
       <c r="R81" t="n">
-        <v>6830282</v>
+        <v>6830221</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9003,10 +9010,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130257295</v>
+        <v>130257275</v>
       </c>
       <c r="B82" t="n">
-        <v>78334</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9014,21 +9021,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9038,10 +9045,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497072</v>
+        <v>497096</v>
       </c>
       <c r="R82" t="n">
-        <v>6830261</v>
+        <v>6830218</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9100,10 +9107,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130257266</v>
+        <v>130257276</v>
       </c>
       <c r="B83" t="n">
-        <v>57953</v>
+        <v>79084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9111,42 +9118,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497142</v>
+        <v>497082</v>
       </c>
       <c r="R83" t="n">
-        <v>6830327</v>
+        <v>6830202</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9205,53 +9204,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130252248</v>
+        <v>130257277</v>
       </c>
       <c r="B84" t="n">
-        <v>57141</v>
+        <v>79084</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497253</v>
+        <v>497092</v>
       </c>
       <c r="R84" t="n">
-        <v>6830469</v>
+        <v>6830180</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9281,24 +9272,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9313,65 +9289,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130257269</v>
+        <v>134571518</v>
       </c>
       <c r="B85" t="n">
-        <v>57144</v>
+        <v>79130</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hötjärnsbäcken, Dlr</t>
+          <t>Hötjärnsbäcken, Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497271</v>
+        <v>497205</v>
       </c>
       <c r="R85" t="n">
-        <v>6830418</v>
+        <v>6830184</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9398,12 +9366,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9418,22 +9386,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130252250</v>
+        <v>130252244</v>
       </c>
       <c r="B86" t="n">
-        <v>58114</v>
+        <v>79946</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9441,46 +9409,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497113</v>
+        <v>497260</v>
       </c>
       <c r="R86" t="n">
-        <v>6830338</v>
+        <v>6830494</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9512,7 +9468,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9522,12 +9478,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Var i ett meståg med bla. trädkrypare</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9554,10 +9505,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130252251</v>
+        <v>130252245</v>
       </c>
       <c r="B87" t="n">
-        <v>58114</v>
+        <v>79946</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9565,42 +9516,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497063</v>
+        <v>497169</v>
       </c>
       <c r="R87" t="n">
-        <v>6830279</v>
+        <v>6830390</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9632,7 +9575,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9642,7 +9585,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9669,32 +9612,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130252253</v>
+        <v>130257261</v>
       </c>
       <c r="B88" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9704,10 +9647,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497334</v>
+        <v>497107</v>
       </c>
       <c r="R88" t="n">
-        <v>6830121</v>
+        <v>6830221</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9737,19 +9680,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9764,44 +9697,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130252254</v>
+        <v>130257262</v>
       </c>
       <c r="B89" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9811,10 +9744,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497253</v>
+        <v>497128</v>
       </c>
       <c r="R89" t="n">
-        <v>6830488</v>
+        <v>6830348</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9844,19 +9777,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9871,44 +9794,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130252255</v>
+        <v>130257294</v>
       </c>
       <c r="B90" t="n">
-        <v>8455</v>
+        <v>78334</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6487</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9918,10 +9841,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497263</v>
+        <v>497072</v>
       </c>
       <c r="R90" t="n">
-        <v>6830449</v>
+        <v>6830282</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9951,19 +9874,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9978,44 +9891,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130252256</v>
+        <v>130257295</v>
       </c>
       <c r="B91" t="n">
-        <v>8455</v>
+        <v>78334</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6487</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10025,10 +9938,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497168</v>
+        <v>497072</v>
       </c>
       <c r="R91" t="n">
-        <v>6830390</v>
+        <v>6830261</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10058,19 +9971,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:49</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10085,57 +9988,65 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130252257</v>
+        <v>130257266</v>
       </c>
       <c r="B92" t="n">
-        <v>8455</v>
+        <v>57953</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497076</v>
+        <v>497142</v>
       </c>
       <c r="R92" t="n">
-        <v>6830213</v>
+        <v>6830327</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10165,19 +10076,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>09:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10192,57 +10093,57 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130252687</v>
+        <v>134571458</v>
       </c>
       <c r="B93" t="n">
-        <v>8455</v>
+        <v>57975</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hötjärnsbäcken, Dlr</t>
+          <t>Hötjärnsbäcken, Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497050</v>
+        <v>497175</v>
       </c>
       <c r="R93" t="n">
-        <v>6830313</v>
+        <v>6830149</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10269,22 +10170,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10299,22 +10195,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130256289</v>
+        <v>130252248</v>
       </c>
       <c r="B94" t="n">
-        <v>8455</v>
+        <v>57141</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10322,30 +10218,29 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10355,10 +10250,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497101</v>
+        <v>497253</v>
       </c>
       <c r="R94" t="n">
-        <v>6830183</v>
+        <v>6830469</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10390,7 +10285,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10400,7 +10295,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Spillning på mark</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10409,29 +10309,28 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130257270</v>
+        <v>130257269</v>
       </c>
       <c r="B95" t="n">
-        <v>8455</v>
+        <v>57144</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10439,30 +10338,29 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>102613</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10472,10 +10370,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497113</v>
+        <v>497271</v>
       </c>
       <c r="R95" t="n">
-        <v>6830234</v>
+        <v>6830418</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10516,7 +10414,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10535,10 +10432,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130252252</v>
+        <v>130252250</v>
       </c>
       <c r="B96" t="n">
-        <v>79085</v>
+        <v>58114</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10546,34 +10443,46 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497077</v>
+        <v>497113</v>
       </c>
       <c r="R96" t="n">
-        <v>6830219</v>
+        <v>6830338</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10605,7 +10514,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10615,7 +10524,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Var i ett meståg med bla. trädkrypare</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10624,7 +10538,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10643,10 +10556,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130252682</v>
+        <v>130252251</v>
       </c>
       <c r="B97" t="n">
-        <v>79085</v>
+        <v>58114</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10654,34 +10567,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497144</v>
+        <v>497063</v>
       </c>
       <c r="R97" t="n">
-        <v>6830357</v>
+        <v>6830279</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10713,7 +10634,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10723,7 +10644,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10738,44 +10659,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130252683</v>
+        <v>130252253</v>
       </c>
       <c r="B98" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10785,10 +10706,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497089</v>
+        <v>497334</v>
       </c>
       <c r="R98" t="n">
-        <v>6830358</v>
+        <v>6830121</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10820,7 +10741,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10830,7 +10751,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10845,44 +10766,44 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130252684</v>
+        <v>130252254</v>
       </c>
       <c r="B99" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10892,10 +10813,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497063</v>
+        <v>497253</v>
       </c>
       <c r="R99" t="n">
-        <v>6830346</v>
+        <v>6830488</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10927,7 +10848,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10937,7 +10858,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10952,44 +10873,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130252685</v>
+        <v>130252255</v>
       </c>
       <c r="B100" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10999,10 +10920,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497071</v>
+        <v>497263</v>
       </c>
       <c r="R100" t="n">
-        <v>6830207</v>
+        <v>6830449</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11034,7 +10955,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11044,7 +10965,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11059,44 +10980,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130252686</v>
+        <v>130252256</v>
       </c>
       <c r="B101" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11106,10 +11027,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497085</v>
+        <v>497168</v>
       </c>
       <c r="R101" t="n">
-        <v>6830215</v>
+        <v>6830390</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11141,7 +11062,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11151,7 +11072,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11166,44 +11087,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256286</v>
+        <v>130252257</v>
       </c>
       <c r="B102" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11213,10 +11134,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497251</v>
+        <v>497076</v>
       </c>
       <c r="R102" t="n">
-        <v>6830494</v>
+        <v>6830213</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11248,7 +11169,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11258,7 +11179,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11273,44 +11194,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256287</v>
+        <v>130252687</v>
       </c>
       <c r="B103" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11320,10 +11241,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497019</v>
+        <v>497050</v>
       </c>
       <c r="R103" t="n">
-        <v>6830205</v>
+        <v>6830313</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11355,7 +11276,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11365,7 +11286,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11380,57 +11301,66 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256288</v>
+        <v>130256289</v>
       </c>
       <c r="B104" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497067</v>
+        <v>497101</v>
       </c>
       <c r="R104" t="n">
-        <v>6830217</v>
+        <v>6830183</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11462,7 +11392,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11472,7 +11402,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11481,6 +11411,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11499,45 +11430,54 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130252246</v>
+        <v>130257270</v>
       </c>
       <c r="B105" t="n">
-        <v>79917</v>
+        <v>8455</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Hötjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497268</v>
+        <v>497113</v>
       </c>
       <c r="R105" t="n">
-        <v>6830458</v>
+        <v>6830234</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11567,49 +11507,40 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130257263</v>
+        <v>130252252</v>
       </c>
       <c r="B106" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11617,21 +11548,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11641,10 +11572,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497069</v>
+        <v>497077</v>
       </c>
       <c r="R106" t="n">
-        <v>6830264</v>
+        <v>6830219</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11674,32 +11605,1200 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>130252682</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>497144</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6830357</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>130252683</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>497089</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6830358</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>130252684</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>497063</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6830346</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>130252685</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>497071</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6830207</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>130252686</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>497085</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6830215</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>130256286</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>497251</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6830494</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>130256287</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>497019</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6830205</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>130256288</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>497067</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6830217</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>134571157</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>497014</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6830154</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>130252246</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>497268</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6830458</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>130257263</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Hötjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>497069</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6830264</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
           <t>Lisa Olson</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
+      <c r="AX117" t="inlineStr">
         <is>
           <t>Lisa Olson</t>
         </is>
       </c>
-      <c r="AY106" t="inlineStr"/>
+      <c r="AY117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59809-2025 artfynd.xlsx
+++ b/artfynd/A 59809-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AZ117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134571724</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134571747</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252271</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252272</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252273</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252697</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252698</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256313</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256314</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256315</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1857,6 +1912,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257293</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1954,6 +2014,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134571180</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2060,6 +2125,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134571398</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2166,6 +2236,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134571459</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134571697</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2369,6 +2449,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257265</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2485,6 +2570,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252263</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2592,6 +2682,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252264</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2699,6 +2794,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252265</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2806,6 +2906,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252266</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2913,6 +3018,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252267</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3020,6 +3130,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252268</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3127,6 +3242,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252269</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3234,6 +3354,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252270</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3341,6 +3466,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252694</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3448,6 +3578,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252695</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3555,6 +3690,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252696</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3662,6 +3802,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256299</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3769,6 +3914,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256300</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3876,6 +4026,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256301</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3983,6 +4138,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256302</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4090,6 +4250,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256303</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4197,6 +4362,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256304</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4304,6 +4474,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256305</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4411,6 +4586,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256306</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4518,6 +4698,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256307</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4625,6 +4810,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256308</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4732,6 +4922,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256309</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4839,6 +5034,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256310</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4946,6 +5146,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256311</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5053,6 +5258,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256312</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5150,6 +5360,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257268</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5247,6 +5462,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257278</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5344,6 +5564,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257279</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5441,6 +5666,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257280</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5538,6 +5768,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257281</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5635,6 +5870,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257282</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5732,6 +5972,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257283</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5829,6 +6074,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257284</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5926,6 +6176,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257285</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6023,6 +6278,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257286</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6120,6 +6380,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257287</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6217,6 +6482,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257288</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6314,6 +6584,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257289</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6411,6 +6686,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257290</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6508,6 +6788,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257291</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6605,6 +6890,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257292</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6702,6 +6992,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134571646</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6799,6 +7094,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134571655</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6896,6 +7196,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257297</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7003,6 +7308,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252258</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7110,6 +7420,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252259</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7217,6 +7532,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252260</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7324,6 +7644,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252261</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7432,6 +7757,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252262</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7539,6 +7869,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252688</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7646,6 +7981,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252689</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7753,6 +8093,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252690</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7860,6 +8205,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252691</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7967,6 +8317,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252692</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8074,6 +8429,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252693</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8181,6 +8541,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256291</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8288,6 +8653,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256292</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8395,6 +8765,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256293</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8502,6 +8877,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256295</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8609,6 +8989,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256296</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8716,6 +9101,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256297</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8813,6 +9203,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257271</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8910,6 +9305,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257272</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9007,6 +9407,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257274</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9104,6 +9509,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257275</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9201,6 +9611,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257276</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9298,6 +9713,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257277</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9395,6 +9815,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134571518</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9502,6 +9927,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252244</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9609,6 +10039,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252245</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9706,6 +10141,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257261</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9803,6 +10243,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257262</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9900,6 +10345,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257294</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9997,6 +10447,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257295</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10102,6 +10557,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257266</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10204,6 +10664,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134571458</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10324,6 +10789,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252248</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10429,6 +10899,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257269</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10553,6 +11028,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252250</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10668,6 +11148,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252251</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10775,6 +11260,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252253</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10882,6 +11372,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252254</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10989,6 +11484,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252255</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11096,6 +11596,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252256</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11203,6 +11708,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252257</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11310,6 +11820,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252687</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11427,6 +11942,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256289</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11534,6 +12054,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257270</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11642,6 +12167,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252252</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11749,6 +12279,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252682</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11856,6 +12391,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252683</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11963,6 +12503,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252684</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12070,6 +12615,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252685</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12177,6 +12727,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252686</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12284,6 +12839,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256286</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12391,6 +12951,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256287</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12498,6 +13063,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256288</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12595,6 +13165,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134571157</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12702,6 +13277,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252246</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12799,8 +13379,131 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257263</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>